--- a/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2361.51</v>
+        <v>27481.23</v>
       </c>
       <c r="C4" t="n">
-        <v>586656</v>
+        <v>5357016</v>
       </c>
       <c r="D4" t="n">
-        <v>460944</v>
+        <v>4209084</v>
       </c>
       <c r="E4" t="n">
-        <v>147600</v>
+        <v>1458900</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>6570</v>
+        <v>80040</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>9030</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>19620</v>
+        <v>196890</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3908.25</v>
+        <v>29785.41</v>
       </c>
       <c r="C5" t="n">
-        <v>686952</v>
+        <v>4628736</v>
       </c>
       <c r="D5" t="n">
-        <v>539748</v>
+        <v>3636864</v>
       </c>
       <c r="E5" t="n">
-        <v>118800</v>
+        <v>1080900</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>8640</v>
+        <v>87150</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7590</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20700</v>
+        <v>188610</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3989.34</v>
+        <v>35365.86</v>
       </c>
       <c r="C6" t="n">
-        <v>405216</v>
+        <v>4842432</v>
       </c>
       <c r="D6" t="n">
-        <v>318384</v>
+        <v>3804768</v>
       </c>
       <c r="E6" t="n">
-        <v>65700</v>
+        <v>873900</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>8280</v>
+        <v>86550</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>12180</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>23100</v>
+        <v>211140</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2622.78</v>
+        <v>27571.23</v>
       </c>
       <c r="C7" t="n">
-        <v>228816</v>
+        <v>2283624</v>
       </c>
       <c r="D7" t="n">
-        <v>179784</v>
+        <v>1794276</v>
       </c>
       <c r="E7" t="n">
-        <v>39600</v>
+        <v>253800</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4950</v>
+        <v>62130</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3930</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10140</v>
+        <v>134220</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1352.25</v>
+        <v>23269.05</v>
       </c>
       <c r="C8" t="n">
-        <v>65520</v>
+        <v>1693944</v>
       </c>
       <c r="D8" t="n">
-        <v>51480</v>
+        <v>1330956</v>
       </c>
       <c r="E8" t="n">
-        <v>8100</v>
+        <v>141300</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1860</v>
+        <v>36330</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3900</v>
+        <v>77160</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>646.74</v>
+        <v>13253.67</v>
       </c>
       <c r="C9" t="n">
-        <v>18144</v>
+        <v>886032</v>
       </c>
       <c r="D9" t="n">
-        <v>14256</v>
+        <v>696168</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>48600</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>810</v>
+        <v>22380</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10057,13 +10051,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>780</v>
+        <v>40890</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>393.48</v>
+        <v>1616.13</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>119448</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>93852</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>2820</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>630</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>222.21</v>
+        <v>330.39</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>39816</v>
       </c>
       <c r="D11" t="n">
-        <v>1980</v>
+        <v>31284</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>1080</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.24</v>
+        <v>191.88</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>10080</v>
       </c>
       <c r="D12" t="n">
-        <v>1188</v>
+        <v>7920</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>166.86</v>
+        <v>113.22</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>52.38</v>
+        <v>13.14</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1980</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.68</v>
+        <v>17.64</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>11.34</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>5.04</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19">
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1758.71</v>
+        <v>13403.43</v>
       </c>
       <c r="C5" t="n">
-        <v>377823.6</v>
+        <v>2545804.8</v>
       </c>
       <c r="D5" t="n">
-        <v>178656.59</v>
+        <v>1203801.98</v>
       </c>
       <c r="E5" t="n">
-        <v>13103.64</v>
+        <v>119223.27</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2732.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4347</v>
+        <v>39608.1</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3191.47</v>
+        <v>28292.69</v>
       </c>
       <c r="C6" t="n">
-        <v>364694.4</v>
+        <v>4358188.8</v>
       </c>
       <c r="D6" t="n">
-        <v>161420.69</v>
+        <v>1929017.38</v>
       </c>
       <c r="E6" t="n">
-        <v>11103.3</v>
+        <v>147689.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>414</v>
+        <v>4327.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6942.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8547</v>
+        <v>78121.8</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2491.64</v>
+        <v>26192.67</v>
       </c>
       <c r="C7" t="n">
-        <v>228816</v>
+        <v>2283624</v>
       </c>
       <c r="D7" t="n">
-        <v>114702.19</v>
+        <v>1144748.09</v>
       </c>
       <c r="E7" t="n">
-        <v>8422.92</v>
+        <v>53983.26</v>
       </c>
       <c r="F7" t="n">
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>742.5</v>
+        <v>9319.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2868.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6084</v>
+        <v>80532</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1352.25</v>
+        <v>23269.05</v>
       </c>
       <c r="C8" t="n">
-        <v>65520</v>
+        <v>1693944</v>
       </c>
       <c r="D8" t="n">
-        <v>37889.28</v>
+        <v>979583.62</v>
       </c>
       <c r="E8" t="n">
-        <v>1986.93</v>
+        <v>34660.89</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1209</v>
+        <v>23614.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2769</v>
+        <v>54783.6</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>646.74</v>
+        <v>13253.67</v>
       </c>
       <c r="C9" t="n">
-        <v>18144</v>
+        <v>886032</v>
       </c>
       <c r="D9" t="n">
-        <v>11447.57</v>
+        <v>559022.9</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>13010.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>688.5</v>
+        <v>19023</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11921,13 +11915,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>631.8</v>
+        <v>33120.9</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>393.48</v>
+        <v>1616.13</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>119448</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>81651.24000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1305</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>2820</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>560.7</v>
+        <v>9478.5</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>222.21</v>
+        <v>330.39</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>39816</v>
       </c>
       <c r="D11" t="n">
-        <v>1779.03</v>
+        <v>28108.67</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>368.82</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>1080</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.24</v>
+        <v>191.88</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>10080</v>
       </c>
       <c r="D12" t="n">
-        <v>1101.28</v>
+        <v>7341.84</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>166.86</v>
+        <v>113.22</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1880.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>52.38</v>
+        <v>13.14</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1924.56</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.68</v>
+        <v>17.64</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1171.37</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>11.34</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>5.04</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19">
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3869167.5</v>
+        <v>29487555.9</v>
       </c>
       <c r="C5" t="n">
-        <v>20780298</v>
+        <v>140019264</v>
       </c>
       <c r="D5" t="n">
-        <v>18103272.06</v>
+        <v>121981255.04</v>
       </c>
       <c r="E5" t="n">
-        <v>2414214.63</v>
+        <v>21965695.26</v>
       </c>
       <c r="F5" t="n">
-        <v>3333.36</v>
+        <v>17500.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>755918.46</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>157499.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40948.74</v>
+        <v>373108.3</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7021238.4</v>
+        <v>62243913.6</v>
       </c>
       <c r="C6" t="n">
-        <v>20058192</v>
+        <v>239700384</v>
       </c>
       <c r="D6" t="n">
-        <v>16356758.32</v>
+        <v>195467330.71</v>
       </c>
       <c r="E6" t="n">
-        <v>2045671.99</v>
+        <v>27210239.78</v>
       </c>
       <c r="F6" t="n">
-        <v>20833.5</v>
+        <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7659</v>
+        <v>80058.75</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1920670.29</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>58333</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>80512.74000000001</v>
+        <v>735907.36</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5481610.2</v>
+        <v>57623870.7</v>
       </c>
       <c r="C7" t="n">
-        <v>12584880</v>
+        <v>125599320</v>
       </c>
       <c r="D7" t="n">
-        <v>11622773.12</v>
+        <v>115997323.76</v>
       </c>
       <c r="E7" t="n">
-        <v>1551838.78</v>
+        <v>9945875.82</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13736.25</v>
+        <v>172410.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>793681.1800000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>57311.28</v>
+        <v>758611.4399999999</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2974950</v>
+        <v>51191910</v>
       </c>
       <c r="C8" t="n">
-        <v>3603600</v>
+        <v>93166920</v>
       </c>
       <c r="D8" t="n">
-        <v>3839320.74</v>
+        <v>99261207.81</v>
       </c>
       <c r="E8" t="n">
-        <v>366071.98</v>
+        <v>6385922.37</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>22366.5</v>
+        <v>436868.25</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>112873.2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26083.98</v>
+        <v>516061.51</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1422828</v>
+        <v>29158074</v>
       </c>
       <c r="C9" t="n">
-        <v>997920</v>
+        <v>48731760</v>
       </c>
       <c r="D9" t="n">
-        <v>1159982.07</v>
+        <v>56645790.86</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>2397002.93</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12737.25</v>
+        <v>351925.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12853,13 +12847,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5951.56</v>
+        <v>311998.88</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>865656</v>
+        <v>3555486</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>6569640</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>8273720.15</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>240433.2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7770</v>
+        <v>52170</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5281.79</v>
+        <v>89287.47</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>488862</v>
+        <v>726858</v>
       </c>
       <c r="C11" t="n">
-        <v>138600</v>
+        <v>2189880</v>
       </c>
       <c r="D11" t="n">
-        <v>180269.11</v>
+        <v>2848251.94</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>67951.39999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>19980</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>43803</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>343728</v>
+        <v>422136</v>
       </c>
       <c r="C12" t="n">
-        <v>83160</v>
+        <v>554400</v>
       </c>
       <c r="D12" t="n">
-        <v>111592.3</v>
+        <v>743948.65</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>79260.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>4440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>33912</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>367092</v>
+        <v>249084</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>190501.41</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>6105</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>16108.2</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>115236</v>
+        <v>28908</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>138600</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>195015.66</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>1665</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>8478</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>10296</v>
+        <v>38808</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118694.72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3108.6</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>24948</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>120380.04</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>11088</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2970</v>
+        <v>3564</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4440</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>5369.4</v>
       </c>
     </row>
     <row r="19">
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>198</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>67710</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="20">
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>160506.72</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>166320</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>240760.08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>27481.23</v>
+        <v>28322.1</v>
       </c>
       <c r="C4" t="n">
-        <v>5357016</v>
+        <v>2831976</v>
       </c>
       <c r="D4" t="n">
-        <v>4209084</v>
+        <v>2225124</v>
       </c>
       <c r="E4" t="n">
-        <v>1458900</v>
+        <v>892800</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>80040</v>
+        <v>84540</v>
       </c>
       <c r="H4" t="n">
-        <v>9030</v>
+        <v>9930</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>196890</v>
+        <v>274530</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29785.41</v>
+        <v>7971.66</v>
       </c>
       <c r="C5" t="n">
-        <v>4628736</v>
+        <v>546840</v>
       </c>
       <c r="D5" t="n">
-        <v>3636864</v>
+        <v>429660</v>
       </c>
       <c r="E5" t="n">
-        <v>1080900</v>
+        <v>212400</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>87150</v>
+        <v>19020</v>
       </c>
       <c r="H5" t="n">
-        <v>7590</v>
+        <v>1860</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>188610</v>
+        <v>80880</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>35365.86</v>
+        <v>703.8</v>
       </c>
       <c r="C6" t="n">
-        <v>4842432</v>
+        <v>63504</v>
       </c>
       <c r="D6" t="n">
-        <v>3804768</v>
+        <v>49896</v>
       </c>
       <c r="E6" t="n">
-        <v>873900</v>
+        <v>19800</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>86550</v>
+        <v>1920</v>
       </c>
       <c r="H6" t="n">
-        <v>12180</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>211140</v>
+        <v>12240</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>27571.23</v>
+        <v>105.57</v>
       </c>
       <c r="C7" t="n">
-        <v>2283624</v>
+        <v>13104</v>
       </c>
       <c r="D7" t="n">
-        <v>1794276</v>
+        <v>10296</v>
       </c>
       <c r="E7" t="n">
-        <v>253800</v>
+        <v>2700</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>62130</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>3930</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>134220</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23269.05</v>
+        <v>7.92</v>
       </c>
       <c r="C8" t="n">
-        <v>1693944</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1330956</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>141300</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>36330</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>77160</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>13253.67</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>886032</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>696168</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>48600</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>22380</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13785,13 +13779,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>40890</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1616.13</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>119448</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>93852</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2820</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>10650</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>330.39</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>39816</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>31284</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4650</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>191.88</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10080</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>7920</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>113.22</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.14</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>11.34</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,13 +14135,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3660</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13403.43</v>
+        <v>3587.25</v>
       </c>
       <c r="C5" t="n">
-        <v>2545804.8</v>
+        <v>300762</v>
       </c>
       <c r="D5" t="n">
-        <v>1203801.98</v>
+        <v>142217.46</v>
       </c>
       <c r="E5" t="n">
-        <v>119223.27</v>
+        <v>23427.72</v>
       </c>
       <c r="F5" t="n">
-        <v>0.42</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2732.4</v>
+        <v>669.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>39608.1</v>
+        <v>16984.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>28292.69</v>
+        <v>563.04</v>
       </c>
       <c r="C6" t="n">
-        <v>4358188.8</v>
+        <v>57153.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1929017.38</v>
+        <v>25297.27</v>
       </c>
       <c r="E6" t="n">
-        <v>147689.1</v>
+        <v>3346.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4327.5</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
-        <v>6942.6</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>78121.8</v>
+        <v>4528.8</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>26192.67</v>
+        <v>100.29</v>
       </c>
       <c r="C7" t="n">
-        <v>2283624</v>
+        <v>13104</v>
       </c>
       <c r="D7" t="n">
-        <v>1144748.09</v>
+        <v>6568.85</v>
       </c>
       <c r="E7" t="n">
-        <v>53983.26</v>
+        <v>574.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9319.5</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>2868.9</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>80532</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23269.05</v>
+        <v>7.92</v>
       </c>
       <c r="C8" t="n">
-        <v>1693944</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>979583.62</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>34660.89</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>23614.5</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>54783.6</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>13253.67</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>886032</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>559022.9</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>13010.22</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>19023</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14717,13 +14711,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>33120.9</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1616.13</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>119448</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>81651.24000000001</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1305</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2820</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9478.5</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>330.39</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>39816</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>28108.67</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>368.82</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4650</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>191.88</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10080</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>7341.84</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>113.22</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1880.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.14</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1924.56</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1171.37</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>11.34</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,13 +15067,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3660</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29487555.9</v>
+        <v>7891943.4</v>
       </c>
       <c r="C5" t="n">
-        <v>140019264</v>
+        <v>16541910</v>
       </c>
       <c r="D5" t="n">
-        <v>121981255.04</v>
+        <v>14410895.22</v>
       </c>
       <c r="E5" t="n">
-        <v>21965695.26</v>
+        <v>4316323.13</v>
       </c>
       <c r="F5" t="n">
-        <v>17500.14</v>
+        <v>5833.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>755918.46</v>
+        <v>185244.84</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>157499.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>373108.3</v>
+        <v>159996.82</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>62243913.6</v>
+        <v>1238688</v>
       </c>
       <c r="C6" t="n">
-        <v>239700384</v>
+        <v>3143448</v>
       </c>
       <c r="D6" t="n">
-        <v>195467330.71</v>
+        <v>2563372.57</v>
       </c>
       <c r="E6" t="n">
-        <v>27210239.78</v>
+        <v>616503.89</v>
       </c>
       <c r="F6" t="n">
-        <v>16666.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>80058.75</v>
+        <v>1776</v>
       </c>
       <c r="H6" t="n">
-        <v>1920670.29</v>
+        <v>42576.43</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>735907.36</v>
+        <v>42661.3</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>57623870.7</v>
+        <v>220641.3</v>
       </c>
       <c r="C7" t="n">
-        <v>125599320</v>
+        <v>720720</v>
       </c>
       <c r="D7" t="n">
-        <v>115997323.76</v>
+        <v>665621.37</v>
       </c>
       <c r="E7" t="n">
-        <v>9945875.82</v>
+        <v>105807.19</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>172410.75</v>
+        <v>166.5</v>
       </c>
       <c r="H7" t="n">
-        <v>793681.1800000001</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>758611.4399999999</v>
+        <v>6612.84</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>51191910</v>
+        <v>17424</v>
       </c>
       <c r="C8" t="n">
-        <v>93166920</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>99261207.81</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6385922.37</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>436868.25</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
-        <v>112873.2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>516061.51</v>
+        <v>1404.52</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>29158074</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>48731760</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>56645790.86</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2397002.93</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>351925.5</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,13 +15643,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>311998.88</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>3555486</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>6569640</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>8273720.15</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>240433.2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>52170</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>89287.47</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>726858</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2189880</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2848251.94</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>19980</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>43803</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>422136</v>
-      </c>
-      <c r="C12" t="n">
-        <v>554400</v>
-      </c>
-      <c r="D12" t="n">
-        <v>743948.65</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>33912</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>249084</v>
-      </c>
-      <c r="C13" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D13" t="n">
-        <v>190501.41</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6105</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>16108.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>28908</v>
-      </c>
-      <c r="C14" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>195015.66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>8478</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>38808</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3108.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>24948</v>
-      </c>
-      <c r="C16" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D16" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>11088</v>
-      </c>
-      <c r="C17" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D17" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4239</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3564</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5369.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>198</v>
-      </c>
-      <c r="C19" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D19" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>67710</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D20" t="n">
-        <v>160506.72</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D24" t="n">
-        <v>240760.08</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4238.64</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1073016</v>
-      </c>
-      <c r="D4" t="n">
-        <v>843084</v>
-      </c>
-      <c r="E4" t="n">
-        <v>320400</v>
-      </c>
-      <c r="F4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14880</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>37830</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5484.42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>847728</v>
-      </c>
-      <c r="D5" t="n">
-        <v>666072</v>
-      </c>
-      <c r="E5" t="n">
-        <v>185400</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17190</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2490</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>33300</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5134.68</v>
-      </c>
-      <c r="C6" t="n">
-        <v>527688</v>
-      </c>
-      <c r="D6" t="n">
-        <v>414612</v>
-      </c>
-      <c r="E6" t="n">
-        <v>99000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7890</v>
-      </c>
-      <c r="H6" t="n">
-        <v>840</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20820</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4772.34</v>
-      </c>
-      <c r="C7" t="n">
-        <v>273672</v>
-      </c>
-      <c r="D7" t="n">
-        <v>215028</v>
-      </c>
-      <c r="E7" t="n">
-        <v>54000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4560</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14280</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4224.15</v>
-      </c>
-      <c r="C8" t="n">
-        <v>219240</v>
-      </c>
-      <c r="D8" t="n">
-        <v>172260</v>
-      </c>
-      <c r="E8" t="n">
-        <v>31500</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4140</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>13470</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2784.51</v>
-      </c>
-      <c r="C9" t="n">
-        <v>92736</v>
-      </c>
-      <c r="D9" t="n">
-        <v>72864</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3060</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6630</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1999.62</v>
-      </c>
-      <c r="C10" t="n">
-        <v>37296</v>
-      </c>
-      <c r="D10" t="n">
-        <v>29304</v>
-      </c>
-      <c r="E10" t="n">
-        <v>900</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>480</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1062.36</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8064</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6336</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>661.05</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>409.95</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>353.79</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>346.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>792</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>375.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>48.78</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2467.99</v>
-      </c>
-      <c r="C5" t="n">
-        <v>466250.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>220469.83</v>
-      </c>
-      <c r="E5" t="n">
-        <v>20449.62</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>896.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6993</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4107.74</v>
-      </c>
-      <c r="C6" t="n">
-        <v>474919.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>210208.28</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16731</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>394.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>478.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7703.4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4533.72</v>
-      </c>
-      <c r="C7" t="n">
-        <v>273672</v>
-      </c>
-      <c r="D7" t="n">
-        <v>137187.86</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11485.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>684</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8568</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4224.15</v>
-      </c>
-      <c r="C8" t="n">
-        <v>219240</v>
-      </c>
-      <c r="D8" t="n">
-        <v>126783.36</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7726.95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2691</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>9563.700000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2784.51</v>
-      </c>
-      <c r="C9" t="n">
-        <v>92736</v>
-      </c>
-      <c r="D9" t="n">
-        <v>58509.79</v>
-      </c>
-      <c r="E9" t="n">
-        <v>963.72</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2601</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5370.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1999.62</v>
-      </c>
-      <c r="C10" t="n">
-        <v>37296</v>
-      </c>
-      <c r="D10" t="n">
-        <v>25494.48</v>
-      </c>
-      <c r="E10" t="n">
-        <v>261</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>480</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1254.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1062.36</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8064</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5692.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>661.05</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2936.74</v>
-      </c>
-      <c r="E12" t="n">
-        <v>430.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>409.95</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1880.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>353.79</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1539.65</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>346.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>375.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>48.78</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5429575.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>25643772</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22340208.08</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3767637.99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>247989.06</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>65874.06</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>9037036.800000001</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26120556</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21300405.42</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3082519.44</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12500.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7298.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>132460.02</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>72566.03</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>9974190.6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15051960</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13901246.26</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2116143.79</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12654</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>80710.56</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9293130</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12058200</v>
-      </c>
-      <c r="D8" t="n">
-        <v>12846957.87</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1423613.27</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>49783.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>90090.05</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>6125922</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5100480</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5928797.22</v>
-      </c>
-      <c r="E9" t="n">
-        <v>177555.77</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>48118.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>50588.23</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>4399164</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2051280</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2583355.66</v>
-      </c>
-      <c r="E10" t="n">
-        <v>48086.64</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8880</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11821.16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2337192</v>
-      </c>
-      <c r="C11" t="n">
-        <v>443520</v>
-      </c>
-      <c r="D11" t="n">
-        <v>576861.15</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5550</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1454310</v>
-      </c>
-      <c r="C12" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D12" t="n">
-        <v>297579.46</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>901890</v>
-      </c>
-      <c r="C13" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D13" t="n">
-        <v>190501.41</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>778338</v>
-      </c>
-      <c r="C14" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D14" t="n">
-        <v>156012.53</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>762300</v>
-      </c>
-      <c r="C15" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D15" t="n">
-        <v>79129.81</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>826650</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>241560</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>107316</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>198</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>28322.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2831976</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2225124</v>
-      </c>
-      <c r="E4" t="n">
-        <v>892800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G4" t="n">
-        <v>84540</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9930</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>274530</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7971.66</v>
-      </c>
-      <c r="C5" t="n">
-        <v>546840</v>
-      </c>
-      <c r="D5" t="n">
-        <v>429660</v>
-      </c>
-      <c r="E5" t="n">
-        <v>212400</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>19020</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1860</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>80880</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>703.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>63504</v>
-      </c>
-      <c r="D6" t="n">
-        <v>49896</v>
-      </c>
-      <c r="E6" t="n">
-        <v>19800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="H6" t="n">
-        <v>270</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>12240</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>105.57</v>
-      </c>
-      <c r="C7" t="n">
-        <v>13104</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10296</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3587.25</v>
-      </c>
-      <c r="C5" t="n">
-        <v>300762</v>
-      </c>
-      <c r="D5" t="n">
-        <v>142217.46</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23427.72</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>669.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>16984.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>563.04</v>
-      </c>
-      <c r="C6" t="n">
-        <v>57153.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>25297.27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3346.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>96</v>
-      </c>
-      <c r="H6" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4528.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>100.29</v>
-      </c>
-      <c r="C7" t="n">
-        <v>13104</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6568.85</v>
-      </c>
-      <c r="E7" t="n">
-        <v>574.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>149.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>60</v>
+        <v>565.2</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7891943.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>16541910</v>
-      </c>
-      <c r="D5" t="n">
-        <v>14410895.22</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4316323.13</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>185244.84</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>159996.82</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1238688</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3143448</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2563372.57</v>
-      </c>
-      <c r="E6" t="n">
-        <v>616503.89</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1776</v>
-      </c>
-      <c r="H6" t="n">
-        <v>42576.43</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>42661.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>220641.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>720720</v>
-      </c>
-      <c r="D7" t="n">
-        <v>665621.37</v>
-      </c>
-      <c r="E7" t="n">
-        <v>105807.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6612.84</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>17424</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1404.52</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>565.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>68550</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>41</v>
@@ -576,7 +576,7 @@
         <v>49410</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>23</v>
@@ -614,7 +614,7 @@
         <v>52020</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -652,7 +652,7 @@
         <v>30210</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -690,7 +690,7 @@
         <v>8940</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -766,7 +766,7 @@
         <v>4830</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>780</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>3180</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>4470</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
         <v>780</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>2703</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>4470</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2744,7 +2744,7 @@
         <v>780</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>747784.95</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         <v>1236625.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>735993.6</v>
       </c>
       <c r="J10" t="n">
         <v>58333</v>
@@ -3676,7 +3676,7 @@
         <v>215787</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>9030</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>
@@ -9896,7 +9896,7 @@
         <v>7590</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>9</v>
@@ -9934,7 +9934,7 @@
         <v>12180</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -9972,7 +9972,7 @@
         <v>3930</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>17787.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>6.9</v>
@@ -10866,7 +10866,7 @@
         <v>29651.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -10904,7 +10904,7 @@
         <v>22053.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="J7" t="n">
         <v>9.800000000000001</v>
@@ -10942,7 +10942,7 @@
         <v>7599</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
@@ -11018,7 +11018,7 @@
         <v>4830</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -11132,7 +11132,7 @@
         <v>780</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2732.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>2.7</v>
@@ -11798,7 +11798,7 @@
         <v>6942.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -11836,7 +11836,7 @@
         <v>2868.9</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11950,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>755918.46</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>157499.1</v>
@@ -12730,7 +12730,7 @@
         <v>1920670.29</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>268331</v>
       </c>
       <c r="J6" t="n">
         <v>58333</v>
@@ -12768,7 +12768,7 @@
         <v>793681.1800000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -12882,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>9930</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -16420,7 +16420,7 @@
         <v>4920939.54</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>402497.7</v>
@@ -16458,7 +16458,7 @@
         <v>8203059.81</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>268331</v>
       </c>
       <c r="J6" t="n">
         <v>291665</v>
@@ -16496,7 +16496,7 @@
         <v>6101045.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>632494.5</v>
       </c>
       <c r="J7" t="n">
         <v>571663.4</v>
@@ -16534,7 +16534,7 @@
         <v>2102263.35</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>198332.2</v>
@@ -16610,7 +16610,7 @@
         <v>1336219.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1103990.4</v>
       </c>
       <c r="J10" t="n">
         <v>174999</v>
@@ -16724,7 +16724,7 @@
         <v>215787</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>8550</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -17428,7 +17428,7 @@
         <v>19770</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -18360,7 +18360,7 @@
         <v>14432.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -19292,7 +19292,7 @@
         <v>3992640.46</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>408331</v>
@@ -20110,7 +20110,7 @@
         <v>25890</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>976</v>
       </c>
       <c r="L4" t="n">
         <v>1326780</v>
@@ -582,7 +582,7 @@
         <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L5" t="n">
         <v>816990</v>
@@ -620,7 +620,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="L6" t="n">
         <v>618240</v>
@@ -658,7 +658,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
         <v>486120</v>
@@ -696,7 +696,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="L8" t="n">
         <v>390720</v>
@@ -734,7 +734,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="L9" t="n">
         <v>300000</v>
@@ -772,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L10" t="n">
         <v>182580</v>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="L11" t="n">
         <v>163200</v>
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L12" t="n">
         <v>102600</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
         <v>44520</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>17970</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>8160</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2460</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>4350</v>
@@ -1476,7 +1476,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>17220</v>
@@ -1514,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
         <v>25830</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
         <v>28890</v>
@@ -1590,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L7" t="n">
         <v>37200</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L8" t="n">
         <v>47910</v>
@@ -1666,7 +1666,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
         <v>44130</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
         <v>56370</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
         <v>92400</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
         <v>68400</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L13" t="n">
         <v>32490</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>13410</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>6810</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>3690</v>
@@ -2446,7 +2446,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="L5" t="n">
         <v>5424.3</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="L6" t="n">
         <v>10689.3</v>
@@ -2522,7 +2522,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17.22</v>
       </c>
       <c r="L7" t="n">
         <v>22320</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="L8" t="n">
         <v>34016.1</v>
@@ -2598,7 +2598,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
         <v>35745.3</v>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
         <v>50169.3</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
         <v>92400</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
         <v>68400</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L13" t="n">
         <v>32490</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>13410</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>6810</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>3690</v>
@@ -3378,7 +3378,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>170245.32</v>
       </c>
       <c r="L5" t="n">
         <v>51096.91</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>332810.4</v>
       </c>
       <c r="L6" t="n">
         <v>100693.21</v>
@@ -3454,7 +3454,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>367371.48</v>
       </c>
       <c r="L7" t="n">
         <v>210254.4</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>518416.2</v>
       </c>
       <c r="L8" t="n">
         <v>320431.66</v>
@@ -3530,7 +3530,7 @@
         <v>277081.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>384012</v>
       </c>
       <c r="L9" t="n">
         <v>336720.73</v>
@@ -3568,7 +3568,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>704022</v>
       </c>
       <c r="L10" t="n">
         <v>472594.81</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>768024</v>
       </c>
       <c r="L11" t="n">
         <v>870408</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>661354</v>
       </c>
       <c r="L12" t="n">
         <v>644328</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>448014</v>
       </c>
       <c r="L13" t="n">
         <v>306055.8</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L14" t="n">
         <v>126322.2</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L15" t="n">
         <v>64150.2</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>34759.8</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
         <v>120630</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>45180</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>9120</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>1980</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="L5" t="n">
         <v>9487.799999999999</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>3374.4</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1188</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>188165.88</v>
       </c>
       <c r="L5" t="n">
         <v>89375.08</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>31786.85</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>11190.96</v>
@@ -7068,7 +7068,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L4" t="n">
         <v>94530</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>28710</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>7140</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2850</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1020</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>10.08</v>
       </c>
       <c r="L5" t="n">
         <v>6029.1</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>2641.8</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>1710</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
         <v>724.2</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>215046.72</v>
       </c>
       <c r="L5" t="n">
         <v>56794.12</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>110936.8</v>
       </c>
       <c r="L6" t="n">
         <v>24885.76</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>16108.2</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>19200.6</v>
       </c>
       <c r="L8" t="n">
         <v>6821.96</v>
@@ -9864,7 +9864,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L4" t="n">
         <v>196890</v>
@@ -9902,7 +9902,7 @@
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L5" t="n">
         <v>188610</v>
@@ -9940,7 +9940,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="L6" t="n">
         <v>211140</v>
@@ -9978,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="L7" t="n">
         <v>134220</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L8" t="n">
         <v>77160</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
         <v>40890</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>10650</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>4650</v>
@@ -10358,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>450</v>
@@ -10834,7 +10834,7 @@
         <v>6.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>235.2</v>
       </c>
       <c r="L5" t="n">
         <v>171567.9</v>
@@ -10872,7 +10872,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>328.9</v>
       </c>
       <c r="L6" t="n">
         <v>228748.8</v>
@@ -10910,7 +10910,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>304.22</v>
       </c>
       <c r="L7" t="n">
         <v>291672</v>
@@ -10948,7 +10948,7 @@
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>304.2</v>
       </c>
       <c r="L8" t="n">
         <v>277411.2</v>
@@ -10986,7 +10986,7 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="L9" t="n">
         <v>243000</v>
@@ -11024,7 +11024,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L10" t="n">
         <v>162496.2</v>
@@ -11062,7 +11062,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="L11" t="n">
         <v>163200</v>
@@ -11100,7 +11100,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L12" t="n">
         <v>102600</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
         <v>44520</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>17970</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>8160</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2460</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>4350</v>
@@ -11766,7 +11766,7 @@
         <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70.98</v>
       </c>
       <c r="L5" t="n">
         <v>39608.1</v>
@@ -11804,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>143.65</v>
       </c>
       <c r="L6" t="n">
         <v>78121.8</v>
@@ -11842,7 +11842,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>104.14</v>
       </c>
       <c r="L7" t="n">
         <v>80532</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>54783.6</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
         <v>33120.9</v>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>9478.5</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>4650</v>
@@ -12222,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>450</v>
@@ -12698,7 +12698,7 @@
         <v>157499.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1514287.32</v>
       </c>
       <c r="L5" t="n">
         <v>373108.3</v>
@@ -12736,7 +12736,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3064629.1</v>
       </c>
       <c r="L6" t="n">
         <v>735907.36</v>
@@ -12774,7 +12774,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2221722.76</v>
       </c>
       <c r="L7" t="n">
         <v>758611.4399999999</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1708853.4</v>
       </c>
       <c r="L8" t="n">
         <v>516061.51</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>981364</v>
       </c>
       <c r="L9" t="n">
         <v>311998.88</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>106670</v>
       </c>
       <c r="L10" t="n">
         <v>89287.47</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L11" t="n">
         <v>43803</v>
@@ -13154,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>4239</v>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L4" t="n">
         <v>274530</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
         <v>80880</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L5" t="n">
         <v>16984.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>179205.6</v>
       </c>
       <c r="L5" t="n">
         <v>159996.82</v>
@@ -16426,7 +16426,7 @@
         <v>402497.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5017756.8</v>
       </c>
       <c r="L5" t="n">
         <v>1616169.62</v>
@@ -16464,7 +16464,7 @@
         <v>291665</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7016752.6</v>
       </c>
       <c r="L6" t="n">
         <v>2154813.7</v>
@@ -16502,7 +16502,7 @@
         <v>571663.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6490229.48</v>
       </c>
       <c r="L7" t="n">
         <v>2747550.24</v>
@@ -16540,7 +16540,7 @@
         <v>198332.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6489802.8</v>
       </c>
       <c r="L8" t="n">
         <v>2613213.5</v>
@@ -16578,7 +16578,7 @@
         <v>554163.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5696178</v>
       </c>
       <c r="L9" t="n">
         <v>2289060</v>
@@ -16616,7 +16616,7 @@
         <v>174999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3605446</v>
       </c>
       <c r="L10" t="n">
         <v>1530714.2</v>
@@ -16654,7 +16654,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2432076</v>
       </c>
       <c r="L11" t="n">
         <v>1537344</v>
@@ -16692,7 +16692,7 @@
         <v>174999</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1301374</v>
       </c>
       <c r="L12" t="n">
         <v>966492</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>725356</v>
       </c>
       <c r="L13" t="n">
         <v>419378.4</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L14" t="n">
         <v>169277.4</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L15" t="n">
         <v>76867.2</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>23173.2</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L17" t="n">
         <v>40977</v>
@@ -17320,7 +17320,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L4" t="n">
         <v>156390</v>
@@ -17358,7 +17358,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="L5" t="n">
         <v>185340</v>
@@ -17396,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="L6" t="n">
         <v>191430</v>
@@ -17434,7 +17434,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="L7" t="n">
         <v>242940</v>
@@ -17472,7 +17472,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="L8" t="n">
         <v>239490</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L9" t="n">
         <v>205560</v>
@@ -17548,7 +17548,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="L10" t="n">
         <v>112200</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L11" t="n">
         <v>65100</v>
@@ -17624,7 +17624,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L12" t="n">
         <v>30390</v>
@@ -17662,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L13" t="n">
         <v>10170</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1020</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>270</v>
@@ -18290,7 +18290,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>67.62</v>
       </c>
       <c r="L5" t="n">
         <v>38921.4</v>
@@ -18328,7 +18328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>100.75</v>
       </c>
       <c r="L6" t="n">
         <v>70829.10000000001</v>
@@ -18366,7 +18366,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>159.08</v>
       </c>
       <c r="L7" t="n">
         <v>145764</v>
@@ -18404,7 +18404,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>195.3</v>
       </c>
       <c r="L8" t="n">
         <v>170037.9</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L9" t="n">
         <v>166503.6</v>
@@ -18480,7 +18480,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="L10" t="n">
         <v>99858</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L11" t="n">
         <v>65100</v>
@@ -18556,7 +18556,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L12" t="n">
         <v>30390</v>
@@ -18594,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L13" t="n">
         <v>10170</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1020</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>270</v>
@@ -19222,7 +19222,7 @@
         <v>69999.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1442605.08</v>
       </c>
       <c r="L5" t="n">
         <v>366639.59</v>
@@ -19260,7 +19260,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2149400.5</v>
       </c>
       <c r="L6" t="n">
         <v>667210.12</v>
@@ -19298,7 +19298,7 @@
         <v>408331</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3393812.72</v>
       </c>
       <c r="L7" t="n">
         <v>1373096.88</v>
@@ -19336,7 +19336,7 @@
         <v>148749.15</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4166530.2</v>
       </c>
       <c r="L8" t="n">
         <v>1601757.02</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4288134</v>
       </c>
       <c r="L9" t="n">
         <v>1568463.91</v>
@@ -19412,7 +19412,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2794754</v>
       </c>
       <c r="L10" t="n">
         <v>940662.36</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1621384</v>
       </c>
       <c r="L11" t="n">
         <v>613242</v>
@@ -19488,7 +19488,7 @@
         <v>174999</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>618686</v>
       </c>
       <c r="L12" t="n">
         <v>286273.8</v>
@@ -19526,7 +19526,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>277342</v>
       </c>
       <c r="L13" t="n">
         <v>95801.39999999999</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>9608.4</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>2543.4</v>
@@ -20116,7 +20116,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
         <v>404670</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L5" t="n">
         <v>200670</v>
@@ -20192,7 +20192,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L6" t="n">
         <v>106710</v>
@@ -20230,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>38700</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>6540</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>60.48</v>
       </c>
       <c r="L5" t="n">
         <v>42140.7</v>
@@ -21124,7 +21124,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>61.75</v>
       </c>
       <c r="L6" t="n">
         <v>39482.7</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="L7" t="n">
         <v>23220</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>4643.4</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1290280.32</v>
       </c>
       <c r="L5" t="n">
         <v>396965.39</v>
@@ -22056,7 +22056,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1317374.5</v>
       </c>
       <c r="L6" t="n">
         <v>371927.03</v>
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>437347</v>
       </c>
       <c r="L7" t="n">
         <v>218732.4</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>43740.83</v>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>158755.86</v>
+        <v>158599.44</v>
       </c>
       <c r="C4" t="n">
         <v>33216120</v>
@@ -529,10 +534,10 @@
         <v>7991100</v>
       </c>
       <c r="F4" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G4" t="n">
-        <v>498720</v>
+        <v>496350</v>
       </c>
       <c r="H4" t="n">
         <v>68550</v>
@@ -544,10 +549,13 @@
         <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>976</v>
+        <v>963</v>
       </c>
       <c r="L4" t="n">
-        <v>1326780</v>
+        <v>1323960</v>
+      </c>
+      <c r="M4" t="n">
+        <v>65010</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>107344.89</v>
+        <v>107182.35</v>
       </c>
       <c r="C5" t="n">
         <v>18937800</v>
@@ -570,7 +578,7 @@
         <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>327990</v>
+        <v>326520</v>
       </c>
       <c r="H5" t="n">
         <v>49410</v>
@@ -582,10 +590,13 @@
         <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>816990</v>
+        <v>814980</v>
+      </c>
+      <c r="M5" t="n">
+        <v>48570</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>85009.77</v>
+        <v>84866.75999999999</v>
       </c>
       <c r="C6" t="n">
         <v>13876632</v>
@@ -608,7 +619,7 @@
         <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>244170</v>
+        <v>243420</v>
       </c>
       <c r="H6" t="n">
         <v>52020</v>
@@ -620,10 +631,13 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>618240</v>
+        <v>616500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29610</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>69574.59</v>
+        <v>69527.88</v>
       </c>
       <c r="C7" t="n">
         <v>8364888</v>
@@ -646,7 +660,7 @@
         <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>194370</v>
+        <v>193920</v>
       </c>
       <c r="H7" t="n">
         <v>30210</v>
@@ -661,7 +675,10 @@
         <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>486120</v>
+        <v>485130</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19770</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>61426.62</v>
+        <v>61426.08</v>
       </c>
       <c r="C8" t="n">
         <v>6948648</v>
@@ -684,7 +701,7 @@
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>159660</v>
+        <v>159210</v>
       </c>
       <c r="H8" t="n">
         <v>8940</v>
@@ -699,7 +716,10 @@
         <v>338</v>
       </c>
       <c r="L8" t="n">
-        <v>390720</v>
+        <v>390000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>12480</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +742,7 @@
         <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>140010</v>
+        <v>139680</v>
       </c>
       <c r="H9" t="n">
         <v>3780</v>
@@ -737,7 +757,10 @@
         <v>267</v>
       </c>
       <c r="L9" t="n">
-        <v>300000</v>
+        <v>299640</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9900</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +768,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>32277.33</v>
+        <v>32276.97</v>
       </c>
       <c r="C10" t="n">
         <v>2918160</v>
@@ -775,7 +798,10 @@
         <v>169</v>
       </c>
       <c r="L10" t="n">
-        <v>182580</v>
+        <v>182490</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6330</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>114</v>
       </c>
       <c r="L11" t="n">
-        <v>163200</v>
+        <v>162930</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3990</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>61</v>
       </c>
       <c r="L12" t="n">
-        <v>102600</v>
+        <v>102390</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3300</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>44520</v>
       </c>
+      <c r="M13" t="n">
+        <v>1860</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>17970</v>
       </c>
+      <c r="M14" t="n">
+        <v>930</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>8160</v>
       </c>
+      <c r="M15" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>2460</v>
       </c>
+      <c r="M16" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>4350</v>
       </c>
+      <c r="M17" t="n">
+        <v>3450</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>1440</v>
       </c>
+      <c r="M18" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>750</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1479,7 +1556,10 @@
         <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>17220</v>
+        <v>17280</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4680</v>
       </c>
     </row>
     <row r="5">
@@ -1502,7 +1582,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>8580</v>
+        <v>8610</v>
       </c>
       <c r="H5" t="n">
         <v>2310</v>
@@ -1517,7 +1597,10 @@
         <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>25830</v>
+        <v>25770</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11820</v>
       </c>
     </row>
     <row r="6">
@@ -1525,7 +1608,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3187.44</v>
+        <v>3187.35</v>
       </c>
       <c r="C6" t="n">
         <v>543816</v>
@@ -1540,7 +1623,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>9150</v>
+        <v>9180</v>
       </c>
       <c r="H6" t="n">
         <v>2880</v>
@@ -1555,7 +1638,10 @@
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>28890</v>
+        <v>29070</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9240</v>
       </c>
     </row>
     <row r="7">
@@ -1578,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>15540</v>
+        <v>15660</v>
       </c>
       <c r="H7" t="n">
         <v>3780</v>
@@ -1593,7 +1679,10 @@
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>37200</v>
+        <v>37410</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6360</v>
       </c>
     </row>
     <row r="8">
@@ -1616,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>19320</v>
+        <v>19350</v>
       </c>
       <c r="H8" t="n">
         <v>3180</v>
@@ -1631,7 +1720,10 @@
         <v>27</v>
       </c>
       <c r="L8" t="n">
-        <v>47910</v>
+        <v>48030</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3840</v>
       </c>
     </row>
     <row r="9">
@@ -1669,7 +1761,10 @@
         <v>18</v>
       </c>
       <c r="L9" t="n">
-        <v>44130</v>
+        <v>44160</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="10">
@@ -1692,7 +1787,7 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>19470</v>
+        <v>19530</v>
       </c>
       <c r="H10" t="n">
         <v>4470</v>
@@ -1707,7 +1802,10 @@
         <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>56370</v>
+        <v>56550</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1590</v>
       </c>
     </row>
     <row r="11">
@@ -1730,7 +1828,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>32370</v>
+        <v>32340</v>
       </c>
       <c r="H11" t="n">
         <v>4620</v>
@@ -1745,7 +1843,10 @@
         <v>36</v>
       </c>
       <c r="L11" t="n">
-        <v>92400</v>
+        <v>92580</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1080</v>
       </c>
     </row>
     <row r="12">
@@ -1783,7 +1884,10 @@
         <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>68400</v>
+        <v>68460</v>
+      </c>
+      <c r="M12" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="13">
@@ -1806,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>15420</v>
+        <v>15450</v>
       </c>
       <c r="H13" t="n">
         <v>780</v>
@@ -1821,7 +1925,10 @@
         <v>21</v>
       </c>
       <c r="L13" t="n">
-        <v>32490</v>
+        <v>32520</v>
+      </c>
+      <c r="M13" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="14">
@@ -1859,7 +1966,10 @@
         <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>13410</v>
+        <v>13470</v>
+      </c>
+      <c r="M14" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>6810</v>
       </c>
+      <c r="M15" t="n">
+        <v>810</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>1890</v>
       </c>
+      <c r="M16" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>3690</v>
       </c>
+      <c r="M17" t="n">
+        <v>2580</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>750</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>660</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,10 +2598,13 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>7.98</v>
+        <v>6.29</v>
       </c>
       <c r="L5" t="n">
-        <v>5424.3</v>
+        <v>5411.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>236.4</v>
       </c>
     </row>
     <row r="6">
@@ -2457,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2549.95</v>
+        <v>2549.88</v>
       </c>
       <c r="C6" t="n">
         <v>489434.4</v>
@@ -2472,7 +2627,7 @@
         <v>0.6</v>
       </c>
       <c r="G6" t="n">
-        <v>457.5</v>
+        <v>459</v>
       </c>
       <c r="H6" t="n">
         <v>1641.6</v>
@@ -2484,10 +2639,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>15.6</v>
+        <v>12.17</v>
       </c>
       <c r="L6" t="n">
-        <v>10689.3</v>
+        <v>10755.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>739.2</v>
       </c>
     </row>
     <row r="7">
@@ -2510,7 +2668,7 @@
         <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2331</v>
+        <v>2349</v>
       </c>
       <c r="H7" t="n">
         <v>2759.4</v>
@@ -2522,10 +2680,13 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>17.22</v>
+        <v>13.4</v>
       </c>
       <c r="L7" t="n">
-        <v>22320</v>
+        <v>22446</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2226</v>
       </c>
     </row>
     <row r="8">
@@ -2548,22 +2709,25 @@
         <v>6.65</v>
       </c>
       <c r="G8" t="n">
-        <v>12558</v>
+        <v>12577.5</v>
       </c>
       <c r="H8" t="n">
         <v>2703</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24.3</v>
+        <v>19.87</v>
       </c>
       <c r="L8" t="n">
-        <v>34016.1</v>
+        <v>34101.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2304</v>
       </c>
     </row>
     <row r="9">
@@ -2598,10 +2762,13 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>14.45</v>
       </c>
       <c r="L9" t="n">
-        <v>35745.3</v>
+        <v>35769.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="10">
@@ -2624,22 +2791,25 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>19470</v>
+        <v>19530</v>
       </c>
       <c r="H10" t="n">
         <v>4470</v>
       </c>
       <c r="I10" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>28.71</v>
       </c>
       <c r="L10" t="n">
-        <v>50169.3</v>
+        <v>50329.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1590</v>
       </c>
     </row>
     <row r="11">
@@ -2662,7 +2832,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>32370</v>
+        <v>32340</v>
       </c>
       <c r="H11" t="n">
         <v>4620</v>
@@ -2674,10 +2844,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>32.35</v>
       </c>
       <c r="L11" t="n">
-        <v>92400</v>
+        <v>92580</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1080</v>
       </c>
     </row>
     <row r="12">
@@ -2712,10 +2885,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>28.74</v>
       </c>
       <c r="L12" t="n">
-        <v>68400</v>
+        <v>68460</v>
+      </c>
+      <c r="M12" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="13">
@@ -2738,22 +2914,25 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>15420</v>
+        <v>15450</v>
       </c>
       <c r="H13" t="n">
         <v>780</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>19.94</v>
       </c>
       <c r="L13" t="n">
-        <v>32490</v>
+        <v>32520</v>
+      </c>
+      <c r="M13" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="14">
@@ -2788,10 +2967,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>13410</v>
+        <v>13470</v>
+      </c>
+      <c r="M14" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -2826,10 +3008,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L15" t="n">
         <v>6810</v>
+      </c>
+      <c r="M15" t="n">
+        <v>810</v>
       </c>
     </row>
     <row r="16">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>1890</v>
       </c>
+      <c r="M16" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>3690</v>
       </c>
+      <c r="M17" t="n">
+        <v>2580</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>750</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>660</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3354,13 +3578,13 @@
         <v>1515769.2</v>
       </c>
       <c r="C5" t="n">
-        <v>15230754</v>
+        <v>11630757.6</v>
       </c>
       <c r="D5" t="n">
-        <v>13268649.15</v>
+        <v>25141425.41</v>
       </c>
       <c r="E5" t="n">
-        <v>6693958.76</v>
+        <v>12534822.9</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>230062.14</v>
+        <v>4740120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>170245.32</v>
+        <v>305368.68</v>
       </c>
       <c r="L5" t="n">
-        <v>51096.91</v>
+        <v>974106</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70920</v>
       </c>
     </row>
     <row r="6">
@@ -3389,25 +3616,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>5609894.4</v>
+        <v>5609736</v>
       </c>
       <c r="C6" t="n">
-        <v>26918892</v>
+        <v>20556244.8</v>
       </c>
       <c r="D6" t="n">
-        <v>21951420.67</v>
+        <v>41593533.7</v>
       </c>
       <c r="E6" t="n">
-        <v>9667901.880000001</v>
+        <v>18103702.5</v>
       </c>
       <c r="F6" t="n">
         <v>25000.2</v>
       </c>
       <c r="G6" t="n">
-        <v>8463.75</v>
+        <v>24786</v>
       </c>
       <c r="H6" t="n">
-        <v>454148.64</v>
+        <v>9357120</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3416,10 +3643,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>332810.4</v>
+        <v>590829.41</v>
       </c>
       <c r="L6" t="n">
-        <v>100693.21</v>
+        <v>1936062</v>
+      </c>
+      <c r="M6" t="n">
+        <v>221760</v>
       </c>
     </row>
     <row r="7">
@@ -3430,34 +3660,37 @@
         <v>9303802.199999999</v>
       </c>
       <c r="C7" t="n">
-        <v>33485760</v>
+        <v>25570944</v>
       </c>
       <c r="D7" t="n">
-        <v>30925792.78</v>
+        <v>58598166.53</v>
       </c>
       <c r="E7" t="n">
-        <v>15518387.81</v>
+        <v>29059074</v>
       </c>
       <c r="F7" t="n">
         <v>150001.2</v>
       </c>
       <c r="G7" t="n">
-        <v>43123.5</v>
+        <v>126846</v>
       </c>
       <c r="H7" t="n">
-        <v>763388.01</v>
+        <v>15728580</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>367371.48</v>
+        <v>650553.29</v>
       </c>
       <c r="L7" t="n">
-        <v>210254.4</v>
+        <v>4040280</v>
+      </c>
+      <c r="M7" t="n">
+        <v>667800</v>
       </c>
     </row>
     <row r="8">
@@ -3468,34 +3701,37 @@
         <v>9991674</v>
       </c>
       <c r="C8" t="n">
-        <v>41441400</v>
+        <v>31646160</v>
       </c>
       <c r="D8" t="n">
-        <v>44152188.54</v>
+        <v>83659530.23999999</v>
       </c>
       <c r="E8" t="n">
-        <v>18384948.49</v>
+        <v>34426873.8</v>
       </c>
       <c r="F8" t="n">
         <v>277085.55</v>
       </c>
       <c r="G8" t="n">
-        <v>232323</v>
+        <v>679185</v>
       </c>
       <c r="H8" t="n">
-        <v>747784.95</v>
+        <v>15407100</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>518416.2</v>
+        <v>964904.83</v>
       </c>
       <c r="L8" t="n">
-        <v>320431.66</v>
+        <v>6138234</v>
+      </c>
+      <c r="M8" t="n">
+        <v>691200</v>
       </c>
     </row>
     <row r="9">
@@ -3506,34 +3742,37 @@
         <v>9841194</v>
       </c>
       <c r="C9" t="n">
-        <v>34455960</v>
+        <v>26311824</v>
       </c>
       <c r="D9" t="n">
-        <v>40051602.98</v>
+        <v>75889744.13</v>
       </c>
       <c r="E9" t="n">
-        <v>13538627.68</v>
+        <v>25351859.25</v>
       </c>
       <c r="F9" t="n">
         <v>125001</v>
       </c>
       <c r="G9" t="n">
-        <v>294843.75</v>
+        <v>860625</v>
       </c>
       <c r="H9" t="n">
-        <v>888046.5</v>
+        <v>18297000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>277081.75</v>
+        <v>115320.5</v>
       </c>
       <c r="K9" t="n">
-        <v>384012</v>
+        <v>701828.42</v>
       </c>
       <c r="L9" t="n">
-        <v>336720.73</v>
+        <v>6438528</v>
+      </c>
+      <c r="M9" t="n">
+        <v>810000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,34 +3783,37 @@
         <v>9062262</v>
       </c>
       <c r="C10" t="n">
-        <v>34705440</v>
+        <v>26502336</v>
       </c>
       <c r="D10" t="n">
-        <v>43707584.92</v>
+        <v>82817095.68000001</v>
       </c>
       <c r="E10" t="n">
-        <v>11204187.12</v>
+        <v>20980485</v>
       </c>
       <c r="F10" t="n">
         <v>333336</v>
       </c>
       <c r="G10" t="n">
-        <v>360195</v>
+        <v>1054620</v>
       </c>
       <c r="H10" t="n">
-        <v>1236625.5</v>
+        <v>25479000</v>
       </c>
       <c r="I10" t="n">
-        <v>735993.6</v>
+        <v>337949.76</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>704022</v>
+        <v>1394042.76</v>
       </c>
       <c r="L10" t="n">
-        <v>472594.81</v>
+        <v>9059310</v>
+      </c>
+      <c r="M10" t="n">
+        <v>477000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,34 +3824,37 @@
         <v>13248972</v>
       </c>
       <c r="C11" t="n">
-        <v>34067880</v>
+        <v>26015472</v>
       </c>
       <c r="D11" t="n">
-        <v>44310147.21</v>
+        <v>83958830.20999999</v>
       </c>
       <c r="E11" t="n">
-        <v>10940174.88</v>
+        <v>20486106.9</v>
       </c>
       <c r="F11" t="n">
         <v>375003</v>
       </c>
       <c r="G11" t="n">
-        <v>598845</v>
+        <v>1746360</v>
       </c>
       <c r="H11" t="n">
-        <v>1278123</v>
+        <v>26334000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>768024</v>
+        <v>1570592.38</v>
       </c>
       <c r="L11" t="n">
-        <v>870408</v>
+        <v>16664400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>324000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,22 +3865,22 @@
         <v>13233924</v>
       </c>
       <c r="C12" t="n">
-        <v>26417160</v>
+        <v>20173104</v>
       </c>
       <c r="D12" t="n">
-        <v>35449153.04</v>
+        <v>67169025.79000001</v>
       </c>
       <c r="E12" t="n">
-        <v>11571967.01</v>
+        <v>21669174</v>
       </c>
       <c r="F12" t="n">
         <v>333336</v>
       </c>
       <c r="G12" t="n">
-        <v>530025</v>
+        <v>1547100</v>
       </c>
       <c r="H12" t="n">
-        <v>406675.5</v>
+        <v>8379000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3644,10 +3889,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>661354</v>
+        <v>1395353.77</v>
       </c>
       <c r="L12" t="n">
-        <v>644328</v>
+        <v>12322800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="13">
@@ -3658,34 +3906,37 @@
         <v>7415298</v>
       </c>
       <c r="C13" t="n">
-        <v>14830200</v>
+        <v>11324880</v>
       </c>
       <c r="D13" t="n">
-        <v>20383651.22</v>
+        <v>38622925.44</v>
       </c>
       <c r="E13" t="n">
-        <v>5615988.94</v>
+        <v>10516262.4</v>
       </c>
       <c r="F13" t="n">
         <v>83334</v>
       </c>
       <c r="G13" t="n">
-        <v>285270</v>
+        <v>834300</v>
       </c>
       <c r="H13" t="n">
-        <v>215787</v>
+        <v>4446000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>448014</v>
+        <v>968182.36</v>
       </c>
       <c r="L13" t="n">
-        <v>306055.8</v>
+        <v>5853600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>144000</v>
       </c>
     </row>
     <row r="14">
@@ -3696,22 +3947,22 @@
         <v>2989800</v>
       </c>
       <c r="C14" t="n">
-        <v>8399160</v>
+        <v>6413904</v>
       </c>
       <c r="D14" t="n">
-        <v>11817949.29</v>
+        <v>22392640.51</v>
       </c>
       <c r="E14" t="n">
-        <v>3492764.81</v>
+        <v>6540403.05</v>
       </c>
       <c r="F14" t="n">
         <v>41667</v>
       </c>
       <c r="G14" t="n">
-        <v>80475</v>
+        <v>234900</v>
       </c>
       <c r="H14" t="n">
-        <v>91294.5</v>
+        <v>1881000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3720,10 +3971,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>213340</v>
+        <v>471964.32</v>
       </c>
       <c r="L14" t="n">
-        <v>126322.2</v>
+        <v>2424600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="15">
@@ -3734,22 +3988,22 @@
         <v>2232252</v>
       </c>
       <c r="C15" t="n">
-        <v>2855160</v>
+        <v>2180304</v>
       </c>
       <c r="D15" t="n">
-        <v>4075185.37</v>
+        <v>7721657.86</v>
       </c>
       <c r="E15" t="n">
-        <v>791008.65</v>
+        <v>1481209.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>57165</v>
+        <v>166860</v>
       </c>
       <c r="H15" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3758,10 +4012,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>64002</v>
+        <v>143628.65</v>
       </c>
       <c r="L15" t="n">
-        <v>64150.2</v>
+        <v>1225800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>243000</v>
       </c>
     </row>
     <row r="16">
@@ -3772,22 +4029,22 @@
         <v>845064</v>
       </c>
       <c r="C16" t="n">
-        <v>693000</v>
+        <v>529200</v>
       </c>
       <c r="D16" t="n">
-        <v>1003167</v>
+        <v>1900800</v>
       </c>
       <c r="E16" t="n">
-        <v>103353.11</v>
+        <v>193534.65</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>9990</v>
+        <v>29160</v>
       </c>
       <c r="H16" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3799,7 +4056,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>17803.8</v>
+        <v>340200</v>
+      </c>
+      <c r="M16" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="17">
@@ -3810,22 +4070,22 @@
         <v>405108</v>
       </c>
       <c r="C17" t="n">
-        <v>997920</v>
+        <v>762048</v>
       </c>
       <c r="D17" t="n">
-        <v>1444560.48</v>
+        <v>2737152</v>
       </c>
       <c r="E17" t="n">
-        <v>246468.9</v>
+        <v>461527.2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3834,10 +4094,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L17" t="n">
-        <v>34759.8</v>
+        <v>664200</v>
+      </c>
+      <c r="M17" t="n">
+        <v>774000</v>
       </c>
     </row>
     <row r="18">
@@ -3848,10 +4111,10 @@
         <v>143748</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3875,7 +4138,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>7065</v>
+        <v>135000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
@@ -3898,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H19" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3913,7 +4179,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6217.2</v>
+        <v>118800</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>38820</v>
+        <v>38880</v>
       </c>
       <c r="H4" t="n">
         <v>4170</v>
@@ -4275,7 +4568,10 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>120630</v>
+        <v>120510</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4298,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>13800</v>
+        <v>13860</v>
       </c>
       <c r="H5" t="n">
         <v>480</v>
@@ -4313,7 +4609,10 @@
         <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>45180</v>
+        <v>45630</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4336,7 +4635,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1740</v>
+        <v>1770</v>
       </c>
       <c r="H6" t="n">
         <v>150</v>
@@ -4352,6 +4651,9 @@
       </c>
       <c r="L6" t="n">
         <v>9120</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>1980</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>420</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.82</v>
+        <v>6.95</v>
       </c>
       <c r="L5" t="n">
-        <v>9487.799999999999</v>
+        <v>9582.299999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5268,7 +5639,7 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>88.5</v>
       </c>
       <c r="H6" t="n">
         <v>85.5</v>
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>3374.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5318,10 +5692,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
         <v>1188</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>298.2</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>3853664.1</v>
       </c>
       <c r="C5" t="n">
-        <v>16038792</v>
+        <v>12247804.8</v>
       </c>
       <c r="D5" t="n">
-        <v>13972591.5</v>
+        <v>26475254.78</v>
       </c>
       <c r="E5" t="n">
-        <v>2798294.23</v>
+        <v>5239966.95</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>47805.12</v>
+        <v>984960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>188165.88</v>
+        <v>337512.76</v>
       </c>
       <c r="L5" t="n">
-        <v>89375.08</v>
+        <v>1724814</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>563112</v>
       </c>
       <c r="C6" t="n">
-        <v>4765068</v>
+        <v>3638779.2</v>
       </c>
       <c r="D6" t="n">
-        <v>3885747.31</v>
+        <v>7362710.78</v>
       </c>
       <c r="E6" t="n">
-        <v>1485213.91</v>
+        <v>2781148.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1609.5</v>
+        <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>31786.85</v>
+        <v>607392</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>74299.5</v>
       </c>
       <c r="C7" t="n">
-        <v>887040</v>
+        <v>677376</v>
       </c>
       <c r="D7" t="n">
-        <v>819226.3</v>
+        <v>1552269.31</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1165.5</v>
+        <v>3402</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6250,10 +6696,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17493.88</v>
+        <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>11190.96</v>
+        <v>213840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>42966</v>
       </c>
       <c r="C8" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D8" t="n">
-        <v>118132.95</v>
+        <v>223838.21</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2809.04</v>
+        <v>53676</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,19 +6754,19 @@
         <v>21978</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>63660</v>
+        <v>63720</v>
       </c>
       <c r="H4" t="n">
         <v>4470</v>
@@ -7071,7 +7580,10 @@
         <v>120</v>
       </c>
       <c r="L4" t="n">
-        <v>94530</v>
+        <v>94620</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7094,7 +7606,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>14850</v>
+        <v>14880</v>
       </c>
       <c r="H5" t="n">
         <v>3180</v>
@@ -7110,6 +7622,9 @@
       </c>
       <c r="L5" t="n">
         <v>28710</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>7140</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>2850</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>1020</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.08</v>
+        <v>7.94</v>
       </c>
       <c r="L5" t="n">
         <v>6029.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>2641.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>1710</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8152,10 +8745,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>724.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>4225834.8</v>
       </c>
       <c r="C5" t="n">
-        <v>16541910</v>
+        <v>12632004</v>
       </c>
       <c r="D5" t="n">
-        <v>14410895.22</v>
+        <v>27305752.32</v>
       </c>
       <c r="E5" t="n">
-        <v>1975266.52</v>
+        <v>3698800.2</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>316708.92</v>
+        <v>6525360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>215046.72</v>
+        <v>385728.86</v>
       </c>
       <c r="L5" t="n">
-        <v>56794.12</v>
+        <v>1085238</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>1034193.6</v>
       </c>
       <c r="C6" t="n">
-        <v>6536376</v>
+        <v>4991414.4</v>
       </c>
       <c r="D6" t="n">
-        <v>5330187.41</v>
+        <v>10099634.69</v>
       </c>
       <c r="E6" t="n">
-        <v>1176961.97</v>
+        <v>2203929</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4162.5</v>
+        <v>12150</v>
       </c>
       <c r="H6" t="n">
-        <v>151382.88</v>
+        <v>3119040</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>110936.8</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>24885.76</v>
+        <v>475524</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,22 +9684,22 @@
         <v>320710.5</v>
       </c>
       <c r="C7" t="n">
-        <v>3437280</v>
+        <v>2624832</v>
       </c>
       <c r="D7" t="n">
-        <v>3174501.91</v>
+        <v>6015043.58</v>
       </c>
       <c r="E7" t="n">
-        <v>458497.82</v>
+        <v>858563.55</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4162.5</v>
+        <v>12150</v>
       </c>
       <c r="H7" t="n">
-        <v>24234.54</v>
+        <v>499320</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>52481.64</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>16108.2</v>
+        <v>307800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,19 +9725,19 @@
         <v>119394</v>
       </c>
       <c r="C8" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D8" t="n">
-        <v>767864.15</v>
+        <v>1454948.35</v>
       </c>
       <c r="E8" t="n">
-        <v>122023.99</v>
+        <v>228496.95</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>360.75</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -9084,10 +9749,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>19200.6</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>6821.96</v>
+        <v>130356</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>80040</v>
+        <v>80100</v>
       </c>
       <c r="H4" t="n">
-        <v>9030</v>
+        <v>9000</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -9867,7 +10592,10 @@
         <v>225</v>
       </c>
       <c r="L4" t="n">
-        <v>196890</v>
+        <v>197400</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17280</v>
       </c>
     </row>
     <row r="5">
@@ -9890,10 +10618,10 @@
         <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>87150</v>
+        <v>87180</v>
       </c>
       <c r="H5" t="n">
-        <v>7590</v>
+        <v>7620</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -9905,7 +10633,10 @@
         <v>169</v>
       </c>
       <c r="L5" t="n">
-        <v>188610</v>
+        <v>188490</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18360</v>
       </c>
     </row>
     <row r="6">
@@ -9928,7 +10659,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>86550</v>
+        <v>86580</v>
       </c>
       <c r="H6" t="n">
         <v>12180</v>
@@ -9943,7 +10674,10 @@
         <v>221</v>
       </c>
       <c r="L6" t="n">
-        <v>211140</v>
+        <v>211230</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10920</v>
       </c>
     </row>
     <row r="7">
@@ -9966,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>62130</v>
+        <v>62220</v>
       </c>
       <c r="H7" t="n">
         <v>3930</v>
@@ -9981,7 +10715,10 @@
         <v>127</v>
       </c>
       <c r="L7" t="n">
-        <v>134220</v>
+        <v>134310</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6360</v>
       </c>
     </row>
     <row r="8">
@@ -10004,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>36330</v>
+        <v>36360</v>
       </c>
       <c r="H8" t="n">
         <v>480</v>
@@ -10019,7 +10756,10 @@
         <v>89</v>
       </c>
       <c r="L8" t="n">
-        <v>77160</v>
+        <v>77220</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3540</v>
       </c>
     </row>
     <row r="9">
@@ -10042,7 +10782,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>22380</v>
+        <v>22410</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10054,10 +10794,13 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L9" t="n">
         <v>40890</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2070</v>
       </c>
     </row>
     <row r="10">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>10650</v>
       </c>
+      <c r="M10" t="n">
+        <v>1080</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>4650</v>
       </c>
+      <c r="M11" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>3600</v>
       </c>
+      <c r="M12" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>1710</v>
       </c>
+      <c r="M13" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>900</v>
       </c>
+      <c r="M14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>330</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>450</v>
       </c>
+      <c r="M17" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>570</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>90</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>48305.2</v>
+        <v>48232.06</v>
       </c>
       <c r="C5" t="n">
         <v>10415790</v>
@@ -10828,16 +11628,19 @@
         <v>17787.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>6.9</v>
       </c>
       <c r="K5" t="n">
-        <v>235.2</v>
+        <v>182.05</v>
       </c>
       <c r="L5" t="n">
-        <v>171567.9</v>
+        <v>171145.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>971.4</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>68007.82000000001</v>
+        <v>67893.41</v>
       </c>
       <c r="C6" t="n">
         <v>12488968.8</v>
@@ -10860,22 +11663,25 @@
         <v>4.9</v>
       </c>
       <c r="G6" t="n">
-        <v>12208.5</v>
+        <v>12171</v>
       </c>
       <c r="H6" t="n">
         <v>29651.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>328.9</v>
+        <v>256.04</v>
       </c>
       <c r="L6" t="n">
-        <v>228748.8</v>
+        <v>228105</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2368.8</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>66095.86</v>
+        <v>66051.49000000001</v>
       </c>
       <c r="C7" t="n">
         <v>8364888</v>
@@ -10898,22 +11704,25 @@
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>29155.5</v>
+        <v>29088</v>
       </c>
       <c r="H7" t="n">
         <v>22053.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>304.22</v>
+        <v>236.7</v>
       </c>
       <c r="L7" t="n">
-        <v>291672</v>
+        <v>291078</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6919.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>61426.62</v>
+        <v>61426.08</v>
       </c>
       <c r="C8" t="n">
         <v>6948648</v>
@@ -10936,22 +11745,25 @@
         <v>17.1</v>
       </c>
       <c r="G8" t="n">
-        <v>103779</v>
+        <v>103486.5</v>
       </c>
       <c r="H8" t="n">
         <v>7599</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>304.2</v>
+        <v>248.77</v>
       </c>
       <c r="L8" t="n">
-        <v>277411.2</v>
+        <v>276900</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7488</v>
       </c>
     </row>
     <row r="9">
@@ -10974,7 +11786,7 @@
         <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>119008.5</v>
+        <v>118728</v>
       </c>
       <c r="H9" t="n">
         <v>3780</v>
@@ -10986,10 +11798,13 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>267</v>
+        <v>214.4</v>
       </c>
       <c r="L9" t="n">
-        <v>243000</v>
+        <v>242708.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9900</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +11812,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>32277.33</v>
+        <v>32276.97</v>
       </c>
       <c r="C10" t="n">
         <v>2918160</v>
@@ -11018,16 +11833,19 @@
         <v>4830</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>169</v>
+        <v>147.03</v>
       </c>
       <c r="L10" t="n">
-        <v>162496.2</v>
+        <v>162416.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6330</v>
       </c>
     </row>
     <row r="11">
@@ -11062,10 +11880,13 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>114</v>
+        <v>102.43</v>
       </c>
       <c r="L11" t="n">
-        <v>163200</v>
+        <v>162930</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3990</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>61</v>
+        <v>56.55</v>
       </c>
       <c r="L12" t="n">
-        <v>102600</v>
+        <v>102390</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3300</v>
       </c>
     </row>
     <row r="13">
@@ -11132,16 +11956,19 @@
         <v>780</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>32.28</v>
       </c>
       <c r="L13" t="n">
         <v>44520</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1860</v>
       </c>
     </row>
     <row r="14">
@@ -11176,10 +12003,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>17970</v>
+      </c>
+      <c r="M14" t="n">
+        <v>930</v>
       </c>
     </row>
     <row r="15">
@@ -11214,10 +12044,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="L15" t="n">
         <v>8160</v>
+      </c>
+      <c r="M15" t="n">
+        <v>870</v>
       </c>
     </row>
     <row r="16">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>2460</v>
       </c>
+      <c r="M16" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>4350</v>
       </c>
+      <c r="M17" t="n">
+        <v>3450</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>1440</v>
       </c>
+      <c r="M18" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>750</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11757,19 +12629,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2732.4</v>
+        <v>2743.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>70.98</v>
+        <v>55.94</v>
       </c>
       <c r="L5" t="n">
-        <v>39608.1</v>
+        <v>39582.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>367.2</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4327.5</v>
+        <v>4329</v>
       </c>
       <c r="H6" t="n">
         <v>6942.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>143.65</v>
+        <v>112.05</v>
       </c>
       <c r="L6" t="n">
-        <v>78121.8</v>
+        <v>78155.10000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>873.6</v>
       </c>
     </row>
     <row r="7">
@@ -11830,22 +12708,25 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>9319.5</v>
+        <v>9333</v>
       </c>
       <c r="H7" t="n">
         <v>2868.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>104.14</v>
+        <v>81.03</v>
       </c>
       <c r="L7" t="n">
-        <v>80532</v>
+        <v>80586</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2226</v>
       </c>
     </row>
     <row r="8">
@@ -11868,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>23614.5</v>
+        <v>23634</v>
       </c>
       <c r="H8" t="n">
         <v>408</v>
@@ -11880,10 +12761,13 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>80.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="L8" t="n">
-        <v>54783.6</v>
+        <v>54826.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2124</v>
       </c>
     </row>
     <row r="9">
@@ -11906,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>19023</v>
+        <v>19048.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11918,10 +12802,13 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>46</v>
+        <v>37.74</v>
       </c>
       <c r="L9" t="n">
         <v>33120.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2070</v>
       </c>
     </row>
     <row r="10">
@@ -11950,16 +12837,19 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>9478.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1080</v>
       </c>
     </row>
     <row r="11">
@@ -11994,10 +12884,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>4650</v>
+      </c>
+      <c r="M11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>3600</v>
       </c>
+      <c r="M12" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>1710</v>
       </c>
+      <c r="M13" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>900</v>
       </c>
+      <c r="M14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>330</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>450</v>
       </c>
+      <c r="M17" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>570</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>90</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>29487555.9</v>
       </c>
       <c r="C5" t="n">
-        <v>140019264</v>
+        <v>106923801.6</v>
       </c>
       <c r="D5" t="n">
-        <v>121981255.04</v>
+        <v>231129980.93</v>
       </c>
       <c r="E5" t="n">
-        <v>21965695.26</v>
+        <v>41132028.15</v>
       </c>
       <c r="F5" t="n">
         <v>17500.14</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>755918.46</v>
+        <v>15636240</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>157499.1</v>
+        <v>65550.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1514287.32</v>
+        <v>2716174.08</v>
       </c>
       <c r="L5" t="n">
-        <v>373108.3</v>
+        <v>7124922</v>
+      </c>
+      <c r="M5" t="n">
+        <v>110160</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>62243913.6</v>
       </c>
       <c r="C6" t="n">
-        <v>239700384</v>
+        <v>183043929.6</v>
       </c>
       <c r="D6" t="n">
-        <v>195467330.71</v>
+        <v>370371336.19</v>
       </c>
       <c r="E6" t="n">
-        <v>27210239.78</v>
+        <v>50952739.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>80058.75</v>
+        <v>233766</v>
       </c>
       <c r="H6" t="n">
-        <v>1920670.29</v>
+        <v>39572820</v>
       </c>
       <c r="I6" t="n">
-        <v>268331</v>
+        <v>196943.14</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>3064629.1</v>
+        <v>5440554.13</v>
       </c>
       <c r="L6" t="n">
-        <v>735907.36</v>
+        <v>14067918</v>
+      </c>
+      <c r="M6" t="n">
+        <v>262080</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>57623870.7</v>
       </c>
       <c r="C7" t="n">
-        <v>125599320</v>
+        <v>95912208</v>
       </c>
       <c r="D7" t="n">
-        <v>115997323.76</v>
+        <v>219791632.9</v>
       </c>
       <c r="E7" t="n">
-        <v>9945875.82</v>
+        <v>18624224.7</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>172410.75</v>
+        <v>503982</v>
       </c>
       <c r="H7" t="n">
-        <v>793681.1800000001</v>
+        <v>16352730</v>
       </c>
       <c r="I7" t="n">
-        <v>421663</v>
+        <v>247829.82</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2221722.76</v>
+        <v>3934298.46</v>
       </c>
       <c r="L7" t="n">
-        <v>758611.4399999999</v>
+        <v>14505480</v>
+      </c>
+      <c r="M7" t="n">
+        <v>667800</v>
       </c>
     </row>
     <row r="8">
@@ -12788,34 +13741,37 @@
         <v>51191910</v>
       </c>
       <c r="C8" t="n">
-        <v>93166920</v>
+        <v>71145648</v>
       </c>
       <c r="D8" t="n">
-        <v>99261207.81</v>
+        <v>188080054.27</v>
       </c>
       <c r="E8" t="n">
-        <v>6385922.37</v>
+        <v>11958007.05</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>436868.25</v>
+        <v>1276236</v>
       </c>
       <c r="H8" t="n">
-        <v>112873.2</v>
+        <v>2325600</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1708853.4</v>
+        <v>3180612.22</v>
       </c>
       <c r="L8" t="n">
-        <v>516061.51</v>
+        <v>9868716</v>
+      </c>
+      <c r="M8" t="n">
+        <v>637200</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>29158074</v>
       </c>
       <c r="C9" t="n">
-        <v>48731760</v>
+        <v>37213344</v>
       </c>
       <c r="D9" t="n">
-        <v>56645790.86</v>
+        <v>107332397.57</v>
       </c>
       <c r="E9" t="n">
-        <v>2397002.93</v>
+        <v>4488525.9</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>351925.5</v>
+        <v>1028619</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12847,13 +13803,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>981364</v>
+        <v>1832552</v>
       </c>
       <c r="L9" t="n">
-        <v>311998.88</v>
+        <v>5961762</v>
+      </c>
+      <c r="M9" t="n">
+        <v>621000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,34 +13823,37 @@
         <v>3555486</v>
       </c>
       <c r="C10" t="n">
-        <v>6569640</v>
+        <v>5016816</v>
       </c>
       <c r="D10" t="n">
-        <v>8273720.15</v>
+        <v>15677038.08</v>
       </c>
       <c r="E10" t="n">
-        <v>240433.2</v>
+        <v>450225</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>52170</v>
+        <v>152280</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>367996.8</v>
+        <v>168974.88</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>106670</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
-        <v>89287.47</v>
+        <v>1706130</v>
+      </c>
+      <c r="M10" t="n">
+        <v>324000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,22 +13864,22 @@
         <v>726858</v>
       </c>
       <c r="C11" t="n">
-        <v>2189880</v>
+        <v>1672272</v>
       </c>
       <c r="D11" t="n">
-        <v>2848251.94</v>
+        <v>5396865.41</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>19980</v>
+        <v>58320</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12926,10 +13888,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>42668</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>43803</v>
+        <v>837000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,19 +13905,19 @@
         <v>422136</v>
       </c>
       <c r="C12" t="n">
-        <v>554400</v>
+        <v>423360</v>
       </c>
       <c r="D12" t="n">
-        <v>743948.65</v>
+        <v>1409633.28</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>33912</v>
+        <v>648000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>249084</v>
       </c>
       <c r="C13" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D13" t="n">
-        <v>190501.41</v>
+        <v>360961.92</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>6105</v>
+        <v>17820</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16108.2</v>
+        <v>307800</v>
+      </c>
+      <c r="M13" t="n">
+        <v>117000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,19 +13987,19 @@
         <v>28908</v>
       </c>
       <c r="C14" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D14" t="n">
-        <v>195015.66</v>
+        <v>369515.52</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8478</v>
+        <v>162000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>38808</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3108.6</v>
+        <v>59400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>24948</v>
       </c>
       <c r="C16" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D16" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,7 +14096,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="17">
@@ -13130,10 +14110,10 @@
         <v>11088</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13154,10 +14134,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L17" t="n">
-        <v>4239</v>
+        <v>81000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="18">
@@ -13168,10 +14151,10 @@
         <v>3564</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13180,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13195,7 +14178,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5369.4</v>
+        <v>102600</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -13206,10 +14192,10 @@
         <v>198</v>
       </c>
       <c r="C19" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D19" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13218,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>67710</v>
+        <v>197640</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13233,7 +14219,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D20" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>84540</v>
+        <v>84570</v>
       </c>
       <c r="H4" t="n">
         <v>9930</v>
@@ -13595,7 +14608,10 @@
         <v>99</v>
       </c>
       <c r="L4" t="n">
-        <v>274530</v>
+        <v>276960</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>19020</v>
+        <v>19080</v>
       </c>
       <c r="H5" t="n">
         <v>1860</v>
@@ -13633,7 +14649,10 @@
         <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>80880</v>
+        <v>81420</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1920</v>
+        <v>2010</v>
       </c>
       <c r="H6" t="n">
         <v>270</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12240</v>
+        <v>12480</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>1170</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>210</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>60</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>60</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.4</v>
+        <v>6.62</v>
       </c>
       <c r="L5" t="n">
-        <v>16984.8</v>
+        <v>17098.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>96</v>
+        <v>100.5</v>
       </c>
       <c r="H6" t="n">
         <v>153.9</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4528.8</v>
+        <v>4617.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>702</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>149.1</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>48.6</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>60</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>7891943.4</v>
       </c>
       <c r="C5" t="n">
-        <v>16541910</v>
+        <v>12632004</v>
       </c>
       <c r="D5" t="n">
-        <v>14410895.22</v>
+        <v>27305752.32</v>
       </c>
       <c r="E5" t="n">
-        <v>4316323.13</v>
+        <v>8082563.4</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>185244.84</v>
+        <v>3816720</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>179205.6</v>
+        <v>321440.72</v>
       </c>
       <c r="L5" t="n">
-        <v>159996.82</v>
+        <v>3077676</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>1238688</v>
       </c>
       <c r="C6" t="n">
-        <v>3143448</v>
+        <v>2400451.2</v>
       </c>
       <c r="D6" t="n">
-        <v>2563372.57</v>
+        <v>4857076.22</v>
       </c>
       <c r="E6" t="n">
-        <v>616503.89</v>
+        <v>1154439</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1776</v>
+        <v>5427</v>
       </c>
       <c r="H6" t="n">
-        <v>42576.43</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>42661.3</v>
+        <v>831168</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>220641.3</v>
       </c>
       <c r="C7" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D7" t="n">
-        <v>665621.37</v>
+        <v>1261218.82</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>166.5</v>
+        <v>486</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6612.84</v>
+        <v>126360</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1404.52</v>
+        <v>26838</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>457.81</v>
+        <v>8748</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>106271441.1</v>
+        <v>106110526.5</v>
       </c>
       <c r="C5" t="n">
-        <v>572868450</v>
+        <v>437463180</v>
       </c>
       <c r="D5" t="n">
-        <v>499068560.33</v>
+        <v>945634694.4</v>
       </c>
       <c r="E5" t="n">
-        <v>98141482.76000001</v>
+        <v>183775572.9</v>
       </c>
       <c r="F5" t="n">
         <v>67500.53999999999</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4920939.54</v>
+        <v>101389320</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>402497.7</v>
+        <v>167518.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5017756.8</v>
+        <v>8839619.800000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1616169.62</v>
+        <v>30806244</v>
+      </c>
+      <c r="M5" t="n">
+        <v>291420</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>149617195.2</v>
+        <v>149365497.6</v>
       </c>
       <c r="C6" t="n">
-        <v>686893284</v>
+        <v>524536689.6</v>
       </c>
       <c r="D6" t="n">
-        <v>560137595.38</v>
+        <v>1061348251.39</v>
       </c>
       <c r="E6" t="n">
-        <v>110045944.01</v>
+        <v>206067361.5</v>
       </c>
       <c r="F6" t="n">
         <v>204168.3</v>
       </c>
       <c r="G6" t="n">
-        <v>225857.25</v>
+        <v>657234</v>
       </c>
       <c r="H6" t="n">
-        <v>8203059.81</v>
+        <v>169012980</v>
       </c>
       <c r="I6" t="n">
-        <v>268331</v>
+        <v>196943.14</v>
       </c>
       <c r="J6" t="n">
-        <v>291665</v>
+        <v>121390</v>
       </c>
       <c r="K6" t="n">
-        <v>7016752.6</v>
+        <v>12432035.46</v>
       </c>
       <c r="L6" t="n">
-        <v>2154813.7</v>
+        <v>41058900</v>
+      </c>
+      <c r="M6" t="n">
+        <v>710640</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>145410893.1</v>
+        <v>145313269.2</v>
       </c>
       <c r="C7" t="n">
-        <v>460068840</v>
+        <v>351325296</v>
       </c>
       <c r="D7" t="n">
-        <v>424896840.08</v>
+        <v>805094180.35</v>
       </c>
       <c r="E7" t="n">
-        <v>91099990.25</v>
+        <v>170589973.05</v>
       </c>
       <c r="F7" t="n">
         <v>750006</v>
       </c>
       <c r="G7" t="n">
-        <v>539376.75</v>
+        <v>1570752</v>
       </c>
       <c r="H7" t="n">
-        <v>6101045.44</v>
+        <v>125703810</v>
       </c>
       <c r="I7" t="n">
-        <v>632494.5</v>
+        <v>371744.74</v>
       </c>
       <c r="J7" t="n">
-        <v>571663.4</v>
+        <v>237924.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6490229.48</v>
+        <v>11493108.09</v>
       </c>
       <c r="L7" t="n">
-        <v>2747550.24</v>
+        <v>52394040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2075850</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>135138564</v>
+        <v>135137376</v>
       </c>
       <c r="C8" t="n">
-        <v>382175640</v>
+        <v>291843216</v>
       </c>
       <c r="D8" t="n">
-        <v>407174731.35</v>
+        <v>771514343.42</v>
       </c>
       <c r="E8" t="n">
-        <v>85701518.73</v>
+        <v>160481024.55</v>
       </c>
       <c r="F8" t="n">
         <v>712505.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1919911.5</v>
+        <v>5588271</v>
       </c>
       <c r="H8" t="n">
-        <v>2102263.35</v>
+        <v>43314300</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>198332.2</v>
+        <v>82545.2</v>
       </c>
       <c r="K8" t="n">
-        <v>6489802.8</v>
+        <v>12079179.01</v>
       </c>
       <c r="L8" t="n">
-        <v>2613213.5</v>
+        <v>49842000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2246400</v>
       </c>
     </row>
     <row r="9">
@@ -16554,34 +17798,37 @@
         <v>110398068</v>
       </c>
       <c r="C9" t="n">
-        <v>296465400</v>
+        <v>226391760</v>
       </c>
       <c r="D9" t="n">
-        <v>344611338.61</v>
+        <v>652969278.72</v>
       </c>
       <c r="E9" t="n">
-        <v>62810354.63</v>
+        <v>117616002.75</v>
       </c>
       <c r="F9" t="n">
         <v>791673</v>
       </c>
       <c r="G9" t="n">
-        <v>2201657.25</v>
+        <v>6411312</v>
       </c>
       <c r="H9" t="n">
-        <v>1045737</v>
+        <v>21546000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>554163.5</v>
+        <v>230641</v>
       </c>
       <c r="K9" t="n">
-        <v>5696178</v>
+        <v>10410454.96</v>
       </c>
       <c r="L9" t="n">
-        <v>2289060</v>
+        <v>43687512</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2970000</v>
       </c>
     </row>
     <row r="10">
@@ -16589,37 +17836,40 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>71010126</v>
+        <v>71009334</v>
       </c>
       <c r="C10" t="n">
-        <v>160498800</v>
+        <v>122562720</v>
       </c>
       <c r="D10" t="n">
-        <v>202130125.16</v>
+        <v>382995993.6</v>
       </c>
       <c r="E10" t="n">
-        <v>40729384.08</v>
+        <v>76268115</v>
       </c>
       <c r="F10" t="n">
         <v>1291677</v>
       </c>
       <c r="G10" t="n">
-        <v>1494060</v>
+        <v>4361040</v>
       </c>
       <c r="H10" t="n">
-        <v>1336219.5</v>
+        <v>27531000</v>
       </c>
       <c r="I10" t="n">
-        <v>1103990.4</v>
+        <v>506924.64</v>
       </c>
       <c r="J10" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>3605446</v>
+        <v>7139188.68</v>
       </c>
       <c r="L10" t="n">
-        <v>1530714.2</v>
+        <v>29234898</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1899000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,34 +17880,37 @@
         <v>51147360</v>
       </c>
       <c r="C11" t="n">
-        <v>90699840</v>
+        <v>69261696</v>
       </c>
       <c r="D11" t="n">
-        <v>117968105.52</v>
+        <v>223525868.54</v>
       </c>
       <c r="E11" t="n">
-        <v>28403683.86</v>
+        <v>53187532.2</v>
       </c>
       <c r="F11" t="n">
         <v>500004</v>
       </c>
       <c r="G11" t="n">
-        <v>1163835</v>
+        <v>3397140</v>
       </c>
       <c r="H11" t="n">
-        <v>1303021.5</v>
+        <v>26847000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>2432076</v>
+        <v>4973542.52</v>
       </c>
       <c r="L11" t="n">
-        <v>1537344</v>
+        <v>29327400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1197000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,34 +17921,37 @@
         <v>35156880</v>
       </c>
       <c r="C12" t="n">
-        <v>50339520</v>
+        <v>38441088</v>
       </c>
       <c r="D12" t="n">
-        <v>67550537.17</v>
+        <v>127994701.82</v>
       </c>
       <c r="E12" t="n">
-        <v>17040910.32</v>
+        <v>31910085</v>
       </c>
       <c r="F12" t="n">
         <v>458337</v>
       </c>
       <c r="G12" t="n">
-        <v>897435</v>
+        <v>2619540</v>
       </c>
       <c r="H12" t="n">
-        <v>406675.5</v>
+        <v>8379000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>1301374</v>
+        <v>2745696.13</v>
       </c>
       <c r="L12" t="n">
-        <v>966492</v>
+        <v>18430200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>990000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,34 +17962,37 @@
         <v>18146106</v>
       </c>
       <c r="C13" t="n">
-        <v>21427560</v>
+        <v>16362864</v>
       </c>
       <c r="D13" t="n">
-        <v>29451518.5</v>
+        <v>55804712.83</v>
       </c>
       <c r="E13" t="n">
-        <v>6844486.52</v>
+        <v>12816694.8</v>
       </c>
       <c r="F13" t="n">
         <v>125001</v>
       </c>
       <c r="G13" t="n">
-        <v>474525</v>
+        <v>1385100</v>
       </c>
       <c r="H13" t="n">
-        <v>215787</v>
+        <v>4446000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>725356</v>
+        <v>1567533.35</v>
       </c>
       <c r="L13" t="n">
-        <v>419378.4</v>
+        <v>8013600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>558000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,22 +18003,22 @@
         <v>6901092</v>
       </c>
       <c r="C14" t="n">
-        <v>10783080</v>
+        <v>8234352</v>
       </c>
       <c r="D14" t="n">
-        <v>15172218.72</v>
+        <v>28748307.46</v>
       </c>
       <c r="E14" t="n">
-        <v>3775961.95</v>
+        <v>7070706</v>
       </c>
       <c r="F14" t="n">
         <v>166668</v>
       </c>
       <c r="G14" t="n">
-        <v>115440</v>
+        <v>336960</v>
       </c>
       <c r="H14" t="n">
-        <v>91294.5</v>
+        <v>1881000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -16768,10 +18027,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>213340</v>
+        <v>471964.32</v>
       </c>
       <c r="L14" t="n">
-        <v>169277.4</v>
+        <v>3234600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>279000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,22 +18044,22 @@
         <v>4236012</v>
       </c>
       <c r="C15" t="n">
-        <v>3437280</v>
+        <v>2624832</v>
       </c>
       <c r="D15" t="n">
-        <v>4906048.4</v>
+        <v>9295976.449999999</v>
       </c>
       <c r="E15" t="n">
-        <v>889884.73</v>
+        <v>1666360.35</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>71595</v>
+        <v>208980</v>
       </c>
       <c r="H15" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -16806,10 +18068,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>85336</v>
+        <v>191504.86</v>
       </c>
       <c r="L15" t="n">
-        <v>76867.2</v>
+        <v>1468800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>261000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,22 +18085,22 @@
         <v>2177406</v>
       </c>
       <c r="C16" t="n">
-        <v>914760</v>
+        <v>698544</v>
       </c>
       <c r="D16" t="n">
-        <v>1324180.44</v>
+        <v>2509056</v>
       </c>
       <c r="E16" t="n">
-        <v>206706.23</v>
+        <v>387069.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>25530</v>
+        <v>74520</v>
       </c>
       <c r="H16" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -16844,10 +18109,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>23173.2</v>
+        <v>442800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,22 +18126,22 @@
         <v>944658</v>
       </c>
       <c r="C17" t="n">
-        <v>1164240</v>
+        <v>889056</v>
       </c>
       <c r="D17" t="n">
-        <v>1685320.56</v>
+        <v>3193344</v>
       </c>
       <c r="E17" t="n">
-        <v>246468.9</v>
+        <v>461527.2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4995</v>
+        <v>14580</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -16882,10 +18150,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>42668</v>
+        <v>97112</v>
       </c>
       <c r="L17" t="n">
-        <v>40977</v>
+        <v>783000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1035000</v>
       </c>
     </row>
     <row r="18">
@@ -16896,10 +18167,10 @@
         <v>480942</v>
       </c>
       <c r="C18" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D18" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16908,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -16923,7 +18194,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>13564.8</v>
+        <v>259200</v>
+      </c>
+      <c r="M18" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>174636</v>
       </c>
       <c r="C19" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D19" t="n">
-        <v>321013.44</v>
+        <v>608256</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16946,10 +18220,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>69375</v>
+        <v>202500</v>
       </c>
       <c r="H19" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -16961,7 +18235,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>7065</v>
+        <v>135000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -16972,10 +18249,10 @@
         <v>30690</v>
       </c>
       <c r="C20" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D20" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17000,6 +18277,9 @@
       </c>
       <c r="L20" t="n">
         <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="21">
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>9000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17048,10 +18331,10 @@
         <v>14454</v>
       </c>
       <c r="C22" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D22" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17076,6 +18359,9 @@
       </c>
       <c r="L22" t="n">
         <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="23">
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D23" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>277200</v>
+        <v>211680</v>
       </c>
       <c r="D24" t="n">
-        <v>401266.8</v>
+        <v>760320</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>12847.86</v>
+        <v>12756.06</v>
       </c>
       <c r="C4" t="n">
         <v>3082464</v>
@@ -17308,7 +18609,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>54750</v>
+        <v>52500</v>
       </c>
       <c r="H4" t="n">
         <v>8550</v>
@@ -17320,10 +18621,13 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="L4" t="n">
-        <v>156390</v>
+        <v>153660</v>
+      </c>
+      <c r="M4" t="n">
+        <v>33120</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>20564.28</v>
+        <v>20500.74</v>
       </c>
       <c r="C5" t="n">
         <v>3421656</v>
@@ -17346,7 +18650,7 @@
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>67290</v>
+        <v>66330</v>
       </c>
       <c r="H5" t="n">
         <v>11910</v>
@@ -17358,10 +18662,13 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L5" t="n">
-        <v>185340</v>
+        <v>183930</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12780</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>25065.63</v>
+        <v>25045.65</v>
       </c>
       <c r="C6" t="n">
         <v>3777480</v>
@@ -17384,10 +18691,10 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>67350</v>
+        <v>66750</v>
       </c>
       <c r="H6" t="n">
-        <v>14100</v>
+        <v>14130</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17396,10 +18703,13 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L6" t="n">
-        <v>191430</v>
+        <v>190920</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6210</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>25094.52</v>
+        <v>25092.36</v>
       </c>
       <c r="C7" t="n">
         <v>3976056</v>
@@ -17422,7 +18732,7 @@
         <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>86250</v>
+        <v>86010</v>
       </c>
       <c r="H7" t="n">
         <v>19770</v>
@@ -17437,7 +18747,10 @@
         <v>194</v>
       </c>
       <c r="L7" t="n">
-        <v>242940</v>
+        <v>241950</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5040</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27692.1</v>
+        <v>27691.74</v>
       </c>
       <c r="C8" t="n">
         <v>4113648</v>
@@ -17460,7 +18773,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>96690</v>
+        <v>96270</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -17475,7 +18788,10 @@
         <v>217</v>
       </c>
       <c r="L8" t="n">
-        <v>239490</v>
+        <v>238800</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3810</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>94440</v>
+        <v>94110</v>
       </c>
       <c r="H9" t="n">
         <v>480</v>
@@ -17513,7 +18829,10 @@
         <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>205560</v>
+        <v>205260</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4770</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>131</v>
       </c>
       <c r="L10" t="n">
-        <v>112200</v>
+        <v>112140</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>76</v>
       </c>
       <c r="L11" t="n">
-        <v>65100</v>
+        <v>64890</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2460</v>
       </c>
     </row>
     <row r="12">
@@ -17612,7 +18937,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>19500</v>
+        <v>19530</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -17624,10 +18949,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
-        <v>30390</v>
+        <v>30270</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2520</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>10170</v>
       </c>
+      <c r="M13" t="n">
+        <v>990</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>3120</v>
       </c>
+      <c r="M14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>1020</v>
       </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>270</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>210</v>
       </c>
+      <c r="M17" t="n">
+        <v>570</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>120</v>
       </c>
+      <c r="M18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>9253.93</v>
+        <v>9225.33</v>
       </c>
       <c r="C5" t="n">
         <v>1881910.8</v>
@@ -18290,10 +19666,13 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>67.62</v>
+        <v>49.98</v>
       </c>
       <c r="L5" t="n">
-        <v>38921.4</v>
+        <v>38625.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>255.6</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>20052.5</v>
+        <v>20036.52</v>
       </c>
       <c r="C6" t="n">
         <v>3399732</v>
@@ -18316,10 +19695,10 @@
         <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>3367.5</v>
+        <v>3337.5</v>
       </c>
       <c r="H6" t="n">
-        <v>8037</v>
+        <v>8054.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18328,10 +19707,13 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>100.75</v>
+        <v>78.08</v>
       </c>
       <c r="L6" t="n">
-        <v>70829.10000000001</v>
+        <v>70640.39999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>496.8</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>23839.79</v>
+        <v>23837.74</v>
       </c>
       <c r="C7" t="n">
         <v>3976056</v>
@@ -18354,22 +19736,25 @@
         <v>11.4</v>
       </c>
       <c r="G7" t="n">
-        <v>12937.5</v>
+        <v>12901.5</v>
       </c>
       <c r="H7" t="n">
         <v>14432.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>159.08</v>
+        <v>123.77</v>
       </c>
       <c r="L7" t="n">
-        <v>145764</v>
+        <v>145170</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1764</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27692.1</v>
+        <v>27691.74</v>
       </c>
       <c r="C8" t="n">
         <v>4113648</v>
@@ -18392,7 +19777,7 @@
         <v>9.5</v>
       </c>
       <c r="G8" t="n">
-        <v>62848.5</v>
+        <v>62575.5</v>
       </c>
       <c r="H8" t="n">
         <v>4080</v>
@@ -18404,10 +19789,13 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>195.3</v>
+        <v>159.71</v>
       </c>
       <c r="L8" t="n">
-        <v>170037.9</v>
+        <v>169548</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2286</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>80274</v>
+        <v>79993.5</v>
       </c>
       <c r="H9" t="n">
         <v>480</v>
@@ -18442,10 +19830,13 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>201</v>
+        <v>161.4</v>
       </c>
       <c r="L9" t="n">
-        <v>166503.6</v>
+        <v>166260.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4770</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>131</v>
+        <v>113.97</v>
       </c>
       <c r="L10" t="n">
-        <v>99858</v>
+        <v>99804.60000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="11">
@@ -18518,10 +19912,13 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>76</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>65100</v>
+        <v>64890</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2460</v>
       </c>
     </row>
     <row r="12">
@@ -18544,7 +19941,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>19500</v>
+        <v>19530</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -18556,10 +19953,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>27.81</v>
       </c>
       <c r="L12" t="n">
-        <v>30390</v>
+        <v>30270</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2520</v>
       </c>
     </row>
     <row r="13">
@@ -18594,10 +19994,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>12.34</v>
       </c>
       <c r="L13" t="n">
         <v>10170</v>
+      </c>
+      <c r="M13" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="14">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>3120</v>
       </c>
+      <c r="M14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18670,10 +20076,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>1020</v>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>270</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>210</v>
       </c>
+      <c r="M17" t="n">
+        <v>570</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>120</v>
       </c>
+      <c r="M18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>20358637.2</v>
+        <v>20295732.6</v>
       </c>
       <c r="C5" t="n">
-        <v>103505094</v>
+        <v>79040253.59999999</v>
       </c>
       <c r="D5" t="n">
-        <v>90171030.09999999</v>
+        <v>170855993.09</v>
       </c>
       <c r="E5" t="n">
-        <v>38316512.56</v>
+        <v>71749874.25</v>
       </c>
       <c r="F5" t="n">
         <v>11666.76</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1186164.54</v>
+        <v>24439320</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>69999.60000000001</v>
+        <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1442605.08</v>
+        <v>2426877.44</v>
       </c>
       <c r="L5" t="n">
-        <v>366639.59</v>
+        <v>6952554</v>
+      </c>
+      <c r="M5" t="n">
+        <v>76680</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>44115508.8</v>
+        <v>44080344</v>
       </c>
       <c r="C6" t="n">
-        <v>186985260</v>
+        <v>142788744</v>
       </c>
       <c r="D6" t="n">
-        <v>152479979.57</v>
+        <v>288918938.88</v>
       </c>
       <c r="E6" t="n">
-        <v>53775952.78</v>
+        <v>100698565.5</v>
       </c>
       <c r="F6" t="n">
         <v>70833.89999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>62298.75</v>
+        <v>180225</v>
       </c>
       <c r="H6" t="n">
-        <v>2223436.05</v>
+        <v>45908370</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>2149400.5</v>
+        <v>3791155.37</v>
       </c>
       <c r="L6" t="n">
-        <v>667210.12</v>
+        <v>12715272</v>
+      </c>
+      <c r="M6" t="n">
+        <v>149040</v>
       </c>
     </row>
     <row r="7">
@@ -19271,37 +20725,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>52447546.8</v>
+        <v>52443032.4</v>
       </c>
       <c r="C7" t="n">
-        <v>218683080</v>
+        <v>166994352</v>
       </c>
       <c r="D7" t="n">
-        <v>201964883.5</v>
+        <v>382682893.82</v>
       </c>
       <c r="E7" t="n">
-        <v>57805994.58</v>
+        <v>108245050.65</v>
       </c>
       <c r="F7" t="n">
         <v>475003.8</v>
       </c>
       <c r="G7" t="n">
-        <v>239343.75</v>
+        <v>696681</v>
       </c>
       <c r="H7" t="n">
-        <v>3992640.46</v>
+        <v>82262970</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>408331</v>
+        <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>3393812.72</v>
+        <v>6009873.23</v>
       </c>
       <c r="L7" t="n">
-        <v>1373096.88</v>
+        <v>26130600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>529200</v>
       </c>
     </row>
     <row r="8">
@@ -19309,37 +20766,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>60922620</v>
+        <v>60921828</v>
       </c>
       <c r="C8" t="n">
-        <v>226250640</v>
+        <v>172773216</v>
       </c>
       <c r="D8" t="n">
-        <v>241050276.15</v>
+        <v>456741863.42</v>
       </c>
       <c r="E8" t="n">
-        <v>58652866.64</v>
+        <v>109830867.3</v>
       </c>
       <c r="F8" t="n">
         <v>395836.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1162697.25</v>
+        <v>3379077</v>
       </c>
       <c r="H8" t="n">
-        <v>1128732</v>
+        <v>23256000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>148749.15</v>
+        <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4166530.2</v>
+        <v>7754975.87</v>
       </c>
       <c r="L8" t="n">
-        <v>1601757.02</v>
+        <v>30518640</v>
+      </c>
+      <c r="M8" t="n">
+        <v>685800</v>
       </c>
     </row>
     <row r="9">
@@ -19350,34 +20810,37 @@
         <v>63727092</v>
       </c>
       <c r="C9" t="n">
-        <v>206458560</v>
+        <v>157659264</v>
       </c>
       <c r="D9" t="n">
-        <v>239987400.65</v>
+        <v>454727927.81</v>
       </c>
       <c r="E9" t="n">
-        <v>46164500.93</v>
+        <v>86445684</v>
       </c>
       <c r="F9" t="n">
         <v>583338</v>
       </c>
       <c r="G9" t="n">
-        <v>1485069</v>
+        <v>4319649</v>
       </c>
       <c r="H9" t="n">
-        <v>132792</v>
+        <v>2736000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>166249.05</v>
+        <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4288134</v>
+        <v>7837084.07</v>
       </c>
       <c r="L9" t="n">
-        <v>1568463.91</v>
+        <v>29926908</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1431000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,34 +20851,37 @@
         <v>53071128</v>
       </c>
       <c r="C10" t="n">
-        <v>116812080</v>
+        <v>89201952</v>
       </c>
       <c r="D10" t="n">
-        <v>147111631.68</v>
+        <v>278746997.76</v>
       </c>
       <c r="E10" t="n">
-        <v>29236677.12</v>
+        <v>54747360</v>
       </c>
       <c r="F10" t="n">
         <v>958341</v>
       </c>
       <c r="G10" t="n">
-        <v>1065045</v>
+        <v>3108780</v>
       </c>
       <c r="H10" t="n">
-        <v>91294.5</v>
+        <v>1881000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>2794754</v>
+        <v>5533927.32</v>
       </c>
       <c r="L10" t="n">
-        <v>940662.36</v>
+        <v>17964828</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1008000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,34 +20892,37 @@
         <v>34334586</v>
       </c>
       <c r="C11" t="n">
-        <v>53804520</v>
+        <v>41087088</v>
       </c>
       <c r="D11" t="n">
-        <v>69980468.45999999</v>
+        <v>132598933.63</v>
       </c>
       <c r="E11" t="n">
-        <v>17395557.58</v>
+        <v>32574182.4</v>
       </c>
       <c r="F11" t="n">
         <v>125001</v>
       </c>
       <c r="G11" t="n">
-        <v>537240</v>
+        <v>1568160</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>1621384</v>
+        <v>3315695.02</v>
       </c>
       <c r="L11" t="n">
-        <v>613242</v>
+        <v>11680200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>738000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>19701594</v>
       </c>
       <c r="C12" t="n">
-        <v>23063040</v>
+        <v>17611776</v>
       </c>
       <c r="D12" t="n">
-        <v>30948263.72</v>
+        <v>58640744.45</v>
       </c>
       <c r="E12" t="n">
-        <v>5310423.22</v>
+        <v>9944073</v>
       </c>
       <c r="F12" t="n">
         <v>83334</v>
       </c>
       <c r="G12" t="n">
-        <v>360750</v>
+        <v>1054620</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19485,13 +20954,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>618686</v>
+        <v>1350342.36</v>
       </c>
       <c r="L12" t="n">
-        <v>286273.8</v>
+        <v>5448600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>756000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,19 +20974,19 @@
         <v>9212346</v>
       </c>
       <c r="C13" t="n">
-        <v>6320160</v>
+        <v>4826304</v>
       </c>
       <c r="D13" t="n">
-        <v>8686864.449999999</v>
+        <v>16459863.55</v>
       </c>
       <c r="E13" t="n">
-        <v>1228497.58</v>
+        <v>2300432.4</v>
       </c>
       <c r="F13" t="n">
         <v>41667</v>
       </c>
       <c r="G13" t="n">
-        <v>180930</v>
+        <v>528120</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19526,10 +20998,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>277342</v>
+        <v>599350.99</v>
       </c>
       <c r="L13" t="n">
-        <v>95801.39999999999</v>
+        <v>1830600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>297000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,19 +21015,19 @@
         <v>2988810</v>
       </c>
       <c r="C14" t="n">
-        <v>2106720</v>
+        <v>1608768</v>
       </c>
       <c r="D14" t="n">
-        <v>2964238.1</v>
+        <v>5616635.9</v>
       </c>
       <c r="E14" t="n">
-        <v>188798.1</v>
+        <v>353535.3</v>
       </c>
       <c r="F14" t="n">
         <v>83334</v>
       </c>
       <c r="G14" t="n">
-        <v>24975</v>
+        <v>72900</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19567,7 +21042,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>29390.4</v>
+        <v>561600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>162000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,19 +21056,19 @@
         <v>1192356</v>
       </c>
       <c r="C15" t="n">
-        <v>443520</v>
+        <v>338688</v>
       </c>
       <c r="D15" t="n">
-        <v>633038.5</v>
+        <v>1199480.83</v>
       </c>
       <c r="E15" t="n">
-        <v>98876.08</v>
+        <v>185151.15</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>11100</v>
+        <v>32400</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19602,10 +21080,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>9608.4</v>
+        <v>183600</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="16">
@@ -19616,19 +21097,19 @@
         <v>478566</v>
       </c>
       <c r="C16" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D16" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E16" t="n">
-        <v>103353.11</v>
+        <v>193534.65</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>14430</v>
+        <v>42120</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -19640,10 +21121,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>2543.4</v>
+        <v>48600</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="17">
@@ -19654,10 +21138,10 @@
         <v>284130</v>
       </c>
       <c r="C17" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D17" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19681,7 +21165,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1978.2</v>
+        <v>37800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>171000</v>
       </c>
     </row>
     <row r="18">
@@ -19692,10 +21179,10 @@
         <v>223344</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19704,7 +21191,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -19719,7 +21206,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M18" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="19">
@@ -19730,10 +21220,10 @@
         <v>112266</v>
       </c>
       <c r="C19" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D19" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19742,7 +21232,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -19757,6 +21247,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>9000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19844,10 +21343,10 @@
         <v>14454</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19872,6 +21371,9 @@
       </c>
       <c r="L22" t="n">
         <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="23">
@@ -19882,10 +21384,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -19909,6 +21411,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D24" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>141510</v>
+        <v>141600</v>
       </c>
       <c r="H4" t="n">
-        <v>25890</v>
+        <v>25980</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -20116,10 +21633,13 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L4" t="n">
-        <v>404670</v>
+        <v>403170</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,7 +21662,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>83850</v>
+        <v>84030</v>
       </c>
       <c r="H5" t="n">
         <v>18960</v>
@@ -20157,7 +21677,10 @@
         <v>144</v>
       </c>
       <c r="L5" t="n">
-        <v>200670</v>
+        <v>200880</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>51270</v>
+        <v>51450</v>
       </c>
       <c r="H6" t="n">
-        <v>19410</v>
+        <v>19440</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>95</v>
       </c>
       <c r="L6" t="n">
-        <v>106710</v>
+        <v>106740</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20218,10 +21744,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>15780</v>
+        <v>15810</v>
       </c>
       <c r="H7" t="n">
-        <v>2490</v>
+        <v>2520</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -20233,7 +21759,10 @@
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>38700</v>
+        <v>38820</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20271,7 +21800,10 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>6540</v>
+        <v>6510</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20294,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -20310,6 +21842,9 @@
       </c>
       <c r="L9" t="n">
         <v>1290</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>420</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21086,10 +22678,13 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>60.48</v>
+        <v>47.66</v>
       </c>
       <c r="L5" t="n">
-        <v>42140.7</v>
+        <v>42184.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2563.5</v>
+        <v>2572.5</v>
       </c>
       <c r="H6" t="n">
-        <v>11063.7</v>
+        <v>11080.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>61.75</v>
+        <v>48.16</v>
       </c>
       <c r="L6" t="n">
-        <v>39482.7</v>
+        <v>39493.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21150,10 +22748,10 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2367</v>
+        <v>2371.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1817.7</v>
+        <v>1839.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -21162,10 +22760,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20.5</v>
+        <v>15.95</v>
       </c>
       <c r="L7" t="n">
-        <v>23220</v>
+        <v>23292</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21200,10 +22801,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="L8" t="n">
-        <v>4643.4</v>
+        <v>4622.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21226,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>102</v>
+        <v>127.5</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -21242,6 +22846,9 @@
       </c>
       <c r="L9" t="n">
         <v>1044.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>373.8</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>29621740.5</v>
       </c>
       <c r="C5" t="n">
-        <v>91018620</v>
+        <v>69505128</v>
       </c>
       <c r="D5" t="n">
-        <v>79293128.55</v>
+        <v>150244554.24</v>
       </c>
       <c r="E5" t="n">
-        <v>6437905.69</v>
+        <v>12055348.8</v>
       </c>
       <c r="F5" t="n">
         <v>8333.4</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1888302.24</v>
+        <v>38905920</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1290280.32</v>
+        <v>2314373.18</v>
       </c>
       <c r="L5" t="n">
-        <v>396965.39</v>
+        <v>7593264</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,34 +23699,37 @@
         <v>18752659.2</v>
       </c>
       <c r="C6" t="n">
-        <v>70952112</v>
+        <v>54181612.8</v>
       </c>
       <c r="D6" t="n">
-        <v>57858980.91</v>
+        <v>109631149.06</v>
       </c>
       <c r="E6" t="n">
-        <v>4091343.98</v>
+        <v>7661277</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>47424.75</v>
+        <v>138915</v>
       </c>
       <c r="H6" t="n">
-        <v>3060772.6</v>
+        <v>63160560</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>1317374.5</v>
+        <v>2338699.74</v>
       </c>
       <c r="L6" t="n">
-        <v>371927.03</v>
+        <v>7108884</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>9964221.300000001</v>
       </c>
       <c r="C7" t="n">
-        <v>25585560</v>
+        <v>19538064</v>
       </c>
       <c r="D7" t="n">
-        <v>23629558.56</v>
+        <v>44773267.97</v>
       </c>
       <c r="E7" t="n">
-        <v>1516569.72</v>
+        <v>2839864.05</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>43789.5</v>
+        <v>128061</v>
       </c>
       <c r="H7" t="n">
-        <v>502866.7</v>
+        <v>10485720</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22094,10 +23764,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>437347</v>
+        <v>774468.2</v>
       </c>
       <c r="L7" t="n">
-        <v>218732.4</v>
+        <v>4192560</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,22 +23781,22 @@
         <v>584496</v>
       </c>
       <c r="C8" t="n">
-        <v>2577960</v>
+        <v>1968624</v>
       </c>
       <c r="D8" t="n">
-        <v>2746590.99</v>
+        <v>5204238.34</v>
       </c>
       <c r="E8" t="n">
-        <v>203373.32</v>
+        <v>380828.25</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7215</v>
+        <v>21060</v>
       </c>
       <c r="H8" t="n">
-        <v>112873.2</v>
+        <v>2325600</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22132,10 +23805,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>38401.2</v>
+        <v>71474.42999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>43740.83</v>
+        <v>831978</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>95634</v>
       </c>
       <c r="C9" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D9" t="n">
-        <v>451104.14</v>
+        <v>854751.74</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22158,10 +23834,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1887</v>
+        <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9842.959999999999</v>
+        <v>188082</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22184,10 +23863,10 @@
         <v>48510</v>
       </c>
       <c r="C10" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D10" t="n">
-        <v>69820.42</v>
+        <v>132295.68</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22199,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3521.2</v>
+        <v>67284</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22237,7 +23919,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22249,7 +23931,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -22287,7 +23972,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>963</v>
+        <v>385</v>
       </c>
       <c r="L4" t="n">
         <v>1323960</v>
@@ -590,7 +590,7 @@
         <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>221</v>
       </c>
       <c r="L5" t="n">
         <v>814980</v>
@@ -631,7 +631,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>505</v>
+        <v>176</v>
       </c>
       <c r="L6" t="n">
         <v>616500</v>
@@ -672,7 +672,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>371</v>
+        <v>104</v>
       </c>
       <c r="L7" t="n">
         <v>485130</v>
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>338</v>
+        <v>104</v>
       </c>
       <c r="L8" t="n">
         <v>390000</v>
@@ -754,7 +754,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>267</v>
+        <v>66</v>
       </c>
       <c r="L9" t="n">
         <v>299640</v>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
         <v>182490</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
         <v>162930</v>
@@ -877,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>102390</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>44520</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>17970</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>8160</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2460</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>4350</v>
@@ -1553,7 +1553,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>17280</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>25770</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
         <v>29070</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
         <v>37410</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>48030</v>
@@ -1758,7 +1758,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>44160</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>56550</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>92580</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>68460</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>32520</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>13470</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>6810</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3690</v>
@@ -2598,7 +2598,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.29</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>5411.7</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12.17</v>
+        <v>5.58</v>
       </c>
       <c r="L6" t="n">
         <v>10755.9</v>
@@ -2680,7 +2680,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>13.4</v>
+        <v>7.66</v>
       </c>
       <c r="L7" t="n">
         <v>22446</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>19.87</v>
+        <v>7.36</v>
       </c>
       <c r="L8" t="n">
         <v>34101.3</v>
@@ -2762,7 +2762,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>14.45</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>35769.6</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>28.71</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
         <v>50329.5</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>32.35</v>
+        <v>3.59</v>
       </c>
       <c r="L11" t="n">
         <v>92580</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>28.74</v>
+        <v>4.64</v>
       </c>
       <c r="L12" t="n">
         <v>68460</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>19.94</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>32520</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>13470</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>6810</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3690</v>
@@ -3602,7 +3602,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>305368.68</v>
+        <v>144648.32</v>
       </c>
       <c r="L5" t="n">
         <v>974106</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>590829.41</v>
+        <v>270796.81</v>
       </c>
       <c r="L6" t="n">
         <v>1936062</v>
@@ -3684,7 +3684,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>650553.29</v>
+        <v>371744.74</v>
       </c>
       <c r="L7" t="n">
         <v>4040280</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>964904.83</v>
+        <v>357372.16</v>
       </c>
       <c r="L8" t="n">
         <v>6138234</v>
@@ -3766,7 +3766,7 @@
         <v>115320.5</v>
       </c>
       <c r="K9" t="n">
-        <v>701828.42</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
         <v>6438528</v>
@@ -3807,7 +3807,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>1394042.76</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
         <v>9059310</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1570592.38</v>
+        <v>174510.26</v>
       </c>
       <c r="L11" t="n">
         <v>16664400</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1395353.77</v>
+        <v>225057.06</v>
       </c>
       <c r="L12" t="n">
         <v>12322800</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>968182.36</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>5853600</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>471964.32</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2424600</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143628.65</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1225800</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>664200</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
         <v>120510</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>45630</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>9120</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.95</v>
+        <v>3.31</v>
       </c>
       <c r="L5" t="n">
         <v>9582.299999999999</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3374.4</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>337512.76</v>
+        <v>160720.36</v>
       </c>
       <c r="L5" t="n">
         <v>1724814</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>607392</v>
@@ -7577,7 +7577,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
         <v>94620</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>28710</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>7140</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2850</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1020</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7.94</v>
+        <v>1.32</v>
       </c>
       <c r="L5" t="n">
         <v>6029.1</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2641.8</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1710</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>724.2</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>385728.86</v>
+        <v>64288.14</v>
       </c>
       <c r="L5" t="n">
         <v>1085238</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>196943.14</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>475524</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>307800</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>35737.22</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>130356</v>
@@ -10589,7 +10589,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="L4" t="n">
         <v>197400</v>
@@ -10630,7 +10630,7 @@
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="L5" t="n">
         <v>188490</v>
@@ -10671,7 +10671,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="L6" t="n">
         <v>211230</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
         <v>134310</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
         <v>77220</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>40890</v>
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>10650</v>
@@ -11122,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>450</v>
@@ -11634,7 +11634,7 @@
         <v>6.9</v>
       </c>
       <c r="K5" t="n">
-        <v>182.05</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>171145.8</v>
@@ -11675,7 +11675,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>256.04</v>
+        <v>89.23</v>
       </c>
       <c r="L6" t="n">
         <v>228105</v>
@@ -11716,7 +11716,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>236.7</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>291078</v>
@@ -11757,7 +11757,7 @@
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>248.77</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>276900</v>
@@ -11798,7 +11798,7 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>214.4</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
         <v>242708.4</v>
@@ -11839,7 +11839,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>147.03</v>
+        <v>34.8</v>
       </c>
       <c r="L10" t="n">
         <v>162416.1</v>
@@ -11880,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>102.43</v>
+        <v>13.48</v>
       </c>
       <c r="L11" t="n">
         <v>162930</v>
@@ -11921,7 +11921,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>56.55</v>
+        <v>5.56</v>
       </c>
       <c r="L12" t="n">
         <v>102390</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>32.28</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>44520</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>17970</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>8160</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2460</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>4350</v>
@@ -12638,7 +12638,7 @@
         <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>55.94</v>
+        <v>27.47</v>
       </c>
       <c r="L5" t="n">
         <v>39582.9</v>
@@ -12679,7 +12679,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>112.05</v>
+        <v>42.59</v>
       </c>
       <c r="L6" t="n">
         <v>78155.10000000001</v>
@@ -12720,7 +12720,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>81.03</v>
+        <v>25.52</v>
       </c>
       <c r="L7" t="n">
         <v>80586</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>65.5</v>
+        <v>24.29</v>
       </c>
       <c r="L8" t="n">
         <v>54826.2</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>37.74</v>
+        <v>5.62</v>
       </c>
       <c r="L9" t="n">
         <v>33120.9</v>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.35</v>
+        <v>1.74</v>
       </c>
       <c r="L10" t="n">
         <v>9478.5</v>
@@ -13130,7 +13130,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>450</v>
@@ -13642,7 +13642,7 @@
         <v>65550.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2716174.08</v>
+        <v>1333978.99</v>
       </c>
       <c r="L5" t="n">
         <v>7124922</v>
@@ -13683,7 +13683,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>5440554.13</v>
+        <v>2067902.93</v>
       </c>
       <c r="L6" t="n">
         <v>14067918</v>
@@ -13724,7 +13724,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3934298.46</v>
+        <v>1239149.12</v>
       </c>
       <c r="L7" t="n">
         <v>14505480</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3180612.22</v>
+        <v>1179328.13</v>
       </c>
       <c r="L8" t="n">
         <v>9868716</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1832552</v>
+        <v>272933.28</v>
       </c>
       <c r="L9" t="n">
         <v>5961762</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>211218.6</v>
+        <v>84487.44</v>
       </c>
       <c r="L10" t="n">
         <v>1706130</v>
@@ -14134,7 +14134,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>81000</v>
@@ -14605,7 +14605,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>276960</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>81420</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.62</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>17098.2</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321440.72</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>3077676</v>
@@ -17658,7 +17658,7 @@
         <v>167518.2</v>
       </c>
       <c r="K5" t="n">
-        <v>8839619.800000001</v>
+        <v>3551919.96</v>
       </c>
       <c r="L5" t="n">
         <v>30806244</v>
@@ -17699,7 +17699,7 @@
         <v>121390</v>
       </c>
       <c r="K6" t="n">
-        <v>12432035.46</v>
+        <v>4332748.99</v>
       </c>
       <c r="L6" t="n">
         <v>41058900</v>
@@ -17740,7 +17740,7 @@
         <v>237924.4</v>
       </c>
       <c r="K7" t="n">
-        <v>11493108.09</v>
+        <v>3221787.71</v>
       </c>
       <c r="L7" t="n">
         <v>52394040</v>
@@ -17781,7 +17781,7 @@
         <v>82545.2</v>
       </c>
       <c r="K8" t="n">
-        <v>12079179.01</v>
+        <v>3716670.46</v>
       </c>
       <c r="L8" t="n">
         <v>49842000</v>
@@ -17822,7 +17822,7 @@
         <v>230641</v>
       </c>
       <c r="K9" t="n">
-        <v>10410454.96</v>
+        <v>2573370.89</v>
       </c>
       <c r="L9" t="n">
         <v>43687512</v>
@@ -17863,7 +17863,7 @@
         <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>7139188.68</v>
+        <v>1689748.8</v>
       </c>
       <c r="L10" t="n">
         <v>29234898</v>
@@ -17904,7 +17904,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>4973542.52</v>
+        <v>654413.49</v>
       </c>
       <c r="L11" t="n">
         <v>29327400</v>
@@ -17945,7 +17945,7 @@
         <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>2745696.13</v>
+        <v>270068.47</v>
       </c>
       <c r="L12" t="n">
         <v>18430200</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1567533.35</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>8013600</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>471964.32</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>3234600</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>191504.86</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1468800</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>442800</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>783000</v>
@@ -18621,7 +18621,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="L4" t="n">
         <v>153660</v>
@@ -18662,7 +18662,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="L5" t="n">
         <v>183930</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="L6" t="n">
         <v>190920</v>
@@ -18744,7 +18744,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="L7" t="n">
         <v>241950</v>
@@ -18785,7 +18785,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="L8" t="n">
         <v>238800</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="L9" t="n">
         <v>205260</v>
@@ -18867,7 +18867,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="L10" t="n">
         <v>112140</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>64890</v>
@@ -18949,7 +18949,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>30270</v>
@@ -18990,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>10170</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1020</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>270</v>
@@ -19666,7 +19666,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>49.98</v>
+        <v>19.2</v>
       </c>
       <c r="L5" t="n">
         <v>38625.3</v>
@@ -19707,7 +19707,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>78.08</v>
+        <v>31.43</v>
       </c>
       <c r="L6" t="n">
         <v>70640.39999999999</v>
@@ -19748,7 +19748,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>123.77</v>
+        <v>31.26</v>
       </c>
       <c r="L7" t="n">
         <v>145170</v>
@@ -19789,7 +19789,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>159.71</v>
+        <v>44.9</v>
       </c>
       <c r="L8" t="n">
         <v>169548</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>161.4</v>
+        <v>44.16</v>
       </c>
       <c r="L9" t="n">
         <v>166260.6</v>
@@ -19871,7 +19871,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>113.97</v>
+        <v>29.58</v>
       </c>
       <c r="L10" t="n">
         <v>99804.60000000001</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>68.29000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="L11" t="n">
         <v>64890</v>
@@ -19953,7 +19953,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>27.81</v>
+        <v>0.93</v>
       </c>
       <c r="L12" t="n">
         <v>30270</v>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>12.34</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>10170</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1020</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>270</v>
@@ -20670,7 +20670,7 @@
         <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2426877.44</v>
+        <v>932178.09</v>
       </c>
       <c r="L5" t="n">
         <v>6952554</v>
@@ -20711,7 +20711,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>3791155.37</v>
+        <v>1526309.3</v>
       </c>
       <c r="L6" t="n">
         <v>12715272</v>
@@ -20752,7 +20752,7 @@
         <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>6009873.23</v>
+        <v>1517957.67</v>
       </c>
       <c r="L7" t="n">
         <v>26130600</v>
@@ -20793,7 +20793,7 @@
         <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7754975.87</v>
+        <v>2179970.18</v>
       </c>
       <c r="L8" t="n">
         <v>30518640</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>7837084.07</v>
+        <v>2144475.74</v>
       </c>
       <c r="L9" t="n">
         <v>29926908</v>
@@ -20875,7 +20875,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>5533927.32</v>
+        <v>1436286.48</v>
       </c>
       <c r="L10" t="n">
         <v>17964828</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>3315695.02</v>
+        <v>392648.09</v>
       </c>
       <c r="L11" t="n">
         <v>11680200</v>
@@ -20957,7 +20957,7 @@
         <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>1350342.36</v>
+        <v>45011.41</v>
       </c>
       <c r="L12" t="n">
         <v>5448600</v>
@@ -20998,7 +20998,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>599350.99</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1830600</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>183600</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>48600</v>
@@ -21633,7 +21633,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>332</v>
+        <v>87</v>
       </c>
       <c r="L4" t="n">
         <v>403170</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="L5" t="n">
         <v>200880</v>
@@ -21715,7 +21715,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
         <v>106740</v>
@@ -21756,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>38820</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>6510</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>47.66</v>
+        <v>15.23</v>
       </c>
       <c r="L5" t="n">
         <v>42184.8</v>
@@ -22719,7 +22719,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>48.16</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>39493.8</v>
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>15.95</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>23292</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>4622.1</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2314373.18</v>
+        <v>739313.66</v>
       </c>
       <c r="L5" t="n">
         <v>7593264</v>
@@ -23723,7 +23723,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>2338699.74</v>
+        <v>467739.95</v>
       </c>
       <c r="L6" t="n">
         <v>7108884</v>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>774468.2</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
         <v>4192560</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>831978</v>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>496350</v>
       </c>
       <c r="H4" t="n">
-        <v>68550</v>
+        <v>74700</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -572,22 +572,22 @@
         <v>385</v>
       </c>
       <c r="L4" t="n">
-        <v>1323960</v>
+        <v>1427520</v>
       </c>
       <c r="M4" t="n">
-        <v>65010</v>
+        <v>50100</v>
       </c>
       <c r="N4" t="n">
-        <v>77880</v>
+        <v>77910</v>
       </c>
       <c r="O4" t="n">
-        <v>228960</v>
+        <v>237270</v>
       </c>
       <c r="P4" t="n">
-        <v>46470</v>
+        <v>18420</v>
       </c>
       <c r="Q4" t="n">
-        <v>196663.31</v>
+        <v>2038002.8</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>326520</v>
       </c>
       <c r="H5" t="n">
-        <v>49410</v>
+        <v>55080</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -625,22 +625,22 @@
         <v>221</v>
       </c>
       <c r="L5" t="n">
-        <v>814980</v>
+        <v>851190</v>
       </c>
       <c r="M5" t="n">
-        <v>48570</v>
+        <v>32460</v>
       </c>
       <c r="N5" t="n">
-        <v>59100</v>
+        <v>74580</v>
       </c>
       <c r="O5" t="n">
-        <v>166710</v>
+        <v>189120</v>
       </c>
       <c r="P5" t="n">
-        <v>60240</v>
+        <v>38310</v>
       </c>
       <c r="Q5" t="n">
-        <v>132906.11</v>
+        <v>1377293.2</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>243420</v>
       </c>
       <c r="H6" t="n">
-        <v>52020</v>
+        <v>53250</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -678,22 +678,22 @@
         <v>176</v>
       </c>
       <c r="L6" t="n">
-        <v>616500</v>
+        <v>622590</v>
       </c>
       <c r="M6" t="n">
-        <v>29610</v>
+        <v>25830</v>
       </c>
       <c r="N6" t="n">
-        <v>14970</v>
+        <v>24180</v>
       </c>
       <c r="O6" t="n">
-        <v>106920</v>
+        <v>118170</v>
       </c>
       <c r="P6" t="n">
-        <v>60570</v>
+        <v>43920</v>
       </c>
       <c r="Q6" t="n">
-        <v>105234.78</v>
+        <v>1090537.87</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>193920</v>
       </c>
       <c r="H7" t="n">
-        <v>30210</v>
+        <v>31410</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -731,22 +731,22 @@
         <v>104</v>
       </c>
       <c r="L7" t="n">
-        <v>485130</v>
+        <v>488160</v>
       </c>
       <c r="M7" t="n">
-        <v>19770</v>
+        <v>26670</v>
       </c>
       <c r="N7" t="n">
-        <v>3750</v>
+        <v>7410</v>
       </c>
       <c r="O7" t="n">
-        <v>71820</v>
+        <v>79380</v>
       </c>
       <c r="P7" t="n">
-        <v>70230</v>
+        <v>53040</v>
       </c>
       <c r="Q7" t="n">
-        <v>86214.57000000001</v>
+        <v>893433.26</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>159210</v>
       </c>
       <c r="H8" t="n">
-        <v>8940</v>
+        <v>12090</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -784,22 +784,22 @@
         <v>104</v>
       </c>
       <c r="L8" t="n">
-        <v>390000</v>
+        <v>406140</v>
       </c>
       <c r="M8" t="n">
-        <v>12480</v>
+        <v>30330</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="O8" t="n">
-        <v>60720</v>
+        <v>68490</v>
       </c>
       <c r="P8" t="n">
-        <v>69000</v>
+        <v>65790</v>
       </c>
       <c r="Q8" t="n">
-        <v>76168.34</v>
+        <v>789325.13</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>139680</v>
       </c>
       <c r="H9" t="n">
-        <v>3780</v>
+        <v>3840</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>66</v>
       </c>
       <c r="L9" t="n">
-        <v>299640</v>
+        <v>331260</v>
       </c>
       <c r="M9" t="n">
-        <v>9900</v>
+        <v>30000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>37260</v>
+        <v>52110</v>
       </c>
       <c r="P9" t="n">
-        <v>73500</v>
+        <v>70800</v>
       </c>
       <c r="Q9" t="n">
-        <v>62224.37</v>
+        <v>644825.08</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>80760</v>
       </c>
       <c r="H10" t="n">
-        <v>4830</v>
+        <v>4530</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
@@ -890,22 +890,22 @@
         <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>182490</v>
+        <v>215580</v>
       </c>
       <c r="M10" t="n">
-        <v>6330</v>
+        <v>25380</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>12600</v>
+        <v>23610</v>
       </c>
       <c r="P10" t="n">
-        <v>80850</v>
+        <v>93480</v>
       </c>
       <c r="Q10" t="n">
-        <v>40023.44</v>
+        <v>414759.06</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>62910</v>
       </c>
       <c r="H11" t="n">
-        <v>4710</v>
+        <v>5670</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>162930</v>
+        <v>208800</v>
       </c>
       <c r="M11" t="n">
-        <v>3990</v>
+        <v>24660</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5160</v>
+        <v>15150</v>
       </c>
       <c r="P11" t="n">
-        <v>64800</v>
+        <v>100590</v>
       </c>
       <c r="Q11" t="n">
-        <v>28828.51</v>
+        <v>298747.08</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>48510</v>
       </c>
       <c r="H12" t="n">
-        <v>1470</v>
+        <v>1980</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>102390</v>
+        <v>145380</v>
       </c>
       <c r="M12" t="n">
-        <v>3300</v>
+        <v>16200</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2550</v>
+        <v>3960</v>
       </c>
       <c r="P12" t="n">
-        <v>47580</v>
+        <v>82050</v>
       </c>
       <c r="Q12" t="n">
-        <v>19815.7</v>
+        <v>205348.14</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>25650</v>
       </c>
       <c r="H13" t="n">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1049,22 +1049,22 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>44520</v>
+        <v>65520</v>
       </c>
       <c r="M13" t="n">
-        <v>1860</v>
+        <v>20310</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3510</v>
+        <v>3300</v>
       </c>
       <c r="P13" t="n">
-        <v>31770</v>
+        <v>47880</v>
       </c>
       <c r="Q13" t="n">
-        <v>10227.81</v>
+        <v>105989.76</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>6240</v>
       </c>
       <c r="H14" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1102,22 +1102,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>17970</v>
+        <v>32010</v>
       </c>
       <c r="M14" t="n">
-        <v>930</v>
+        <v>7230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>840</v>
+        <v>1440</v>
       </c>
       <c r="P14" t="n">
-        <v>27810</v>
+        <v>29970</v>
       </c>
       <c r="Q14" t="n">
-        <v>3889.71</v>
+        <v>40308.65</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>3870</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8160</v>
+        <v>24930</v>
       </c>
       <c r="M15" t="n">
-        <v>870</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P15" t="n">
-        <v>38040</v>
+        <v>51060</v>
       </c>
       <c r="Q15" t="n">
-        <v>2387.57</v>
+        <v>24742.16</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>1380</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2460</v>
+        <v>10200</v>
       </c>
       <c r="M16" t="n">
-        <v>180</v>
+        <v>1710</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P16" t="n">
-        <v>24810</v>
+        <v>41970</v>
       </c>
       <c r="Q16" t="n">
-        <v>1227.27</v>
+        <v>12718.03</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>270</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4350</v>
+        <v>9090</v>
       </c>
       <c r="M17" t="n">
-        <v>3450</v>
+        <v>4410</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>19080</v>
+        <v>27030</v>
       </c>
       <c r="Q17" t="n">
-        <v>532.4400000000001</v>
+        <v>5517.66</v>
       </c>
     </row>
     <row r="18">
@@ -1314,22 +1314,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1440</v>
+        <v>4770</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>1380</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18330</v>
+        <v>24030</v>
       </c>
       <c r="Q18" t="n">
-        <v>271.08</v>
+        <v>2809.14</v>
       </c>
     </row>
     <row r="19">
@@ -1355,7 +1355,7 @@
         <v>3750</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1367,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>750</v>
+        <v>3090</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>7530</v>
+        <v>19080</v>
       </c>
       <c r="Q19" t="n">
-        <v>98.43000000000001</v>
+        <v>1020.03</v>
       </c>
     </row>
     <row r="20">
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.3</v>
+        <v>179.26</v>
       </c>
     </row>
     <row r="21">
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.01</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="22">
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="23">
@@ -1852,7 +1852,7 @@
         <v>7680</v>
       </c>
       <c r="H4" t="n">
-        <v>2670</v>
+        <v>3150</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>17280</v>
+        <v>15810</v>
       </c>
       <c r="M4" t="n">
-        <v>4680</v>
+        <v>2370</v>
       </c>
       <c r="N4" t="n">
-        <v>1050</v>
+        <v>570</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>206.71</v>
+        <v>23427.36</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>8610</v>
       </c>
       <c r="H5" t="n">
-        <v>2310</v>
+        <v>3240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>25770</v>
+        <v>20040</v>
       </c>
       <c r="M5" t="n">
-        <v>11820</v>
+        <v>6210</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>660</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>459.32</v>
+        <v>52056.72</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>9180</v>
       </c>
       <c r="H6" t="n">
-        <v>2880</v>
+        <v>2490</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>29070</v>
+        <v>22590</v>
       </c>
       <c r="M6" t="n">
-        <v>9240</v>
+        <v>5310</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>870</v>
+        <v>750</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>956.2</v>
+        <v>108369.9</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>15660</v>
       </c>
       <c r="H7" t="n">
-        <v>3780</v>
+        <v>2700</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>37410</v>
+        <v>32670</v>
       </c>
       <c r="M7" t="n">
-        <v>6360</v>
+        <v>2670</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1335.47</v>
+        <v>151353.72</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>19350</v>
       </c>
       <c r="H8" t="n">
-        <v>3180</v>
+        <v>4980</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -2076,22 +2076,22 @@
         <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>48030</v>
+        <v>45360</v>
       </c>
       <c r="M8" t="n">
-        <v>3840</v>
+        <v>2760</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1362.5</v>
+        <v>154416.78</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>18750</v>
       </c>
       <c r="H9" t="n">
-        <v>3210</v>
+        <v>3000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>44160</v>
+        <v>46110</v>
       </c>
       <c r="M9" t="n">
-        <v>2700</v>
+        <v>1350</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1341.98</v>
+        <v>152091.18</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>19530</v>
       </c>
       <c r="H10" t="n">
-        <v>4470</v>
+        <v>3900</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -2182,22 +2182,22 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>56550</v>
+        <v>53100</v>
       </c>
       <c r="M10" t="n">
-        <v>1590</v>
+        <v>2970</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1235.76</v>
+        <v>140053.14</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>32340</v>
       </c>
       <c r="H11" t="n">
-        <v>4620</v>
+        <v>5250</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2235,22 +2235,22 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>92580</v>
+        <v>94470</v>
       </c>
       <c r="M11" t="n">
-        <v>1080</v>
+        <v>3780</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1806.68</v>
+        <v>204756.84</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>28650</v>
       </c>
       <c r="H12" t="n">
-        <v>1470</v>
+        <v>1830</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>68460</v>
+        <v>78210</v>
       </c>
       <c r="M12" t="n">
-        <v>360</v>
+        <v>3240</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1804.63</v>
+        <v>204524.28</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>15450</v>
       </c>
       <c r="H13" t="n">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2341,10 +2341,10 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>32520</v>
+        <v>38670</v>
       </c>
       <c r="M13" t="n">
-        <v>480</v>
+        <v>3570</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1011.18</v>
+        <v>114600.06</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>4350</v>
       </c>
       <c r="H14" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>13470</v>
+        <v>18630</v>
       </c>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>3330</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>407.7</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>3090</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6810</v>
+        <v>12900</v>
       </c>
       <c r="M15" t="n">
-        <v>810</v>
+        <v>2370</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>304.4</v>
+        <v>34498.44</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>540</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1890</v>
+        <v>4260</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>115.24</v>
+        <v>13060.08</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3690</v>
+        <v>5070</v>
       </c>
       <c r="M17" t="n">
-        <v>2580</v>
+        <v>3390</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>55.24</v>
+        <v>6260.76</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>750</v>
+        <v>1950</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>1320</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>19.6</v>
+        <v>2221.56</v>
       </c>
     </row>
     <row r="19">
@@ -2647,7 +2647,7 @@
         <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>2550</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.4</v>
+        <v>951.66</v>
       </c>
     </row>
     <row r="20">
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.59</v>
+        <v>180.54</v>
       </c>
     </row>
     <row r="21">
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.38</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="22">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>831.6</v>
+        <v>1166.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>2.98</v>
       </c>
       <c r="L5" t="n">
-        <v>5411.7</v>
+        <v>4208.4</v>
       </c>
       <c r="M5" t="n">
-        <v>236.4</v>
+        <v>124.2</v>
       </c>
       <c r="N5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.5</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.97</v>
+        <v>2602.84</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>459</v>
       </c>
       <c r="H6" t="n">
-        <v>1641.6</v>
+        <v>1419.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>5.58</v>
       </c>
       <c r="L6" t="n">
-        <v>10755.9</v>
+        <v>8358.299999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>739.2</v>
+        <v>424.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>217.5</v>
+        <v>187.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>717.15</v>
+        <v>81277.42</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>2349</v>
       </c>
       <c r="H7" t="n">
-        <v>2759.4</v>
+        <v>1971</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         <v>7.66</v>
       </c>
       <c r="L7" t="n">
-        <v>22446</v>
+        <v>19602</v>
       </c>
       <c r="M7" t="n">
-        <v>2226</v>
+        <v>934.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1068.38</v>
+        <v>121082.98</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>12577.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2703</v>
+        <v>4233</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -3368,22 +3368,22 @@
         <v>7.36</v>
       </c>
       <c r="L8" t="n">
-        <v>34101.3</v>
+        <v>32205.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2112</v>
+        <v>1518</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1294.38</v>
+        <v>146695.94</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>15937.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3210</v>
+        <v>3000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>2.41</v>
       </c>
       <c r="L9" t="n">
-        <v>35769.6</v>
+        <v>37349.1</v>
       </c>
       <c r="M9" t="n">
-        <v>1890</v>
+        <v>945</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1301.72</v>
+        <v>147528.44</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>19530</v>
       </c>
       <c r="H10" t="n">
-        <v>4470</v>
+        <v>3900</v>
       </c>
       <c r="I10" t="n">
         <v>1.74</v>
@@ -3474,22 +3474,22 @@
         <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>50329.5</v>
+        <v>47259</v>
       </c>
       <c r="M10" t="n">
-        <v>1351.5</v>
+        <v>2524.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1235.76</v>
+        <v>140053.14</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>32340</v>
       </c>
       <c r="H11" t="n">
-        <v>4620</v>
+        <v>5250</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>3.59</v>
       </c>
       <c r="L11" t="n">
-        <v>92580</v>
+        <v>94470</v>
       </c>
       <c r="M11" t="n">
-        <v>972</v>
+        <v>3402</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>127.5</v>
+        <v>204</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1806.68</v>
+        <v>204756.84</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>28650</v>
       </c>
       <c r="H12" t="n">
-        <v>1470</v>
+        <v>1830</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
         <v>4.64</v>
       </c>
       <c r="L12" t="n">
-        <v>68460</v>
+        <v>78210</v>
       </c>
       <c r="M12" t="n">
-        <v>342</v>
+        <v>3078</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1804.63</v>
+        <v>204524.28</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>15450</v>
       </c>
       <c r="H13" t="n">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -3633,10 +3633,10 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>32520</v>
+        <v>38670</v>
       </c>
       <c r="M13" t="n">
-        <v>480</v>
+        <v>3570</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1011.18</v>
+        <v>114600.06</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>4350</v>
       </c>
       <c r="H14" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>13470</v>
+        <v>18630</v>
       </c>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>3330</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>407.7</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>3090</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6810</v>
+        <v>12900</v>
       </c>
       <c r="M15" t="n">
-        <v>810</v>
+        <v>2370</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>304.4</v>
+        <v>34498.44</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>540</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1890</v>
+        <v>4260</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>115.24</v>
+        <v>13060.08</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3690</v>
+        <v>5070</v>
       </c>
       <c r="M17" t="n">
-        <v>2580</v>
+        <v>3390</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>55.24</v>
+        <v>6260.76</v>
       </c>
     </row>
     <row r="18">
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>750</v>
+        <v>1950</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>1320</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>19.6</v>
+        <v>2221.56</v>
       </c>
     </row>
     <row r="19">
@@ -3939,7 +3939,7 @@
         <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>2550</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.4</v>
+        <v>951.66</v>
       </c>
     </row>
     <row r="20">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.59</v>
+        <v>180.54</v>
       </c>
     </row>
     <row r="21">
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.38</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="22">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4740120</v>
+        <v>6648480</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>144648.32</v>
       </c>
       <c r="L5" t="n">
-        <v>974106</v>
+        <v>757512</v>
       </c>
       <c r="M5" t="n">
-        <v>82740</v>
+        <v>43470</v>
       </c>
       <c r="N5" t="n">
+        <v>1122</v>
+      </c>
+      <c r="O5" t="n">
         <v>255</v>
       </c>
-      <c r="O5" t="n">
-        <v>510</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>13779.72</v>
+        <v>1561701.6</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>24786</v>
       </c>
       <c r="H6" t="n">
-        <v>9357120</v>
+        <v>8090010</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>270796.81</v>
       </c>
       <c r="L6" t="n">
-        <v>1936062</v>
+        <v>1504494</v>
       </c>
       <c r="M6" t="n">
-        <v>258720</v>
+        <v>148680</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>36975</v>
+        <v>31875</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>430292.25</v>
+        <v>48766455</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>126846</v>
       </c>
       <c r="H7" t="n">
-        <v>15728580</v>
+        <v>11234700</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>371744.74</v>
       </c>
       <c r="L7" t="n">
-        <v>4040280</v>
+        <v>3528360</v>
       </c>
       <c r="M7" t="n">
-        <v>779100</v>
+        <v>327075</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>641027.52</v>
+        <v>72649785.59999999</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>679185</v>
       </c>
       <c r="H8" t="n">
-        <v>15407100</v>
+        <v>24128100</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -4660,22 +4660,22 @@
         <v>357372.16</v>
       </c>
       <c r="L8" t="n">
-        <v>6138234</v>
+        <v>5797008</v>
       </c>
       <c r="M8" t="n">
-        <v>739200</v>
+        <v>531300</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>13770</v>
+        <v>22950</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>776625.5699999999</v>
+        <v>88017564.59999999</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>860625</v>
       </c>
       <c r="H9" t="n">
-        <v>18297000</v>
+        <v>17100000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>6438528</v>
+        <v>6722838</v>
       </c>
       <c r="M9" t="n">
-        <v>661500</v>
+        <v>330750</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>11220</v>
+        <v>16830</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>781032.9399999999</v>
+        <v>88517066.76000001</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1054620</v>
       </c>
       <c r="H10" t="n">
-        <v>25479000</v>
+        <v>22230000</v>
       </c>
       <c r="I10" t="n">
         <v>337949.76</v>
@@ -4766,22 +4766,22 @@
         <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>9059310</v>
+        <v>8506620</v>
       </c>
       <c r="M10" t="n">
-        <v>473025</v>
+        <v>883575</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17850</v>
+        <v>7140</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>741457.8</v>
+        <v>84031884</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>1746360</v>
       </c>
       <c r="H11" t="n">
-        <v>26334000</v>
+        <v>29925000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4819,22 +4819,22 @@
         <v>174510.26</v>
       </c>
       <c r="L11" t="n">
-        <v>16664400</v>
+        <v>17004600</v>
       </c>
       <c r="M11" t="n">
-        <v>340200</v>
+        <v>1190700</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>21675</v>
+        <v>34680</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1084006.8</v>
+        <v>122854104</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1547100</v>
       </c>
       <c r="H12" t="n">
-        <v>8379000</v>
+        <v>10431000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>225057.06</v>
       </c>
       <c r="L12" t="n">
-        <v>12322800</v>
+        <v>14077800</v>
       </c>
       <c r="M12" t="n">
-        <v>119700</v>
+        <v>1077300</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1082775.6</v>
+        <v>122714568</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>834300</v>
       </c>
       <c r="H13" t="n">
-        <v>4446000</v>
+        <v>4617000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -4925,10 +4925,10 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>5853600</v>
+        <v>6960600</v>
       </c>
       <c r="M13" t="n">
-        <v>168000</v>
+        <v>1249500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>606706.2</v>
+        <v>68760036</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>234900</v>
       </c>
       <c r="H14" t="n">
-        <v>1881000</v>
+        <v>2907000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2424600</v>
+        <v>3353400</v>
       </c>
       <c r="M14" t="n">
-        <v>73500</v>
+        <v>1165500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>244620</v>
+        <v>27723600</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>166860</v>
       </c>
       <c r="H15" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1225800</v>
+        <v>2322000</v>
       </c>
       <c r="M15" t="n">
-        <v>283500</v>
+        <v>829500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>182638.8</v>
+        <v>20699064</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>29160</v>
       </c>
       <c r="H16" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>340200</v>
+        <v>766800</v>
       </c>
       <c r="M16" t="n">
-        <v>31500</v>
+        <v>262500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>69141.60000000001</v>
+        <v>7836048</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>6480</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>664200</v>
+        <v>912600</v>
       </c>
       <c r="M17" t="n">
-        <v>903000</v>
+        <v>1186500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33145.2</v>
+        <v>3756456</v>
       </c>
     </row>
     <row r="18">
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>135000</v>
+        <v>351000</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>462000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>11761.2</v>
+        <v>1332936</v>
       </c>
     </row>
     <row r="19">
@@ -5231,7 +5231,7 @@
         <v>3240</v>
       </c>
       <c r="H19" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>118800</v>
+        <v>459000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>504000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5038.2</v>
+        <v>570996</v>
       </c>
     </row>
     <row r="20">
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>955.8</v>
+        <v>108324</v>
       </c>
     </row>
     <row r="21">
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>226.8</v>
+        <v>25704</v>
       </c>
     </row>
     <row r="22">
@@ -5728,7 +5728,7 @@
         <v>38880</v>
       </c>
       <c r="H4" t="n">
-        <v>4170</v>
+        <v>6360</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>120510</v>
+        <v>140640</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9060</v>
+        <v>7710</v>
       </c>
       <c r="O4" t="n">
-        <v>18990</v>
+        <v>20730</v>
       </c>
       <c r="P4" t="n">
-        <v>10980</v>
+        <v>8640</v>
       </c>
       <c r="Q4" t="n">
-        <v>21502.29</v>
+        <v>113169.96</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>13860</v>
       </c>
       <c r="H5" t="n">
-        <v>480</v>
+        <v>1200</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>45630</v>
+        <v>59670</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8190</v>
+        <v>10380</v>
       </c>
       <c r="O5" t="n">
-        <v>6000</v>
+        <v>9900</v>
       </c>
       <c r="P5" t="n">
-        <v>8550</v>
+        <v>12240</v>
       </c>
       <c r="Q5" t="n">
-        <v>8875.110000000001</v>
+        <v>46711.08</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1770</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9120</v>
+        <v>14040</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="O6" t="n">
-        <v>360</v>
+        <v>1170</v>
       </c>
       <c r="P6" t="n">
-        <v>6000</v>
+        <v>8730</v>
       </c>
       <c r="Q6" t="n">
-        <v>729.49</v>
+        <v>3839.4</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>420</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1980</v>
+        <v>3720</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5580</v>
+        <v>8280</v>
       </c>
       <c r="Q7" t="n">
-        <v>81.05</v>
+        <v>426.6</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>420</v>
+        <v>1920</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>10260</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.53</v>
+        <v>234.36</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4170</v>
+        <v>10380</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.78</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1350</v>
+        <v>3930</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.210000000000001</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>172.8</v>
+        <v>432</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>3.31</v>
       </c>
       <c r="L5" t="n">
-        <v>9582.299999999999</v>
+        <v>12530.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>81.90000000000001</v>
+        <v>103.8</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>495</v>
       </c>
       <c r="P5" t="n">
-        <v>171</v>
+        <v>244.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>443.76</v>
+        <v>2335.55</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>88.5</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3374.4</v>
+        <v>5194.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>292.5</v>
       </c>
       <c r="P6" t="n">
-        <v>900</v>
+        <v>1309.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>547.11</v>
+        <v>2879.55</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>63</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>109.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1188</v>
+        <v>2232</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1395</v>
+        <v>2070</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.84</v>
+        <v>341.28</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>298.2</v>
+        <v>1363.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1938</v>
+        <v>3898.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>42.3</v>
+        <v>222.64</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>704.7</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2085</v>
+        <v>5190</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.09</v>
+        <v>116.28</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1147.5</v>
+        <v>3340.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.210000000000001</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>984960</v>
+        <v>2462400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>160720.36</v>
       </c>
       <c r="L5" t="n">
-        <v>1724814</v>
+        <v>2255526</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>13923</v>
+        <v>17646</v>
       </c>
       <c r="O5" t="n">
-        <v>51000</v>
+        <v>84150</v>
       </c>
       <c r="P5" t="n">
-        <v>11115</v>
+        <v>15912</v>
       </c>
       <c r="Q5" t="n">
-        <v>266253.16</v>
+        <v>1401332.4</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>607392</v>
+        <v>935064</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1530</v>
+        <v>3570</v>
       </c>
       <c r="O6" t="n">
-        <v>15300</v>
+        <v>49725</v>
       </c>
       <c r="P6" t="n">
-        <v>58500</v>
+        <v>85117.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>328268.7</v>
+        <v>1727730</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>3402</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>624150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>213840</v>
+        <v>401760</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>90675</v>
+        <v>134550</v>
       </c>
       <c r="Q7" t="n">
-        <v>38905.92</v>
+        <v>204768</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53676</v>
+        <v>245376</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>125970</v>
+        <v>253422</v>
       </c>
       <c r="Q8" t="n">
-        <v>25381.19</v>
+        <v>133585.2</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>126846</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>135525</v>
+        <v>337350</v>
       </c>
       <c r="Q9" t="n">
-        <v>13256.33</v>
+        <v>69770.16</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>74587.5</v>
+        <v>217132.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4924.8</v>
+        <v>25920</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>63720</v>
       </c>
       <c r="H4" t="n">
-        <v>4470</v>
+        <v>4560</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>94620</v>
+        <v>114930</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18630</v>
+        <v>21810</v>
       </c>
       <c r="O4" t="n">
-        <v>31650</v>
+        <v>31950</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>26667.01</v>
+        <v>144704.7</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>14880</v>
       </c>
       <c r="H5" t="n">
-        <v>3180</v>
+        <v>3750</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>28710</v>
+        <v>34350</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7530</v>
+        <v>8310</v>
       </c>
       <c r="O5" t="n">
-        <v>26340</v>
+        <v>26310</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5506.39</v>
+        <v>29879.64</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>4500</v>
       </c>
       <c r="H6" t="n">
-        <v>960</v>
+        <v>1470</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7140</v>
+        <v>12780</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3630</v>
+        <v>4410</v>
       </c>
       <c r="O6" t="n">
-        <v>21450</v>
+        <v>23670</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>758.02</v>
+        <v>4113.27</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>1500</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2850</v>
+        <v>4410</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>750</v>
+        <v>2190</v>
       </c>
       <c r="O7" t="n">
-        <v>8970</v>
+        <v>11010</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>197.95</v>
+        <v>1074.15</v>
       </c>
     </row>
     <row r="8">
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1020</v>
+        <v>1830</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O8" t="n">
-        <v>1740</v>
+        <v>3840</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>70.01000000000001</v>
+        <v>379.89</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>300</v>
+        <v>720</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.02</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1144.8</v>
+        <v>1350</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>1.32</v>
       </c>
       <c r="L5" t="n">
-        <v>6029.1</v>
+        <v>7213.5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>75.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1317</v>
+        <v>1315.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>275.32</v>
+        <v>1493.98</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>225</v>
       </c>
       <c r="H6" t="n">
-        <v>547.2</v>
+        <v>837.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2641.8</v>
+        <v>4728.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>181.5</v>
+        <v>220.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5362.5</v>
+        <v>5917.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>568.51</v>
+        <v>3084.95</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>225</v>
       </c>
       <c r="H7" t="n">
-        <v>87.59999999999999</v>
+        <v>372.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1710</v>
+        <v>2646</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>52.5</v>
+        <v>153.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3139.5</v>
+        <v>3853.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>158.36</v>
+        <v>859.3200000000001</v>
       </c>
     </row>
     <row r="8">
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>724.2</v>
+        <v>1299.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O8" t="n">
-        <v>783</v>
+        <v>1728</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>66.51000000000001</v>
+        <v>360.9</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>396</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.93</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6525360</v>
+        <v>7695000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>64288.14</v>
       </c>
       <c r="L5" t="n">
-        <v>1085238</v>
+        <v>1298430</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>12801</v>
+        <v>14127</v>
       </c>
       <c r="O5" t="n">
-        <v>223890</v>
+        <v>223635</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>165191.72</v>
+        <v>896389.2</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>12150</v>
       </c>
       <c r="H6" t="n">
-        <v>3119040</v>
+        <v>4776030</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>475524</v>
+        <v>851148</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>30855</v>
+        <v>37485</v>
       </c>
       <c r="O6" t="n">
-        <v>911625</v>
+        <v>1005975</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>341107.61</v>
+        <v>1850971.5</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>12150</v>
       </c>
       <c r="H7" t="n">
-        <v>499320</v>
+        <v>2122110</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>307800</v>
+        <v>476280</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8925</v>
+        <v>26061</v>
       </c>
       <c r="O7" t="n">
-        <v>533715</v>
+        <v>655095</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>95016.24000000001</v>
+        <v>515592</v>
       </c>
     </row>
     <row r="8">
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>130356</v>
+        <v>233874</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="O8" t="n">
-        <v>133110</v>
+        <v>293760</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>39904.73</v>
+        <v>216537.3</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>28050</v>
+        <v>67320</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1756.83</v>
+        <v>9533.16</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>80100</v>
       </c>
       <c r="H4" t="n">
-        <v>9000</v>
+        <v>9900</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>133</v>
       </c>
       <c r="L4" t="n">
-        <v>197400</v>
+        <v>195900</v>
       </c>
       <c r="M4" t="n">
-        <v>17280</v>
+        <v>990</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>37410</v>
+        <v>41220</v>
       </c>
       <c r="P4" t="n">
-        <v>23550</v>
+        <v>4920</v>
       </c>
       <c r="Q4" t="n">
         <v>34076.73</v>
@@ -13533,7 +13533,7 @@
         <v>87180</v>
       </c>
       <c r="H5" t="n">
-        <v>7620</v>
+        <v>8040</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -13545,19 +13545,19 @@
         <v>83</v>
       </c>
       <c r="L5" t="n">
-        <v>188490</v>
+        <v>176610</v>
       </c>
       <c r="M5" t="n">
-        <v>18360</v>
+        <v>1950</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>30900</v>
+        <v>37860</v>
       </c>
       <c r="P5" t="n">
-        <v>35550</v>
+        <v>16050</v>
       </c>
       <c r="Q5" t="n">
         <v>36933.91</v>
@@ -13586,7 +13586,7 @@
         <v>86580</v>
       </c>
       <c r="H6" t="n">
-        <v>12180</v>
+        <v>12930</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -13598,19 +13598,19 @@
         <v>84</v>
       </c>
       <c r="L6" t="n">
-        <v>211230</v>
+        <v>195690</v>
       </c>
       <c r="M6" t="n">
-        <v>10920</v>
+        <v>4020</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>24210</v>
+        <v>23250</v>
       </c>
       <c r="P6" t="n">
-        <v>34680</v>
+        <v>22980</v>
       </c>
       <c r="Q6" t="n">
         <v>43853.67</v>
@@ -13639,7 +13639,7 @@
         <v>62220</v>
       </c>
       <c r="H7" t="n">
-        <v>3930</v>
+        <v>4050</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -13651,19 +13651,19 @@
         <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>134310</v>
+        <v>124620</v>
       </c>
       <c r="M7" t="n">
-        <v>6360</v>
+        <v>5160</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>20670</v>
+        <v>21660</v>
       </c>
       <c r="P7" t="n">
-        <v>35790</v>
+        <v>28830</v>
       </c>
       <c r="Q7" t="n">
         <v>34188.33</v>
@@ -13692,7 +13692,7 @@
         <v>36360</v>
       </c>
       <c r="H8" t="n">
-        <v>480</v>
+        <v>750</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -13704,19 +13704,19 @@
         <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>77220</v>
+        <v>85140</v>
       </c>
       <c r="M8" t="n">
-        <v>3540</v>
+        <v>10140</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27330</v>
+        <v>26220</v>
       </c>
       <c r="P8" t="n">
-        <v>32250</v>
+        <v>33810</v>
       </c>
       <c r="Q8" t="n">
         <v>28853.62</v>
@@ -13745,7 +13745,7 @@
         <v>22410</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>40890</v>
+        <v>48960</v>
       </c>
       <c r="M9" t="n">
-        <v>2070</v>
+        <v>12270</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>11430</v>
+        <v>17160</v>
       </c>
       <c r="P9" t="n">
-        <v>35640</v>
+        <v>35340</v>
       </c>
       <c r="Q9" t="n">
         <v>16434.55</v>
@@ -13810,19 +13810,19 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>10650</v>
+        <v>23130</v>
       </c>
       <c r="M10" t="n">
-        <v>1080</v>
+        <v>10950</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>780</v>
+        <v>1830</v>
       </c>
       <c r="P10" t="n">
-        <v>38730</v>
+        <v>44670</v>
       </c>
       <c r="Q10" t="n">
         <v>2004</v>
@@ -13863,10 +13863,10 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>4650</v>
+        <v>29790</v>
       </c>
       <c r="M11" t="n">
-        <v>360</v>
+        <v>10080</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>31380</v>
+        <v>48450</v>
       </c>
       <c r="Q11" t="n">
         <v>409.68</v>
@@ -13904,7 +13904,7 @@
         <v>240</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3600</v>
+        <v>24630</v>
       </c>
       <c r="M12" t="n">
-        <v>330</v>
+        <v>5940</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>25650</v>
+        <v>46920</v>
       </c>
       <c r="Q12" t="n">
         <v>237.93</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1710</v>
+        <v>11100</v>
       </c>
       <c r="M13" t="n">
-        <v>390</v>
+        <v>9780</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14700</v>
+        <v>26340</v>
       </c>
       <c r="Q13" t="n">
         <v>140.39</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>900</v>
+        <v>3990</v>
       </c>
       <c r="M14" t="n">
-        <v>180</v>
+        <v>1260</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10890</v>
+        <v>10680</v>
       </c>
       <c r="Q14" t="n">
         <v>16.29</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>330</v>
+        <v>6000</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12750</v>
+        <v>21690</v>
       </c>
       <c r="Q15" t="n">
         <v>21.87</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>3030</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>10350</v>
+        <v>24360</v>
       </c>
       <c r="Q16" t="n">
         <v>14.06</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>2760</v>
       </c>
       <c r="M17" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3750</v>
+        <v>8220</v>
       </c>
       <c r="Q17" t="n">
         <v>6.25</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>570</v>
+        <v>1140</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q18" t="n">
         <v>2.01</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17787.6</v>
+        <v>19828.8</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -14837,22 +14837,22 @@
         <v>73.15000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>171145.8</v>
+        <v>178749.9</v>
       </c>
       <c r="M5" t="n">
-        <v>971.4</v>
+        <v>649.2</v>
       </c>
       <c r="N5" t="n">
-        <v>591</v>
+        <v>745.8</v>
       </c>
       <c r="O5" t="n">
-        <v>8335.5</v>
+        <v>9456</v>
       </c>
       <c r="P5" t="n">
-        <v>1204.8</v>
+        <v>766.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>6645.31</v>
+        <v>68864.66</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>12171</v>
       </c>
       <c r="H6" t="n">
-        <v>29651.4</v>
+        <v>30352.5</v>
       </c>
       <c r="I6" t="n">
         <v>1.01</v>
@@ -14890,22 +14890,22 @@
         <v>89.23</v>
       </c>
       <c r="L6" t="n">
-        <v>228105</v>
+        <v>230358.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2368.8</v>
+        <v>2066.4</v>
       </c>
       <c r="N6" t="n">
-        <v>748.5</v>
+        <v>1209</v>
       </c>
       <c r="O6" t="n">
-        <v>26730</v>
+        <v>29542.5</v>
       </c>
       <c r="P6" t="n">
-        <v>9085.5</v>
+        <v>6588</v>
       </c>
       <c r="Q6" t="n">
-        <v>78926.09</v>
+        <v>817903.4</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>29088</v>
       </c>
       <c r="H7" t="n">
-        <v>22053.3</v>
+        <v>22929.3</v>
       </c>
       <c r="I7" t="n">
         <v>1.91</v>
@@ -14943,22 +14943,22 @@
         <v>66.34999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>291078</v>
+        <v>292896</v>
       </c>
       <c r="M7" t="n">
-        <v>6919.5</v>
+        <v>9334.5</v>
       </c>
       <c r="N7" t="n">
-        <v>262.5</v>
+        <v>518.7</v>
       </c>
       <c r="O7" t="n">
-        <v>25137</v>
+        <v>27783</v>
       </c>
       <c r="P7" t="n">
-        <v>17557.5</v>
+        <v>13260</v>
       </c>
       <c r="Q7" t="n">
-        <v>68971.66</v>
+        <v>714746.61</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>103486.5</v>
       </c>
       <c r="H8" t="n">
-        <v>7599</v>
+        <v>10276.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -14996,22 +14996,22 @@
         <v>76.54000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>276900</v>
+        <v>288359.4</v>
       </c>
       <c r="M8" t="n">
-        <v>6864</v>
+        <v>16681.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O8" t="n">
-        <v>27324</v>
+        <v>30820.5</v>
       </c>
       <c r="P8" t="n">
-        <v>26220</v>
+        <v>25000.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>72359.92</v>
+        <v>749858.87</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>118728</v>
       </c>
       <c r="H9" t="n">
-        <v>3780</v>
+        <v>3840</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>242708.4</v>
+        <v>268320.6</v>
       </c>
       <c r="M9" t="n">
-        <v>6930</v>
+        <v>21000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>20493</v>
+        <v>28660.5</v>
       </c>
       <c r="P9" t="n">
-        <v>36750</v>
+        <v>35400</v>
       </c>
       <c r="Q9" t="n">
-        <v>60357.63</v>
+        <v>625480.33</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>80760</v>
       </c>
       <c r="H10" t="n">
-        <v>4830</v>
+        <v>4530</v>
       </c>
       <c r="I10" t="n">
         <v>2.61</v>
@@ -15102,22 +15102,22 @@
         <v>34.8</v>
       </c>
       <c r="L10" t="n">
-        <v>162416.1</v>
+        <v>191866.2</v>
       </c>
       <c r="M10" t="n">
-        <v>5380.5</v>
+        <v>21573</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>8820</v>
+        <v>16527</v>
       </c>
       <c r="P10" t="n">
-        <v>68722.5</v>
+        <v>79458</v>
       </c>
       <c r="Q10" t="n">
-        <v>40023.44</v>
+        <v>414759.06</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>62910</v>
       </c>
       <c r="H11" t="n">
-        <v>4710</v>
+        <v>5670</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15155,22 +15155,22 @@
         <v>13.48</v>
       </c>
       <c r="L11" t="n">
-        <v>162930</v>
+        <v>208800</v>
       </c>
       <c r="M11" t="n">
-        <v>3591</v>
+        <v>22194</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4386</v>
+        <v>12877.5</v>
       </c>
       <c r="P11" t="n">
-        <v>58320</v>
+        <v>90531</v>
       </c>
       <c r="Q11" t="n">
-        <v>28828.51</v>
+        <v>298747.08</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>48510</v>
       </c>
       <c r="H12" t="n">
-        <v>1470</v>
+        <v>1980</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>5.56</v>
       </c>
       <c r="L12" t="n">
-        <v>102390</v>
+        <v>145380</v>
       </c>
       <c r="M12" t="n">
-        <v>3135</v>
+        <v>15390</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2550</v>
+        <v>3960</v>
       </c>
       <c r="P12" t="n">
-        <v>47580</v>
+        <v>82050</v>
       </c>
       <c r="Q12" t="n">
-        <v>19815.7</v>
+        <v>205348.14</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>25650</v>
       </c>
       <c r="H13" t="n">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -15261,22 +15261,22 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>44520</v>
+        <v>65520</v>
       </c>
       <c r="M13" t="n">
-        <v>1860</v>
+        <v>20310</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3510</v>
+        <v>3300</v>
       </c>
       <c r="P13" t="n">
-        <v>31770</v>
+        <v>47880</v>
       </c>
       <c r="Q13" t="n">
-        <v>10227.81</v>
+        <v>105989.76</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>6240</v>
       </c>
       <c r="H14" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15314,22 +15314,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>17970</v>
+        <v>32010</v>
       </c>
       <c r="M14" t="n">
-        <v>930</v>
+        <v>7230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>840</v>
+        <v>1440</v>
       </c>
       <c r="P14" t="n">
-        <v>27810</v>
+        <v>29970</v>
       </c>
       <c r="Q14" t="n">
-        <v>3889.71</v>
+        <v>40308.65</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>3870</v>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8160</v>
+        <v>24930</v>
       </c>
       <c r="M15" t="n">
-        <v>870</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P15" t="n">
-        <v>38040</v>
+        <v>51060</v>
       </c>
       <c r="Q15" t="n">
-        <v>2387.57</v>
+        <v>24742.16</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>1380</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2460</v>
+        <v>10200</v>
       </c>
       <c r="M16" t="n">
-        <v>180</v>
+        <v>1710</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P16" t="n">
-        <v>24810</v>
+        <v>41970</v>
       </c>
       <c r="Q16" t="n">
-        <v>1227.27</v>
+        <v>12718.03</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>270</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4350</v>
+        <v>9090</v>
       </c>
       <c r="M17" t="n">
-        <v>3450</v>
+        <v>4410</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>19080</v>
+        <v>27030</v>
       </c>
       <c r="Q17" t="n">
-        <v>532.4400000000001</v>
+        <v>5517.66</v>
       </c>
     </row>
     <row r="18">
@@ -15526,22 +15526,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1440</v>
+        <v>4770</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>1380</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18330</v>
+        <v>24030</v>
       </c>
       <c r="Q18" t="n">
-        <v>271.08</v>
+        <v>2809.14</v>
       </c>
     </row>
     <row r="19">
@@ -15567,7 +15567,7 @@
         <v>3750</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>750</v>
+        <v>3090</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>7530</v>
+        <v>19080</v>
       </c>
       <c r="Q19" t="n">
-        <v>98.43000000000001</v>
+        <v>1020.03</v>
       </c>
     </row>
     <row r="20">
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.3</v>
+        <v>179.26</v>
       </c>
     </row>
     <row r="21">
@@ -15685,10 +15685,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.01</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="22">
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="23">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2743.2</v>
+        <v>2894.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -16129,19 +16129,19 @@
         <v>27.47</v>
       </c>
       <c r="L5" t="n">
-        <v>39582.9</v>
+        <v>37088.1</v>
       </c>
       <c r="M5" t="n">
-        <v>367.2</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1545</v>
+        <v>1893</v>
       </c>
       <c r="P5" t="n">
-        <v>711</v>
+        <v>321</v>
       </c>
       <c r="Q5" t="n">
         <v>1846.7</v>
@@ -16170,7 +16170,7 @@
         <v>4329</v>
       </c>
       <c r="H6" t="n">
-        <v>6942.6</v>
+        <v>7370.1</v>
       </c>
       <c r="I6" t="n">
         <v>1.01</v>
@@ -16182,19 +16182,19 @@
         <v>42.59</v>
       </c>
       <c r="L6" t="n">
-        <v>78155.10000000001</v>
+        <v>72405.3</v>
       </c>
       <c r="M6" t="n">
-        <v>873.6</v>
+        <v>321.6</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6052.5</v>
+        <v>5812.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5202</v>
+        <v>3447</v>
       </c>
       <c r="Q6" t="n">
         <v>32890.25</v>
@@ -16223,7 +16223,7 @@
         <v>9333</v>
       </c>
       <c r="H7" t="n">
-        <v>2868.9</v>
+        <v>2956.5</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -16235,19 +16235,19 @@
         <v>25.52</v>
       </c>
       <c r="L7" t="n">
-        <v>80586</v>
+        <v>74772</v>
       </c>
       <c r="M7" t="n">
-        <v>2226</v>
+        <v>1806</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7234.5</v>
+        <v>7581</v>
       </c>
       <c r="P7" t="n">
-        <v>8947.5</v>
+        <v>7207.5</v>
       </c>
       <c r="Q7" t="n">
         <v>27350.66</v>
@@ -16276,7 +16276,7 @@
         <v>23634</v>
       </c>
       <c r="H8" t="n">
-        <v>408</v>
+        <v>637.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16288,19 +16288,19 @@
         <v>24.29</v>
       </c>
       <c r="L8" t="n">
-        <v>54826.2</v>
+        <v>60449.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1947</v>
+        <v>5577</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>12298.5</v>
+        <v>11799</v>
       </c>
       <c r="P8" t="n">
-        <v>12255</v>
+        <v>12847.8</v>
       </c>
       <c r="Q8" t="n">
         <v>27410.94</v>
@@ -16329,7 +16329,7 @@
         <v>19048.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>5.62</v>
       </c>
       <c r="L9" t="n">
-        <v>33120.9</v>
+        <v>39657.6</v>
       </c>
       <c r="M9" t="n">
-        <v>1449</v>
+        <v>8589</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6286.5</v>
+        <v>9438</v>
       </c>
       <c r="P9" t="n">
-        <v>17820</v>
+        <v>17670</v>
       </c>
       <c r="Q9" t="n">
         <v>15941.51</v>
@@ -16394,19 +16394,19 @@
         <v>1.74</v>
       </c>
       <c r="L10" t="n">
-        <v>9478.5</v>
+        <v>20585.7</v>
       </c>
       <c r="M10" t="n">
-        <v>918</v>
+        <v>9307.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>546</v>
+        <v>1281</v>
       </c>
       <c r="P10" t="n">
-        <v>32920.5</v>
+        <v>37969.5</v>
       </c>
       <c r="Q10" t="n">
         <v>2004</v>
@@ -16447,10 +16447,10 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>4650</v>
+        <v>29790</v>
       </c>
       <c r="M11" t="n">
-        <v>324</v>
+        <v>9072</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>28242</v>
+        <v>43605</v>
       </c>
       <c r="Q11" t="n">
         <v>409.68</v>
@@ -16488,7 +16488,7 @@
         <v>240</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3600</v>
+        <v>24630</v>
       </c>
       <c r="M12" t="n">
-        <v>313.5</v>
+        <v>5643</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>25650</v>
+        <v>46920</v>
       </c>
       <c r="Q12" t="n">
         <v>237.93</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1710</v>
+        <v>11100</v>
       </c>
       <c r="M13" t="n">
-        <v>390</v>
+        <v>9780</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14700</v>
+        <v>26340</v>
       </c>
       <c r="Q13" t="n">
         <v>140.39</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>900</v>
+        <v>3990</v>
       </c>
       <c r="M14" t="n">
-        <v>180</v>
+        <v>1260</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10890</v>
+        <v>10680</v>
       </c>
       <c r="Q14" t="n">
         <v>16.29</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>330</v>
+        <v>6000</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12750</v>
+        <v>21690</v>
       </c>
       <c r="Q15" t="n">
         <v>21.87</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>3030</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>10350</v>
+        <v>24360</v>
       </c>
       <c r="Q16" t="n">
         <v>14.06</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>2760</v>
       </c>
       <c r="M17" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3750</v>
+        <v>8220</v>
       </c>
       <c r="Q17" t="n">
         <v>6.25</v>
@@ -16818,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>570</v>
+        <v>1140</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q18" t="n">
         <v>2.01</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>15636240</v>
+        <v>16498080</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -17421,19 +17421,19 @@
         <v>1333978.99</v>
       </c>
       <c r="L5" t="n">
-        <v>7124922</v>
+        <v>6675858</v>
       </c>
       <c r="M5" t="n">
-        <v>128520</v>
+        <v>13650</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>262650</v>
+        <v>321810</v>
       </c>
       <c r="P5" t="n">
-        <v>46215</v>
+        <v>20865</v>
       </c>
       <c r="Q5" t="n">
         <v>1108017.25</v>
@@ -17462,7 +17462,7 @@
         <v>233766</v>
       </c>
       <c r="H6" t="n">
-        <v>39572820</v>
+        <v>42009570</v>
       </c>
       <c r="I6" t="n">
         <v>196943.14</v>
@@ -17474,19 +17474,19 @@
         <v>2067902.93</v>
       </c>
       <c r="L6" t="n">
-        <v>14067918</v>
+        <v>13032954</v>
       </c>
       <c r="M6" t="n">
-        <v>305760</v>
+        <v>112560</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1028925</v>
+        <v>988125</v>
       </c>
       <c r="P6" t="n">
-        <v>338130</v>
+        <v>224055</v>
       </c>
       <c r="Q6" t="n">
         <v>19734149.88</v>
@@ -17515,7 +17515,7 @@
         <v>503982</v>
       </c>
       <c r="H7" t="n">
-        <v>16352730</v>
+        <v>16852050</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -17527,19 +17527,19 @@
         <v>1239149.12</v>
       </c>
       <c r="L7" t="n">
-        <v>14505480</v>
+        <v>13458960</v>
       </c>
       <c r="M7" t="n">
-        <v>779100</v>
+        <v>632100</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1229865</v>
+        <v>1288770</v>
       </c>
       <c r="P7" t="n">
-        <v>581587.5</v>
+        <v>468487.5</v>
       </c>
       <c r="Q7" t="n">
         <v>16410396.1</v>
@@ -17568,7 +17568,7 @@
         <v>1276236</v>
       </c>
       <c r="H8" t="n">
-        <v>2325600</v>
+        <v>3633750</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17580,19 +17580,19 @@
         <v>1179328.13</v>
       </c>
       <c r="L8" t="n">
-        <v>9868716</v>
+        <v>10880892</v>
       </c>
       <c r="M8" t="n">
-        <v>681450</v>
+        <v>1951950</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2090745</v>
+        <v>2005830</v>
       </c>
       <c r="P8" t="n">
-        <v>796575</v>
+        <v>835107</v>
       </c>
       <c r="Q8" t="n">
         <v>16446564.54</v>
@@ -17621,7 +17621,7 @@
         <v>1028619</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>272933.28</v>
       </c>
       <c r="L9" t="n">
-        <v>5961762</v>
+        <v>7138368</v>
       </c>
       <c r="M9" t="n">
-        <v>507150</v>
+        <v>3006150</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1068705</v>
+        <v>1604460</v>
       </c>
       <c r="P9" t="n">
-        <v>1158300</v>
+        <v>1148550</v>
       </c>
       <c r="Q9" t="n">
         <v>9564908.57</v>
@@ -17686,19 +17686,19 @@
         <v>84487.44</v>
       </c>
       <c r="L10" t="n">
-        <v>1706130</v>
+        <v>3705426</v>
       </c>
       <c r="M10" t="n">
-        <v>321300</v>
+        <v>3257625</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>92820</v>
+        <v>217770</v>
       </c>
       <c r="P10" t="n">
-        <v>2139832.5</v>
+        <v>2468017.5</v>
       </c>
       <c r="Q10" t="n">
         <v>1202400.72</v>
@@ -17739,10 +17739,10 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>837000</v>
+        <v>5362200</v>
       </c>
       <c r="M11" t="n">
-        <v>113400</v>
+        <v>3175200</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1835730</v>
+        <v>2834325</v>
       </c>
       <c r="Q11" t="n">
         <v>245810.16</v>
@@ -17780,7 +17780,7 @@
         <v>12960</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>648000</v>
+        <v>4433400</v>
       </c>
       <c r="M12" t="n">
-        <v>109725</v>
+        <v>1975050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P12" t="n">
-        <v>1667250</v>
+        <v>3049800</v>
       </c>
       <c r="Q12" t="n">
         <v>142758.72</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>307800</v>
+        <v>1998000</v>
       </c>
       <c r="M13" t="n">
-        <v>136500</v>
+        <v>3423000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>955500</v>
+        <v>1712100</v>
       </c>
       <c r="Q13" t="n">
         <v>84235.67999999999</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>162000</v>
+        <v>718200</v>
       </c>
       <c r="M14" t="n">
-        <v>63000</v>
+        <v>441000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>707850</v>
+        <v>694200</v>
       </c>
       <c r="Q14" t="n">
         <v>9776.16</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>59400</v>
+        <v>1080000</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>828750</v>
+        <v>1409850</v>
       </c>
       <c r="Q15" t="n">
         <v>13124.16</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>54000</v>
+        <v>545400</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>52500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>672750</v>
+        <v>1583400</v>
       </c>
       <c r="Q16" t="n">
         <v>8436.959999999999</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>81000</v>
+        <v>496800</v>
       </c>
       <c r="M17" t="n">
-        <v>105000</v>
+        <v>126000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>243750</v>
+        <v>534300</v>
       </c>
       <c r="Q17" t="n">
         <v>3749.76</v>
@@ -18110,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>102600</v>
+        <v>205200</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>44850</v>
+        <v>79950</v>
       </c>
       <c r="Q18" t="n">
         <v>1205.28</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>16200</v>
+        <v>75600</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>84570</v>
       </c>
       <c r="H4" t="n">
-        <v>9930</v>
+        <v>12630</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>276960</v>
+        <v>320190</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>16290</v>
+        <v>12660</v>
       </c>
       <c r="O4" t="n">
-        <v>50370</v>
+        <v>54060</v>
       </c>
       <c r="P4" t="n">
-        <v>6300</v>
+        <v>3420</v>
       </c>
       <c r="Q4" t="n">
-        <v>27189.22</v>
+        <v>311543.1</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>19080</v>
       </c>
       <c r="H5" t="n">
-        <v>1860</v>
+        <v>3120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>81420</v>
+        <v>107970</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>20760</v>
+        <v>27180</v>
       </c>
       <c r="O5" t="n">
-        <v>25950</v>
+        <v>36750</v>
       </c>
       <c r="P5" t="n">
-        <v>5190</v>
+        <v>7140</v>
       </c>
       <c r="Q5" t="n">
-        <v>7652.79</v>
+        <v>87688.25999999999</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>2010</v>
       </c>
       <c r="H6" t="n">
-        <v>270</v>
+        <v>420</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12480</v>
+        <v>20460</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2220</v>
+        <v>5970</v>
       </c>
       <c r="O6" t="n">
-        <v>3990</v>
+        <v>6240</v>
       </c>
       <c r="P6" t="n">
-        <v>3540</v>
+        <v>7200</v>
       </c>
       <c r="Q6" t="n">
-        <v>675.65</v>
+        <v>7741.8</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1170</v>
+        <v>4140</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="O7" t="n">
-        <v>330</v>
+        <v>900</v>
       </c>
       <c r="P7" t="n">
-        <v>3600</v>
+        <v>9060</v>
       </c>
       <c r="Q7" t="n">
-        <v>101.35</v>
+        <v>1161.27</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>210</v>
+        <v>540</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1200</v>
+        <v>4110</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.6</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>669.6</v>
+        <v>1123.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>17098.2</v>
+        <v>22673.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>207.6</v>
+        <v>271.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1297.5</v>
+        <v>1837.5</v>
       </c>
       <c r="P5" t="n">
-        <v>103.8</v>
+        <v>142.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>382.64</v>
+        <v>4384.41</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>100.5</v>
       </c>
       <c r="H6" t="n">
-        <v>153.9</v>
+        <v>239.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4617.6</v>
+        <v>7570.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>111</v>
+        <v>298.5</v>
       </c>
       <c r="O6" t="n">
-        <v>997.5</v>
+        <v>1560</v>
       </c>
       <c r="P6" t="n">
-        <v>531</v>
+        <v>1080</v>
       </c>
       <c r="Q6" t="n">
-        <v>506.74</v>
+        <v>5806.35</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>702</v>
+        <v>2484</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="O7" t="n">
-        <v>115.5</v>
+        <v>315</v>
       </c>
       <c r="P7" t="n">
-        <v>900</v>
+        <v>2265</v>
       </c>
       <c r="Q7" t="n">
-        <v>81.08</v>
+        <v>929.02</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>149.1</v>
+        <v>383.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>456</v>
+        <v>1561.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.22</v>
+        <v>82.76000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3816720</v>
+        <v>6402240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3077676</v>
+        <v>4081266</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>35292</v>
+        <v>46206</v>
       </c>
       <c r="O5" t="n">
-        <v>220575</v>
+        <v>312375</v>
       </c>
       <c r="P5" t="n">
-        <v>6747</v>
+        <v>9282</v>
       </c>
       <c r="Q5" t="n">
-        <v>229583.81</v>
+        <v>2630647.8</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>5427</v>
       </c>
       <c r="H6" t="n">
-        <v>877230</v>
+        <v>1364580</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>831168</v>
+        <v>1362636</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>18870</v>
+        <v>50745</v>
       </c>
       <c r="O6" t="n">
-        <v>169575</v>
+        <v>265200</v>
       </c>
       <c r="P6" t="n">
-        <v>34515</v>
+        <v>70200</v>
       </c>
       <c r="Q6" t="n">
-        <v>304041.6</v>
+        <v>3483810</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>126360</v>
+        <v>447120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>714</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
-        <v>19635</v>
+        <v>53550</v>
       </c>
       <c r="P7" t="n">
-        <v>58500</v>
+        <v>147225</v>
       </c>
       <c r="Q7" t="n">
-        <v>48646.66</v>
+        <v>557409.6</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26838</v>
+        <v>69012</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>29640</v>
+        <v>101517</v>
       </c>
       <c r="Q8" t="n">
-        <v>4333.82</v>
+        <v>49658.4</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10800</v>
+        <v>27000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>101389320</v>
+        <v>113024160</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -22589,22 +22589,22 @@
         <v>3551919.96</v>
       </c>
       <c r="L5" t="n">
-        <v>30806244</v>
+        <v>32174982</v>
       </c>
       <c r="M5" t="n">
-        <v>339990</v>
+        <v>227220</v>
       </c>
       <c r="N5" t="n">
-        <v>100470</v>
+        <v>126786</v>
       </c>
       <c r="O5" t="n">
-        <v>1417035</v>
+        <v>1607520</v>
       </c>
       <c r="P5" t="n">
-        <v>78312</v>
+        <v>49803</v>
       </c>
       <c r="Q5" t="n">
-        <v>3987183.42</v>
+        <v>41318795.92</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>657234</v>
       </c>
       <c r="H6" t="n">
-        <v>169012980</v>
+        <v>173009250</v>
       </c>
       <c r="I6" t="n">
         <v>196943.14</v>
@@ -22642,22 +22642,22 @@
         <v>4332748.99</v>
       </c>
       <c r="L6" t="n">
-        <v>41058900</v>
+        <v>41464494</v>
       </c>
       <c r="M6" t="n">
-        <v>829080</v>
+        <v>723240</v>
       </c>
       <c r="N6" t="n">
-        <v>127245</v>
+        <v>205530</v>
       </c>
       <c r="O6" t="n">
-        <v>4544100</v>
+        <v>5022225</v>
       </c>
       <c r="P6" t="n">
-        <v>590557.5</v>
+        <v>428220</v>
       </c>
       <c r="Q6" t="n">
-        <v>47355652.08</v>
+        <v>490742039.7</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1570752</v>
       </c>
       <c r="H7" t="n">
-        <v>125703810</v>
+        <v>130697010</v>
       </c>
       <c r="I7" t="n">
         <v>371744.74</v>
@@ -22695,22 +22695,22 @@
         <v>3221787.71</v>
       </c>
       <c r="L7" t="n">
-        <v>52394040</v>
+        <v>52721280</v>
       </c>
       <c r="M7" t="n">
-        <v>2421825</v>
+        <v>3267075</v>
       </c>
       <c r="N7" t="n">
-        <v>44625</v>
+        <v>88179</v>
       </c>
       <c r="O7" t="n">
-        <v>4273290</v>
+        <v>4723110</v>
       </c>
       <c r="P7" t="n">
-        <v>1141237.5</v>
+        <v>861900</v>
       </c>
       <c r="Q7" t="n">
-        <v>41382994.18</v>
+        <v>428847963.84</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>5588271</v>
       </c>
       <c r="H8" t="n">
-        <v>43314300</v>
+        <v>58576050</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -22748,22 +22748,22 @@
         <v>3716670.46</v>
       </c>
       <c r="L8" t="n">
-        <v>49842000</v>
+        <v>51904692</v>
       </c>
       <c r="M8" t="n">
-        <v>2402400</v>
+        <v>5838525</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>9180</v>
       </c>
       <c r="O8" t="n">
-        <v>4645080</v>
+        <v>5239485</v>
       </c>
       <c r="P8" t="n">
-        <v>1704300</v>
+        <v>1625013</v>
       </c>
       <c r="Q8" t="n">
-        <v>43415953.34</v>
+        <v>449915322.96</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>6411312</v>
       </c>
       <c r="H9" t="n">
-        <v>21546000</v>
+        <v>21888000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>2573370.89</v>
       </c>
       <c r="L9" t="n">
-        <v>43687512</v>
+        <v>48297708</v>
       </c>
       <c r="M9" t="n">
-        <v>2425500</v>
+        <v>7350000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3483810</v>
+        <v>4872285</v>
       </c>
       <c r="P9" t="n">
-        <v>2388750</v>
+        <v>2301000</v>
       </c>
       <c r="Q9" t="n">
-        <v>36214580.78</v>
+        <v>375288195.98</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>4361040</v>
       </c>
       <c r="H10" t="n">
-        <v>27531000</v>
+        <v>25821000</v>
       </c>
       <c r="I10" t="n">
         <v>506924.64</v>
@@ -22854,22 +22854,22 @@
         <v>1689748.8</v>
       </c>
       <c r="L10" t="n">
-        <v>29234898</v>
+        <v>34535916</v>
       </c>
       <c r="M10" t="n">
-        <v>1883175</v>
+        <v>7550550</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1499400</v>
+        <v>2809590</v>
       </c>
       <c r="P10" t="n">
-        <v>4466962.5</v>
+        <v>5164770</v>
       </c>
       <c r="Q10" t="n">
-        <v>24014065.68</v>
+        <v>248855438.7</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>3397140</v>
       </c>
       <c r="H11" t="n">
-        <v>26847000</v>
+        <v>32319000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22907,22 +22907,22 @@
         <v>654413.49</v>
       </c>
       <c r="L11" t="n">
-        <v>29327400</v>
+        <v>37584000</v>
       </c>
       <c r="M11" t="n">
-        <v>1256850</v>
+        <v>7767900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>745620</v>
+        <v>2189175</v>
       </c>
       <c r="P11" t="n">
-        <v>3790800</v>
+        <v>5884515</v>
       </c>
       <c r="Q11" t="n">
-        <v>17297107.2</v>
+        <v>179248248</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>2619540</v>
       </c>
       <c r="H12" t="n">
-        <v>8379000</v>
+        <v>11286000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>270068.47</v>
       </c>
       <c r="L12" t="n">
-        <v>18430200</v>
+        <v>26168400</v>
       </c>
       <c r="M12" t="n">
-        <v>1097250</v>
+        <v>5386500</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>433500</v>
+        <v>673200</v>
       </c>
       <c r="P12" t="n">
-        <v>3092700</v>
+        <v>5333250</v>
       </c>
       <c r="Q12" t="n">
-        <v>11889417.6</v>
+        <v>123208884</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>1385100</v>
       </c>
       <c r="H13" t="n">
-        <v>4446000</v>
+        <v>4617000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -23013,22 +23013,22 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>8013600</v>
+        <v>11793600</v>
       </c>
       <c r="M13" t="n">
-        <v>651000</v>
+        <v>7108500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>596700</v>
+        <v>561000</v>
       </c>
       <c r="P13" t="n">
-        <v>2065050</v>
+        <v>3112200</v>
       </c>
       <c r="Q13" t="n">
-        <v>6136683.12</v>
+        <v>63593853.3</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>336960</v>
       </c>
       <c r="H14" t="n">
-        <v>1881000</v>
+        <v>2907000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23066,22 +23066,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3234600</v>
+        <v>5761800</v>
       </c>
       <c r="M14" t="n">
-        <v>325500</v>
+        <v>2530500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>142800</v>
+        <v>244800</v>
       </c>
       <c r="P14" t="n">
-        <v>1807650</v>
+        <v>1948050</v>
       </c>
       <c r="Q14" t="n">
-        <v>2333823.84</v>
+        <v>24185190.6</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>208980</v>
       </c>
       <c r="H15" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1468800</v>
+        <v>4487400</v>
       </c>
       <c r="M15" t="n">
-        <v>304500</v>
+        <v>1239000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5100</v>
+        <v>30600</v>
       </c>
       <c r="P15" t="n">
-        <v>2472600</v>
+        <v>3318900</v>
       </c>
       <c r="Q15" t="n">
-        <v>1432542.24</v>
+        <v>14845296.6</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>74520</v>
       </c>
       <c r="H16" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>442800</v>
+        <v>1836000</v>
       </c>
       <c r="M16" t="n">
-        <v>63000</v>
+        <v>598500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P16" t="n">
-        <v>1612650</v>
+        <v>2728050</v>
       </c>
       <c r="Q16" t="n">
-        <v>736359.12</v>
+        <v>7630818.3</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>14580</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>783000</v>
+        <v>1636200</v>
       </c>
       <c r="M17" t="n">
-        <v>1207500</v>
+        <v>1543500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1240200</v>
+        <v>1756950</v>
       </c>
       <c r="Q17" t="n">
-        <v>319466.16</v>
+        <v>3310596.9</v>
       </c>
     </row>
     <row r="18">
@@ -23278,22 +23278,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>259200</v>
+        <v>858600</v>
       </c>
       <c r="M18" t="n">
-        <v>63000</v>
+        <v>483000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1191450</v>
+        <v>1561950</v>
       </c>
       <c r="Q18" t="n">
-        <v>162645.84</v>
+        <v>1685483.1</v>
       </c>
     </row>
     <row r="19">
@@ -23319,7 +23319,7 @@
         <v>202500</v>
       </c>
       <c r="H19" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>135000</v>
+        <v>556200</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>535500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23343,10 +23343,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>489450</v>
+        <v>1240200</v>
       </c>
       <c r="Q19" t="n">
-        <v>59058.72</v>
+        <v>612019.8</v>
       </c>
     </row>
     <row r="20">
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>10378.8</v>
+        <v>107554.5</v>
       </c>
     </row>
     <row r="21">
@@ -23437,10 +23437,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M21" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23452,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1807.92</v>
+        <v>18735.3</v>
       </c>
     </row>
     <row r="22">
@@ -23493,7 +23493,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4888.08</v>
+        <v>50654.7</v>
       </c>
     </row>
     <row r="23">
@@ -23816,7 +23816,7 @@
         <v>52500</v>
       </c>
       <c r="H4" t="n">
-        <v>8550</v>
+        <v>7740</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>65</v>
       </c>
       <c r="L4" t="n">
-        <v>153660</v>
+        <v>142680</v>
       </c>
       <c r="M4" t="n">
-        <v>33120</v>
+        <v>42660</v>
       </c>
       <c r="N4" t="n">
-        <v>17880</v>
+        <v>17520</v>
       </c>
       <c r="O4" t="n">
-        <v>16140</v>
+        <v>17040</v>
       </c>
       <c r="P4" t="n">
-        <v>2670</v>
+        <v>1050</v>
       </c>
       <c r="Q4" t="n">
-        <v>13011.18</v>
+        <v>127560.6</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>66330</v>
       </c>
       <c r="H5" t="n">
-        <v>11910</v>
+        <v>12390</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>58</v>
       </c>
       <c r="L5" t="n">
-        <v>183930</v>
+        <v>169110</v>
       </c>
       <c r="M5" t="n">
-        <v>12780</v>
+        <v>21780</v>
       </c>
       <c r="N5" t="n">
-        <v>14370</v>
+        <v>16950</v>
       </c>
       <c r="O5" t="n">
-        <v>20520</v>
+        <v>22020</v>
       </c>
       <c r="P5" t="n">
-        <v>3360</v>
+        <v>1020</v>
       </c>
       <c r="Q5" t="n">
-        <v>20910.75</v>
+        <v>205007.4</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>66750</v>
       </c>
       <c r="H6" t="n">
-        <v>14130</v>
+        <v>13710</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>62</v>
       </c>
       <c r="L6" t="n">
-        <v>190920</v>
+        <v>188730</v>
       </c>
       <c r="M6" t="n">
-        <v>6210</v>
+        <v>13650</v>
       </c>
       <c r="N6" t="n">
-        <v>7410</v>
+        <v>9810</v>
       </c>
       <c r="O6" t="n">
-        <v>20760</v>
+        <v>19770</v>
       </c>
       <c r="P6" t="n">
-        <v>4230</v>
+        <v>2370</v>
       </c>
       <c r="Q6" t="n">
-        <v>25546.56</v>
+        <v>250456.5</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>86010</v>
       </c>
       <c r="H7" t="n">
-        <v>19770</v>
+        <v>20490</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -23987,22 +23987,22 @@
         <v>49</v>
       </c>
       <c r="L7" t="n">
-        <v>241950</v>
+        <v>245310</v>
       </c>
       <c r="M7" t="n">
-        <v>5040</v>
+        <v>13740</v>
       </c>
       <c r="N7" t="n">
-        <v>1980</v>
+        <v>3240</v>
       </c>
       <c r="O7" t="n">
-        <v>22830</v>
+        <v>24090</v>
       </c>
       <c r="P7" t="n">
-        <v>5760</v>
+        <v>4050</v>
       </c>
       <c r="Q7" t="n">
-        <v>25594.21</v>
+        <v>250923.6</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>96270</v>
       </c>
       <c r="H8" t="n">
-        <v>4800</v>
+        <v>5730</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>238800</v>
+        <v>243630</v>
       </c>
       <c r="M8" t="n">
-        <v>3810</v>
+        <v>11610</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>19620</v>
+        <v>21270</v>
       </c>
       <c r="P8" t="n">
-        <v>8700</v>
+        <v>6270</v>
       </c>
       <c r="Q8" t="n">
-        <v>28245.57</v>
+        <v>276917.4</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>94110</v>
       </c>
       <c r="H9" t="n">
-        <v>480</v>
+        <v>690</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>55</v>
       </c>
       <c r="L9" t="n">
-        <v>205260</v>
+        <v>222570</v>
       </c>
       <c r="M9" t="n">
-        <v>4770</v>
+        <v>10020</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22680</v>
+        <v>25950</v>
       </c>
       <c r="P9" t="n">
-        <v>10800</v>
+        <v>5760</v>
       </c>
       <c r="Q9" t="n">
-        <v>29546.2</v>
+        <v>289668.6</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>57570</v>
       </c>
       <c r="H10" t="n">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>112140</v>
+        <v>131430</v>
       </c>
       <c r="M10" t="n">
-        <v>3360</v>
+        <v>6810</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>11400</v>
+        <v>19170</v>
       </c>
       <c r="P10" t="n">
-        <v>15570</v>
+        <v>8610</v>
       </c>
       <c r="Q10" t="n">
-        <v>24605.7</v>
+        <v>241232.4</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>29040</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>64890</v>
+        <v>79380</v>
       </c>
       <c r="M11" t="n">
-        <v>2460</v>
+        <v>5520</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5100</v>
+        <v>14970</v>
       </c>
       <c r="P11" t="n">
-        <v>14610</v>
+        <v>14850</v>
       </c>
       <c r="Q11" t="n">
-        <v>15918.76</v>
+        <v>156066.3</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>30270</v>
+        <v>40080</v>
       </c>
       <c r="M12" t="n">
-        <v>2520</v>
+        <v>4620</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2550</v>
+        <v>3930</v>
       </c>
       <c r="P12" t="n">
-        <v>12480</v>
+        <v>11880</v>
       </c>
       <c r="Q12" t="n">
-        <v>9134.379999999999</v>
+        <v>89552.7</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10170</v>
+        <v>15420</v>
       </c>
       <c r="M13" t="n">
-        <v>990</v>
+        <v>4770</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3510</v>
+        <v>3300</v>
       </c>
       <c r="P13" t="n">
-        <v>13020</v>
+        <v>11970</v>
       </c>
       <c r="Q13" t="n">
-        <v>4271.18</v>
+        <v>41874.3</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3120</v>
+        <v>8730</v>
       </c>
       <c r="M14" t="n">
-        <v>540</v>
+        <v>2280</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>840</v>
+        <v>1440</v>
       </c>
       <c r="P14" t="n">
-        <v>15090</v>
+        <v>16410</v>
       </c>
       <c r="Q14" t="n">
-        <v>1385.72</v>
+        <v>13585.5</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1020</v>
+        <v>6030</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>780</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P15" t="n">
-        <v>24990</v>
+        <v>28770</v>
       </c>
       <c r="Q15" t="n">
-        <v>552.8200000000001</v>
+        <v>5419.8</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>2910</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P16" t="n">
-        <v>14460</v>
+        <v>17610</v>
       </c>
       <c r="Q16" t="n">
-        <v>221.88</v>
+        <v>2175.3</v>
       </c>
     </row>
     <row r="17">
@@ -24517,10 +24517,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>1260</v>
       </c>
       <c r="M17" t="n">
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>15360</v>
+        <v>18840</v>
       </c>
       <c r="Q17" t="n">
-        <v>131.73</v>
+        <v>1291.5</v>
       </c>
     </row>
     <row r="18">
@@ -24570,22 +24570,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1680</v>
       </c>
       <c r="M18" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>150</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>60</v>
-      </c>
       <c r="P18" t="n">
-        <v>17640</v>
+        <v>22800</v>
       </c>
       <c r="Q18" t="n">
-        <v>103.55</v>
+        <v>1015.2</v>
       </c>
     </row>
     <row r="19">
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>7530</v>
+        <v>19080</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.05</v>
+        <v>510.3</v>
       </c>
     </row>
     <row r="20">
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.81</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -24744,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.19</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="22">
@@ -24785,7 +24785,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="23">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4287.6</v>
+        <v>4460.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>19.2</v>
       </c>
       <c r="L5" t="n">
-        <v>38625.3</v>
+        <v>35513.1</v>
       </c>
       <c r="M5" t="n">
-        <v>255.6</v>
+        <v>435.6</v>
       </c>
       <c r="N5" t="n">
-        <v>143.7</v>
+        <v>169.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1026</v>
+        <v>1101</v>
       </c>
       <c r="P5" t="n">
-        <v>67.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1045.54</v>
+        <v>10250.37</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3337.5</v>
       </c>
       <c r="H6" t="n">
-        <v>8054.1</v>
+        <v>7814.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>31.43</v>
       </c>
       <c r="L6" t="n">
-        <v>70640.39999999999</v>
+        <v>69830.10000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>496.8</v>
+        <v>1092</v>
       </c>
       <c r="N6" t="n">
-        <v>370.5</v>
+        <v>490.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5190</v>
+        <v>4942.5</v>
       </c>
       <c r="P6" t="n">
-        <v>634.5</v>
+        <v>355.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>19159.92</v>
+        <v>187842.38</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>12901.5</v>
       </c>
       <c r="H7" t="n">
-        <v>14432.1</v>
+        <v>14957.7</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -25279,22 +25279,22 @@
         <v>31.26</v>
       </c>
       <c r="L7" t="n">
-        <v>145170</v>
+        <v>147186</v>
       </c>
       <c r="M7" t="n">
-        <v>1764</v>
+        <v>4809</v>
       </c>
       <c r="N7" t="n">
-        <v>138.6</v>
+        <v>226.8</v>
       </c>
       <c r="O7" t="n">
-        <v>7990.5</v>
+        <v>8431.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1440</v>
+        <v>1012.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>20475.37</v>
+        <v>200738.88</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>62575.5</v>
       </c>
       <c r="H8" t="n">
-        <v>4080</v>
+        <v>4870.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>44.9</v>
       </c>
       <c r="L8" t="n">
-        <v>169548</v>
+        <v>172977.3</v>
       </c>
       <c r="M8" t="n">
-        <v>2095.5</v>
+        <v>6385.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8829</v>
+        <v>9571.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3306</v>
+        <v>2382.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>26833.3</v>
+        <v>263071.53</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>79993.5</v>
       </c>
       <c r="H9" t="n">
-        <v>480</v>
+        <v>690</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>44.16</v>
       </c>
       <c r="L9" t="n">
-        <v>166260.6</v>
+        <v>180281.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3339</v>
+        <v>7014</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>12474</v>
+        <v>14272.5</v>
       </c>
       <c r="P9" t="n">
-        <v>5400</v>
+        <v>2880</v>
       </c>
       <c r="Q9" t="n">
-        <v>28659.81</v>
+        <v>280978.54</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>57570</v>
       </c>
       <c r="H10" t="n">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>29.58</v>
       </c>
       <c r="L10" t="n">
-        <v>99804.60000000001</v>
+        <v>116972.7</v>
       </c>
       <c r="M10" t="n">
-        <v>2856</v>
+        <v>5788.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>7980</v>
+        <v>13419</v>
       </c>
       <c r="P10" t="n">
-        <v>13234.5</v>
+        <v>7318.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>24605.7</v>
+        <v>241232.4</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>29040</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>8.09</v>
       </c>
       <c r="L11" t="n">
-        <v>64890</v>
+        <v>79380</v>
       </c>
       <c r="M11" t="n">
-        <v>2214</v>
+        <v>4968</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4335</v>
+        <v>12724.5</v>
       </c>
       <c r="P11" t="n">
-        <v>13149</v>
+        <v>13365</v>
       </c>
       <c r="Q11" t="n">
-        <v>15918.76</v>
+        <v>156066.3</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>0.93</v>
       </c>
       <c r="L12" t="n">
-        <v>30270</v>
+        <v>40080</v>
       </c>
       <c r="M12" t="n">
-        <v>2394</v>
+        <v>4389</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2550</v>
+        <v>3930</v>
       </c>
       <c r="P12" t="n">
-        <v>12480</v>
+        <v>11880</v>
       </c>
       <c r="Q12" t="n">
-        <v>9134.379999999999</v>
+        <v>89552.7</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10170</v>
+        <v>15420</v>
       </c>
       <c r="M13" t="n">
-        <v>990</v>
+        <v>4770</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3510</v>
+        <v>3300</v>
       </c>
       <c r="P13" t="n">
-        <v>13020</v>
+        <v>11970</v>
       </c>
       <c r="Q13" t="n">
-        <v>4271.18</v>
+        <v>41874.3</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3120</v>
+        <v>8730</v>
       </c>
       <c r="M14" t="n">
-        <v>540</v>
+        <v>2280</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>840</v>
+        <v>1440</v>
       </c>
       <c r="P14" t="n">
-        <v>15090</v>
+        <v>16410</v>
       </c>
       <c r="Q14" t="n">
-        <v>1385.72</v>
+        <v>13585.5</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1020</v>
+        <v>6030</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>780</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P15" t="n">
-        <v>24990</v>
+        <v>28770</v>
       </c>
       <c r="Q15" t="n">
-        <v>552.8200000000001</v>
+        <v>5419.8</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>270</v>
+        <v>2910</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P16" t="n">
-        <v>14460</v>
+        <v>17610</v>
       </c>
       <c r="Q16" t="n">
-        <v>221.88</v>
+        <v>2175.3</v>
       </c>
     </row>
     <row r="17">
@@ -25809,10 +25809,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>1260</v>
       </c>
       <c r="M17" t="n">
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>15360</v>
+        <v>18840</v>
       </c>
       <c r="Q17" t="n">
-        <v>131.73</v>
+        <v>1291.5</v>
       </c>
     </row>
     <row r="18">
@@ -25862,22 +25862,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1680</v>
       </c>
       <c r="M18" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>150</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>60</v>
-      </c>
       <c r="P18" t="n">
-        <v>17640</v>
+        <v>22800</v>
       </c>
       <c r="Q18" t="n">
-        <v>103.55</v>
+        <v>1015.2</v>
       </c>
     </row>
     <row r="19">
@@ -25915,10 +25915,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -25927,10 +25927,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>7530</v>
+        <v>19080</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.05</v>
+        <v>510.3</v>
       </c>
     </row>
     <row r="20">
@@ -25971,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.81</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -26024,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.19</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="22">
@@ -26077,7 +26077,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="23">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>24439320</v>
+        <v>25424280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>932178.09</v>
       </c>
       <c r="L5" t="n">
-        <v>6952554</v>
+        <v>6392358</v>
       </c>
       <c r="M5" t="n">
-        <v>89460</v>
+        <v>152460</v>
       </c>
       <c r="N5" t="n">
-        <v>24429</v>
+        <v>28815</v>
       </c>
       <c r="O5" t="n">
-        <v>174420</v>
+        <v>187170</v>
       </c>
       <c r="P5" t="n">
-        <v>4368</v>
+        <v>1326</v>
       </c>
       <c r="Q5" t="n">
-        <v>627322.64</v>
+        <v>6150222</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>180225</v>
       </c>
       <c r="H6" t="n">
-        <v>45908370</v>
+        <v>44543790</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1526309.3</v>
       </c>
       <c r="L6" t="n">
-        <v>12715272</v>
+        <v>12569418</v>
       </c>
       <c r="M6" t="n">
-        <v>173880</v>
+        <v>382200</v>
       </c>
       <c r="N6" t="n">
-        <v>62985</v>
+        <v>83385</v>
       </c>
       <c r="O6" t="n">
-        <v>882300</v>
+        <v>840225</v>
       </c>
       <c r="P6" t="n">
-        <v>41242.5</v>
+        <v>23107.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>11495953.35</v>
+        <v>112705425</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>696681</v>
       </c>
       <c r="H7" t="n">
-        <v>82262970</v>
+        <v>85258890</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -26571,22 +26571,22 @@
         <v>1517957.67</v>
       </c>
       <c r="L7" t="n">
-        <v>26130600</v>
+        <v>26493480</v>
       </c>
       <c r="M7" t="n">
-        <v>617400</v>
+        <v>1683150</v>
       </c>
       <c r="N7" t="n">
-        <v>23562</v>
+        <v>38556</v>
       </c>
       <c r="O7" t="n">
-        <v>1358385</v>
+        <v>1433355</v>
       </c>
       <c r="P7" t="n">
-        <v>93600</v>
+        <v>65812.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>12285219.46</v>
+        <v>120443328</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>3379077</v>
       </c>
       <c r="H8" t="n">
-        <v>23256000</v>
+        <v>27761850</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>2179970.18</v>
       </c>
       <c r="L8" t="n">
-        <v>30518640</v>
+        <v>31135914</v>
       </c>
       <c r="M8" t="n">
-        <v>733425</v>
+        <v>2234925</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1500930</v>
+        <v>1627155</v>
       </c>
       <c r="P8" t="n">
-        <v>214890</v>
+        <v>154869</v>
       </c>
       <c r="Q8" t="n">
-        <v>16099977.64</v>
+        <v>157842918</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4319649</v>
       </c>
       <c r="H9" t="n">
-        <v>2736000</v>
+        <v>3933000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>2144475.74</v>
       </c>
       <c r="L9" t="n">
-        <v>29926908</v>
+        <v>32450706</v>
       </c>
       <c r="M9" t="n">
-        <v>1168650</v>
+        <v>2454900</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2120580</v>
+        <v>2426325</v>
       </c>
       <c r="P9" t="n">
-        <v>351000</v>
+        <v>187200</v>
       </c>
       <c r="Q9" t="n">
-        <v>17195886.77</v>
+        <v>168587125.2</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>3108780</v>
       </c>
       <c r="H10" t="n">
-        <v>1881000</v>
+        <v>2394000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>1436286.48</v>
       </c>
       <c r="L10" t="n">
-        <v>17964828</v>
+        <v>21055086</v>
       </c>
       <c r="M10" t="n">
-        <v>999600</v>
+        <v>2025975</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1356600</v>
+        <v>2281230</v>
       </c>
       <c r="P10" t="n">
-        <v>860242.5</v>
+        <v>475702.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>14763422.88</v>
+        <v>144739440</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>1568160</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>392648.09</v>
       </c>
       <c r="L11" t="n">
-        <v>11680200</v>
+        <v>14288400</v>
       </c>
       <c r="M11" t="n">
-        <v>774900</v>
+        <v>1738800</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>736950</v>
+        <v>2163165</v>
       </c>
       <c r="P11" t="n">
-        <v>854685</v>
+        <v>868725</v>
       </c>
       <c r="Q11" t="n">
-        <v>9551257.560000001</v>
+        <v>93639780</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>45011.41</v>
       </c>
       <c r="L12" t="n">
-        <v>5448600</v>
+        <v>7214400</v>
       </c>
       <c r="M12" t="n">
-        <v>837900</v>
+        <v>1536150</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>433500</v>
+        <v>668100</v>
       </c>
       <c r="P12" t="n">
-        <v>811200</v>
+        <v>772200</v>
       </c>
       <c r="Q12" t="n">
-        <v>5480625.24</v>
+        <v>53731620</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1830600</v>
+        <v>2775600</v>
       </c>
       <c r="M13" t="n">
-        <v>346500</v>
+        <v>1669500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>596700</v>
+        <v>561000</v>
       </c>
       <c r="P13" t="n">
-        <v>846300</v>
+        <v>778050</v>
       </c>
       <c r="Q13" t="n">
-        <v>2562707.16</v>
+        <v>25124580</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>561600</v>
+        <v>1571400</v>
       </c>
       <c r="M14" t="n">
-        <v>189000</v>
+        <v>798000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>142800</v>
+        <v>244800</v>
       </c>
       <c r="P14" t="n">
-        <v>980850</v>
+        <v>1066650</v>
       </c>
       <c r="Q14" t="n">
-        <v>831432.6</v>
+        <v>8151300</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>183600</v>
+        <v>1085400</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>273000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5100</v>
+        <v>30600</v>
       </c>
       <c r="P15" t="n">
-        <v>1624350</v>
+        <v>1870050</v>
       </c>
       <c r="Q15" t="n">
-        <v>331691.76</v>
+        <v>3251880</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>48600</v>
+        <v>523800</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>283500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P16" t="n">
-        <v>939900</v>
+        <v>1144650</v>
       </c>
       <c r="Q16" t="n">
-        <v>133128.36</v>
+        <v>1305180</v>
       </c>
     </row>
     <row r="17">
@@ -27101,10 +27101,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>37800</v>
+        <v>226800</v>
       </c>
       <c r="M17" t="n">
-        <v>199500</v>
+        <v>231000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>998400</v>
+        <v>1224600</v>
       </c>
       <c r="Q17" t="n">
-        <v>79039.8</v>
+        <v>774900</v>
       </c>
     </row>
     <row r="18">
@@ -27154,22 +27154,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>21600</v>
+        <v>302400</v>
       </c>
       <c r="M18" t="n">
-        <v>52500</v>
+        <v>21000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1146600</v>
+        <v>1482000</v>
       </c>
       <c r="Q18" t="n">
-        <v>62130.24</v>
+        <v>609120</v>
       </c>
     </row>
     <row r="19">
@@ -27207,10 +27207,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -27219,10 +27219,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>489450</v>
+        <v>1240200</v>
       </c>
       <c r="Q19" t="n">
-        <v>31230.36</v>
+        <v>306180</v>
       </c>
     </row>
     <row r="20">
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>5287.68</v>
+        <v>51840</v>
       </c>
     </row>
     <row r="21">
@@ -27316,7 +27316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -27328,7 +27328,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>716.04</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="22">
@@ -27369,7 +27369,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4020.84</v>
+        <v>39420</v>
       </c>
     </row>
     <row r="23">
@@ -27692,7 +27692,7 @@
         <v>141600</v>
       </c>
       <c r="H4" t="n">
-        <v>25980</v>
+        <v>26130</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>87</v>
       </c>
       <c r="L4" t="n">
-        <v>403170</v>
+        <v>437340</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>72540</v>
+        <v>70500</v>
       </c>
       <c r="P4" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>41617.82</v>
+        <v>579488.58</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>84030</v>
       </c>
       <c r="H5" t="n">
-        <v>18960</v>
+        <v>20010</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>46</v>
       </c>
       <c r="L5" t="n">
-        <v>200880</v>
+        <v>221730</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>50190</v>
+        <v>51000</v>
       </c>
       <c r="P5" t="n">
-        <v>1170</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>23637.55</v>
+        <v>329130.45</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>51450</v>
       </c>
       <c r="H6" t="n">
-        <v>19440</v>
+        <v>19860</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>19</v>
       </c>
       <c r="L6" t="n">
-        <v>106740</v>
+        <v>115200</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>31950</v>
+        <v>38580</v>
       </c>
       <c r="P6" t="n">
-        <v>2370</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8417.389999999999</v>
+        <v>117204.12</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>15810</v>
       </c>
       <c r="H7" t="n">
-        <v>2520</v>
+        <v>3090</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>38820</v>
+        <v>43410</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>13620</v>
+        <v>16110</v>
       </c>
       <c r="P7" t="n">
-        <v>3480</v>
+        <v>450</v>
       </c>
       <c r="Q7" t="n">
-        <v>3766.38</v>
+        <v>52443.27</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>600</v>
       </c>
       <c r="H8" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6510</v>
+        <v>8040</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5970</v>
+        <v>10200</v>
       </c>
       <c r="P8" t="n">
-        <v>4680</v>
+        <v>1110</v>
       </c>
       <c r="Q8" t="n">
-        <v>209.89</v>
+        <v>2922.48</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1290</v>
+        <v>2340</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2280</v>
+        <v>7680</v>
       </c>
       <c r="P9" t="n">
-        <v>5280</v>
+        <v>3540</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.34</v>
+        <v>478.17</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>330</v>
+        <v>2610</v>
       </c>
       <c r="P10" t="n">
-        <v>5520</v>
+        <v>9660</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.42</v>
+        <v>242.55</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>1680</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>2610</v>
+        <v>6300</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.91</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1590</v>
+        <v>5610</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.43</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="13">
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>270</v>
+        <v>1230</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,7 +28246,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6825.6</v>
+        <v>7203.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>15.23</v>
       </c>
       <c r="L5" t="n">
-        <v>42184.8</v>
+        <v>46563.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2509.5</v>
+        <v>2550</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1181.88</v>
+        <v>16456.52</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2572.5</v>
       </c>
       <c r="H6" t="n">
-        <v>11080.8</v>
+        <v>11320.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>39493.8</v>
+        <v>42624</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>7987.5</v>
+        <v>9645</v>
       </c>
       <c r="P6" t="n">
-        <v>355.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6313.04</v>
+        <v>87903.09</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>2371.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1839.6</v>
+        <v>2255.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>1.28</v>
       </c>
       <c r="L7" t="n">
-        <v>23292</v>
+        <v>26046</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4767</v>
+        <v>5638.5</v>
       </c>
       <c r="P7" t="n">
-        <v>870</v>
+        <v>112.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3013.1</v>
+        <v>41954.62</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>390</v>
       </c>
       <c r="H8" t="n">
-        <v>408</v>
+        <v>535.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4622.1</v>
+        <v>5708.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2686.5</v>
+        <v>4590</v>
       </c>
       <c r="P8" t="n">
-        <v>1778.4</v>
+        <v>421.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>199.39</v>
+        <v>2776.36</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>127.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1044.9</v>
+        <v>1895.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1254</v>
+        <v>4224</v>
       </c>
       <c r="P9" t="n">
-        <v>2640</v>
+        <v>1770</v>
       </c>
       <c r="Q9" t="n">
-        <v>33.31</v>
+        <v>463.82</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>373.8</v>
+        <v>2162.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>231</v>
+        <v>1827</v>
       </c>
       <c r="P10" t="n">
-        <v>4692</v>
+        <v>8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.42</v>
+        <v>242.55</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>1680</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="P11" t="n">
-        <v>2349</v>
+        <v>5670</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.91</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1590</v>
+        <v>5610</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.43</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="13">
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>270</v>
+        <v>1230</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,7 +29538,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>38905920</v>
+        <v>41060520</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>739313.66</v>
       </c>
       <c r="L5" t="n">
-        <v>7593264</v>
+        <v>8381394</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>426615</v>
+        <v>433500</v>
       </c>
       <c r="P5" t="n">
-        <v>1521</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>709126.52</v>
+        <v>9873913.5</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>138915</v>
       </c>
       <c r="H6" t="n">
-        <v>63160560</v>
+        <v>64525140</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>467739.95</v>
       </c>
       <c r="L6" t="n">
-        <v>7108884</v>
+        <v>7672320</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1357875</v>
+        <v>1639650</v>
       </c>
       <c r="P6" t="n">
-        <v>23107.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3787824.06</v>
+        <v>52741854</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>128061</v>
       </c>
       <c r="H7" t="n">
-        <v>10485720</v>
+        <v>12857490</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>4192560</v>
+        <v>4688280</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>810390</v>
+        <v>958545</v>
       </c>
       <c r="P7" t="n">
-        <v>56550</v>
+        <v>7312.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1807862.54</v>
+        <v>25172769.6</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>21060</v>
       </c>
       <c r="H8" t="n">
-        <v>2325600</v>
+        <v>3052350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>831978</v>
+        <v>1027512</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>456705</v>
+        <v>780300</v>
       </c>
       <c r="P8" t="n">
-        <v>115596</v>
+        <v>27417</v>
       </c>
       <c r="Q8" t="n">
-        <v>119635.7</v>
+        <v>1665813.6</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>188082</v>
+        <v>341172</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>213180</v>
+        <v>718080</v>
       </c>
       <c r="P9" t="n">
-        <v>171600</v>
+        <v>115050</v>
       </c>
       <c r="Q9" t="n">
-        <v>19986.64</v>
+        <v>278294.94</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>67284</v>
+        <v>389286</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>39270</v>
+        <v>310590</v>
       </c>
       <c r="P10" t="n">
-        <v>304980</v>
+        <v>533715</v>
       </c>
       <c r="Q10" t="n">
-        <v>10451.7</v>
+        <v>145530</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>1710000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>302400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>8670</v>
       </c>
       <c r="P11" t="n">
-        <v>152685</v>
+        <v>368550</v>
       </c>
       <c r="Q11" t="n">
-        <v>2346.3</v>
+        <v>32670</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5400</v>
+        <v>194400</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>103350</v>
+        <v>364650</v>
       </c>
       <c r="Q12" t="n">
-        <v>255.96</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>17550</v>
+        <v>79950</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.31999999999999</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1950</v>
+        <v>13650</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
